--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -589,7 +589,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,7 +589,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -956,262 +956,6 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2035469309464719545</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic/status/2035469309464719545</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>acroboatic</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>saudaaaas</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>@emiratesislamic 
-Kindly resolve this urgently and release my funds immediately</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Kindly resolve this urgently and release my funds immediately</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Mar 21, 2026 · 9:31 PM UTC</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-03-21T21:31:00Z</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2035469171564384606</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic/status/2035469171564384606</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>acroboatic</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>saudaaaas</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>@emiratesislamic
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Mar 21, 2026 · 9:30 PM UTC</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-03-21T21:30:00Z</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2034756691150217623</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/Ben252024/status/2034756691150217623</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/Ben252024</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ben252024</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Mar 19</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Mar 19, 2026 · 10:19 PM UTC</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-03-19T22:19:00Z</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
         <v>2</v>
       </c>
     </row>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,7 +589,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -956,6 +956,262 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2035469309464719545</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic/status/2035469309464719545</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>acroboatic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>saudaaaas</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+Kindly resolve this urgently and release my funds immediately</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
+Kindly resolve this urgently and release my funds immediately</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mar 21, 2026 · 9:31 PM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-03-21T21:31:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2035469171564384606</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic/status/2035469171564384606</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>acroboatic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>saudaaaas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>@emiratesislamic
+Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
+Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mar 21, 2026 · 9:30 PM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-03-21T21:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2034756691150217623</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/Ben252024/status/2034756691150217623</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/Ben252024</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ben252024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Mar 19</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Mar 19, 2026 · 10:19 PM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-03-19T22:19:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>2</v>
       </c>
     </row>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -675,7 +675,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -589,7 +589,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -589,7 +589,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,7 +589,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 21</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 21</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -881,43 +881,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2034756691150217623</t>
+          <t>2035469309464719545</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/Ben252024/status/2034756691150217623</t>
+          <t>https://x.com/acroboatic/status/2035469309464719545</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/Ben252024</t>
+          <t>https://x.com/acroboatic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben252024</t>
+          <t>acroboatic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>saudaaaas</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
+          <t>@emiratesislamic 
+Kindly resolve this urgently and release my funds immediately</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
+Kindly resolve this urgently and release my funds immediately</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -927,17 +929,17 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mar 19</t>
+          <t>Mar 21</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Mar 19, 2026 · 10:19 PM UTC</t>
+          <t>Mar 21, 2026 · 9:31 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-03-19T22:19:00Z</t>
+          <t>2026-03-21T21:31:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -956,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -965,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2035469309464719545</t>
+          <t>2035469171564384606</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2035469309464719545</t>
+          <t>https://x.com/acroboatic/status/2035469171564384606</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -996,14 +998,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-Kindly resolve this urgently and release my funds immediately</t>
+          <t>@emiratesislamic
+Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Kindly resolve this urgently and release my funds immediately</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
+Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1013,17 +1015,17 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 21</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Mar 21, 2026 · 9:31 PM UTC</t>
+          <t>Mar 21, 2026 · 9:30 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-03-21T21:31:00Z</t>
+          <t>2026-03-21T21:30:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1042,177 +1044,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2035469171564384606</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic/status/2035469171564384606</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>acroboatic</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>saudaaaas</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>@emiratesislamic
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Mar 21, 2026 · 9:30 PM UTC</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-03-21T21:30:00Z</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2034756691150217623</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/Ben252024/status/2034756691150217623</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/Ben252024</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ben252024</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Mar 19</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Mar 19, 2026 · 10:19 PM UTC</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-03-19T22:19:00Z</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,45 +541,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2035469309464719545</t>
+          <t>2036045570406535456</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2035469309464719545</t>
+          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>acroboatic</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>saudaaaas</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-Kindly resolve this urgently and release my funds immediately</t>
+          <t>الحين وقتك مع الإمارات الإسلامي.
+احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
+عروض حصرية للإماراتيين.
+العرض ساري حتى 31 مارس 2026.
+تُطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Kindly resolve this urgently and release my funds immediately</t>
+          <t>الحين وقتك مع الإمارات الإسلامي.
+احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
+عروض حصرية للإماراتيين.
+العرض ساري حتى 31 مارس 2026.
+تُطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -589,25 +595,21 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mar 21</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Mar 21, 2026 · 9:31 PM UTC</t>
+          <t>Mar 23, 2026 · 11:41 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-03-21T21:31:00Z</t>
+          <t>2026-03-23T11:41:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -618,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -627,73 +629,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2035469171564384606</t>
+          <t>2035996471896449306</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2035469171564384606</t>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>acroboatic</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>saudaaaas</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>@emiratesislamic
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['Ben252024']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mar 21</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Mar 21, 2026 · 9:30 PM UTC</t>
+          <t>Mar 23, 2026 · 8:26 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-03-21T21:30:00Z</t>
+          <t>2026-03-23T08:26:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -713,67 +713,65 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2034937309435752463</t>
+          <t>2035989928291488100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/NazeerM61358/status/2034937309435752463</t>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/NazeerM61358</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NazeerM61358</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>V.M.Nazeer Basha 🇮🇳</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1995135750833418240/5Vg5uS1A_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Masha Allah world 🌍 the great crown prince 👑 hamdan mohammad al Arab Emirates islamic leadership people armed forces  Home land my god protect eid al fitr wishes in uae</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masha Allah world 🌍 the great crown prince 👑 hamdan mohammad al Arab Emirates islamic leadership people armed forces  Home land my god protect eid al fitr wishes in uae</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['HamdanMohammed']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mar 20</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 · 10:17 AM UTC</t>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-03-20T10:17:00Z</t>
+          <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -788,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>38</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
@@ -797,67 +795,65 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2034892902359498836</t>
+          <t>2035989927905693845</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/NazeerM61358/status/2034892902359498836</t>
+          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/NazeerM61358</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NazeerM61358</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>V.M.Nazeer Basha 🇮🇳</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1995135750833418240/5Vg5uS1A_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Masha Allah world 🌍 the best poltison leader hamadn bin Zayed Arab Emirates islamic leadership people armed forces my god protect Ramadan eid mubarak in uae</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masha Allah world 🌍 the best poltison leader hamadn bin Zayed Arab Emirates islamic leadership people armed forces my god protect Ramadan eid mubarak in uae</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['HamdanBinZayed']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mar 20</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 · 7:20 AM UTC</t>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-03-20T07:20:00Z</t>
+          <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -872,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
@@ -881,45 +877,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2035469309464719545</t>
+          <t>2035627541164077389</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2035469309464719545</t>
+          <t>https://x.com/emiratesislamic/status/2035627541164077389</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>acroboatic</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>saudaaaas</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-Kindly resolve this urgently and release my funds immediately</t>
+          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
+What if a brand offer asks for your card details and CVV?</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Kindly resolve this urgently and release my funds immediately</t>
+          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
+What if a brand offer asks for your card details and CVV?</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -929,25 +925,21 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mar 21</t>
+          <t>Mar 22</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Mar 21, 2026 · 9:31 PM UTC</t>
+          <t>Mar 22, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-03-21T21:31:00Z</t>
+          <t>2026-03-22T08:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -958,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
@@ -967,45 +959,51 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2035469171564384606</t>
+          <t>2036045570406535456</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2035469171564384606</t>
+          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>acroboatic</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>saudaaaas</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>@emiratesislamic
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
+          <t>الحين وقتك مع الإمارات الإسلامي.
+احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
+عروض حصرية للإماراتيين.
+العرض ساري حتى 31 مارس 2026.
+تُطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
-Hi, I’m extremely disappointed. A declined international transfer has resulted in my funds being put on hold. E&amp;amp;Money has already confirmed they are not holding anything from their side. Why should I wait 14 days to access my own money? This is unacceptable.</t>
+          <t>الحين وقتك مع الإمارات الإسلامي.
+احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
+عروض حصرية للإماراتيين.
+العرض ساري حتى 31 مارس 2026.
+تُطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1015,25 +1013,21 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mar 21</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Mar 21, 2026 · 9:30 PM UTC</t>
+          <t>Mar 23, 2026 · 11:41 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-03-21T21:30:00Z</t>
+          <t>2026-03-23T11:41:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1044,7 +1038,337 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2035996471896449306</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['Ben252024']</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:26:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2035989928291488100</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2035989927905693845</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2035627541164077389</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035627541164077389</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
+What if a brand offer asks for your card details and CVV?</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
+What if a brand offer asks for your card details and CVV?</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -761,7 +761,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1179,7 +1179,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>192</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -1261,7 +1261,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -761,7 +761,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1179,7 +1179,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -1261,7 +1261,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -761,7 +761,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1179,7 +1179,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -1261,7 +1261,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -761,7 +761,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1179,7 +1179,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -1261,7 +1261,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -761,7 +761,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -1013,7 +1013,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1179,7 +1179,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1261,7 +1261,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -617,10 +617,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -761,7 +761,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6">
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2035627541164077389</t>
+          <t>2036045570406535456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035627541164077389</t>
+          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -907,88 +907,6 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
-What if a brand offer asks for your card details and CVV?</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
-What if a brand offer asks for your card details and CVV?</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Mar 22</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Mar 22, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-03-22T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2036045570406535456</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -997,7 +915,7 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -1006,24 +924,108 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 11:41 AM UTC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-03-23T11:41:00Z</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2035996471896449306</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['Ben252024']</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 11:41 AM UTC</t>
+          <t>Mar 23, 2026 · 8:26 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-03-23T11:41:00Z</t>
+          <t>2026-03-23T08:26:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1038,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>120</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1047,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2035996471896449306</t>
+          <t>2035989928291488100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1078,36 +1080,34 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['Ben252024']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:26 AM UTC</t>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-03-23T08:26:00Z</t>
+          <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2035989928291488100</t>
+          <t>2035989927905693845</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
+          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1162,14 +1162,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1179,7 +1179,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1204,171 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2035989927905693845</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-03-23T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2035627541164077389</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035627541164077389</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
-What if a brand offer asks for your card details and CVV?</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
-What if a brand offer asks for your card details and CVV?</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Mar 22</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Mar 22, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-03-22T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -595,7 +595,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -611,7 +611,7 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +679,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -761,7 +761,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
@@ -931,7 +931,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -956,7 +956,7 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1097,7 +1097,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9">
@@ -1179,7 +1179,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,12 +541,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2036045570406535456</t>
+          <t>2036410734163247450</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
+          <t>https://x.com/emiratesislamic/status/2036410734163247450</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -571,6 +571,1200 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['Abdulla40446316']</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2036399322183442876</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036399322183442876</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>54m</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:06:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2036399290717704546</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036399290717704546</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>54m</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:06:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2036385610118623239</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 10:12 AM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-03-24T10:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2036385607883034826</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036385607883034826</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+📅Payment holiday of up to 6 months</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+📅Payment holiday of up to 6 months</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 10:12 AM UTC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-03-24T10:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2036382130784047605</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:58:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2036382128359751773</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036382128359751773</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+📅فترة سماح السداد تصل إلى 6 أشهر</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+📅فترة سماح السداد تصل إلى 6 أشهر</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:58:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2036353357435248836</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic/status/2036353357435248836</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>acroboatic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>saudaaaas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Thanks
+I have followed your page now</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Thanks
+I have followed your page now</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 8:04 AM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:04:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2036352538568802661</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic/status/2036352538568802661</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>acroboatic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>saudaaaas</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2036331891541127358</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/Ben252024/status/2036331891541127358</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/Ben252024</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ben252024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>When ?</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>When ?</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 6:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-03-24T06:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2036319304132473271</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['wasishion']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:48:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2036313897985020336</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313897985020336</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2036313593797288395</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313593797288395</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:26:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2036313549929107798</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313549929107798</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2036045570406535456</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -579,7 +1773,7 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -588,325 +1782,1261 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 11:41 AM UTC</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2026-03-23T11:41:00Z</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V2" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="V16" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2035996471896449306</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>['Ben252024']</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:26:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2035996471896449306</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2035989928291488100</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['Ben252024']</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:26 AM UTC</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-03-23T08:26:00Z</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2035989928291488100</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>2035989927905693845</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
 Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
 Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2036410734163247450</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036410734163247450</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['Abdulla40446316']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2036399322183442876</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036399322183442876</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>54m</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:06:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2036399290717704546</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036399290717704546</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>55m</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:06:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2036385610118623239</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 10:12 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-03-24T10:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2036385607883034826</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036385607883034826</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+📅Payment holiday of up to 6 months</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+📅Payment holiday of up to 6 months</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 10:12 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-03-24T10:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2036382130784047605</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:58:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2036382128359751773</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036382128359751773</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+📅فترة سماح السداد تصل إلى 6 أشهر</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+📅فترة سماح السداد تصل إلى 6 أشهر</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:58:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2036319304132473271</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>['wasishion']</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:48:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2036313897985020336</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313897985020336</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2036313593797288395</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313593797288395</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:26:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2036313549929107798</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313549929107798</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>2036045570406535456</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -915,7 +3045,7 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -924,287 +3054,725 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 11:41 AM UTC</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>2026-03-23T11:41:00Z</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="V31" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>2035996471896449306</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>['Ben252024']</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 8:26 AM UTC</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>2026-03-23T08:26:00Z</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>2035989928291488100</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>2035989927905693845</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
         <is>
           <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
 Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
 Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>168</v>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2036385610118623239</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 10:12 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-03-24T10:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2036382130784047605</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:58:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2036353357435248836</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic/status/2036353357435248836</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>acroboatic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>saudaaaas</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Thanks
+I have followed your page now</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Thanks
+I have followed your page now</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 8:04 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:04:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2036352538568802661</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic/status/2036352538568802661</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/acroboatic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>acroboatic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>saudaaaas</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2036331891541127358</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/Ben252024/status/2036331891541127358</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/Ben252024</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ben252024</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>When ?</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>When ?</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 6:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-03-24T06:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>54m</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -759,7 +759,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>54m</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -845,7 +845,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -933,7 +933,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1019,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1209,7 +1209,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1297,7 +1297,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>278</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19">
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>54m</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>55m</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2375,7 +2375,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
@@ -2463,7 +2463,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
@@ -2549,7 +2549,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -2637,7 +2637,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -3086,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>278</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34">
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35">
@@ -3395,7 +3395,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3485,7 +3485,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3591,7 +3591,7 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3679,7 +3679,7 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,7 +591,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -759,7 +759,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -845,7 +845,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -933,7 +933,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1019,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2036045570406535456</t>
+          <t>2036410734163247450</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
+          <t>https://x.com/emiratesislamic/status/2036410734163247450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1766,55 +1766,51 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>الحين وقتك مع الإمارات الإسلامي.
-احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
-عروض حصرية للإماراتيين.
-العرض ساري حتى 31 مارس 2026.
-تُطبق الشروط والأحكام.</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>الحين وقتك مع الإمارات الإسلامي.
-احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
-عروض حصرية للإماراتيين.
-العرض ساري حتى 31 مارس 2026.
-تُطبق الشروط والأحكام.</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>['Abdulla40446316']</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Mar 23</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 11:41 AM UTC</t>
+          <t>Mar 24, 2026 · 11:52 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-03-23T11:41:00Z</t>
+          <t>2026-03-24T11:52:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>202</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1823,12 +1819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2035996471896449306</t>
+          <t>2036399322183442876</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+          <t>https://x.com/emiratesislamic/status/2036399322183442876</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1868,28 +1864,28 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>['Ben252024']</t>
+          <t>['acroboatic']</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Mar 23</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:26 AM UTC</t>
+          <t>Mar 24, 2026 · 11:06 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-03-23T08:26:00Z</t>
+          <t>2026-03-24T11:06:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1898,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -1907,12 +1903,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2035989928291488100</t>
+          <t>2036399290717704546</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
+          <t>https://x.com/emiratesislamic/status/2036399290717704546</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1938,34 +1934,36 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mar 23</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+          <t>Mar 24, 2026 · 11:06 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-03-23T08:00:00Z</t>
+          <t>2026-03-24T11:06:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -1980,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>295</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -1989,12 +1987,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2035989927905693845</t>
+          <t>2036385610118623239</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
+          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2020,14 +2018,18 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2037,21 +2039,25 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Mar 23</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+          <t>Mar 24, 2026 · 10:12 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-03-23T08:00:00Z</t>
+          <t>2026-03-24T10:12:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
@@ -2062,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>187</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -2071,12 +2077,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2036410734163247450</t>
+          <t>2036385607883034826</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036410734163247450</t>
+          <t>https://x.com/emiratesislamic/status/2036385607883034826</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2102,42 +2108,42 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+📅Payment holiday of up to 6 months</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+📅Payment holiday of up to 6 months</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['Abdulla40446316']</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:52 AM UTC</t>
+          <t>Mar 24, 2026 · 10:12 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-03-24T11:52:00Z</t>
+          <t>2026-03-24T10:12:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2146,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -2155,12 +2161,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2036399322183442876</t>
+          <t>2036382130784047605</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036399322183442876</t>
+          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2186,40 +2192,46 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مارس 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['acroboatic']</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+          <t>Mar 24, 2026 · 9:58 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-03-24T11:06:00Z</t>
+          <t>2026-03-24T09:58:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+        </is>
+      </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
@@ -2230,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -2239,12 +2251,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2036399290717704546</t>
+          <t>2036382128359751773</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036399290717704546</t>
+          <t>https://x.com/emiratesislamic/status/2036382128359751773</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2270,42 +2282,42 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+📅فترة سماح السداد تصل إلى 6 أشهر</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+📅فترة سماح السداد تصل إلى 6 أشهر</t>
         </is>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>['acroboatic']</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+          <t>Mar 24, 2026 · 9:58 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-03-24T11:06:00Z</t>
+          <t>2026-03-24T09:58:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2314,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
@@ -2323,12 +2335,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2036385610118623239</t>
+          <t>2036319304132473271</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2353,6 +2365,342 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['wasishion']</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:48:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2036313897985020336</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313897985020336</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2036313593797288395</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313593797288395</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:26:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2036313549929107798</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313549929107798</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2036385610118623239</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
         <is>
           <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
 📅Offer valid till 31 March 2026.
@@ -2360,7 +2708,7 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
 📅Offer valid till 31 March 2026.
@@ -2368,165 +2716,81 @@
 &lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 10:12 AM UTC</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>2026-03-24T10:12:00Z</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
         </is>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>45</v>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>50</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2036385607883034826</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036385607883034826</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2036382130784047605</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-📅Payment holiday of up to 6 months</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-📅Payment holiday of up to 6 months</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 10:12 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-03-24T10:12:00Z</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2036382130784047605</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
 📅يسري لغاية 31 مارس 2026.
@@ -2534,7 +2798,7 @@
 emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
 📅يسري لغاية 31 مارس 2026.
@@ -2542,286 +2806,34 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 9:58 AM UTC</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>2026-03-24T09:58:00Z</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
         </is>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2036382128359751773</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036382128359751773</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
-📅فترة سماح السداد تصل إلى 6 أشهر</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
-📅فترة سماح السداد تصل إلى 6 أشهر</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 9:58 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-03-24T09:58:00Z</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2036319304132473271</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>['wasishion']</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 5:48 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-03-24T05:48:00Z</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2036313897985020336</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036313897985020336</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>['acroboatic']</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 5:27 AM UTC</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-03-24T05:27:00Z</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2830,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
@@ -2839,43 +2851,45 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2036313593797288395</t>
+          <t>2036353357435248836</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313593797288395</t>
+          <t>https://x.com/acroboatic/status/2036353357435248836</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/acroboatic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>acroboatic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>saudaaaas</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Thanks
+I have followed your page now</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Thanks
+I have followed your page now</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -2884,28 +2898,28 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>['acroboatic']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:26 AM UTC</t>
+          <t>Mar 24, 2026 · 8:04 AM UTC</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-03-24T05:26:00Z</t>
+          <t>2026-03-24T08:04:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2914,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -2923,43 +2937,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2036313549929107798</t>
+          <t>2036352538568802661</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313549929107798</t>
+          <t>https://x.com/acroboatic/status/2036352538568802661</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/acroboatic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>acroboatic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>saudaaaas</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -2968,22 +2986,22 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>['acroboatic']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:25 AM UTC</t>
+          <t>Mar 24, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-03-24T05:25:00Z</t>
+          <t>2026-03-24T08:00:00Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
@@ -2998,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -3007,772 +3025,82 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2036045570406535456</t>
+          <t>2036331891541127358</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
+          <t>https://x.com/Ben252024/status/2036331891541127358</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Ben252024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Ben252024</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>الحين وقتك مع الإمارات الإسلامي.
-احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
-عروض حصرية للإماراتيين.
-العرض ساري حتى 31 مارس 2026.
-تُطبق الشروط والأحكام.</t>
+          <t>When ?</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>الحين وقتك مع الإمارات الإسلامي.
-احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
-عروض حصرية للإماراتيين.
-العرض ساري حتى 31 مارس 2026.
-تُطبق الشروط والأحكام.</t>
+          <t>When ?</t>
         </is>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Mar 23</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 11:41 AM UTC</t>
+          <t>Mar 24, 2026 · 6:38 AM UTC</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-03-23T11:41:00Z</t>
+          <t>2026-03-24T06:38:00Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2035996471896449306</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>['Ben252024']</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Mar 23</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:26 AM UTC</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2026-03-23T08:26:00Z</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2035989928291488100</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Mar 23</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2026-03-23T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2035989927905693845</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Mar 23</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2026-03-23T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2036385610118623239</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 March 2026.
-Terms &amp; Conditions apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 March 2026.
-Terms &amp;amp; Conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 10:12 AM UTC</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-03-24T10:12:00Z</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
-        </is>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2036382130784047605</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مارس 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مارس 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 9:58 AM UTC</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-03-24T09:58:00Z</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2036353357435248836</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic/status/2036353357435248836</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>acroboatic</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>saudaaaas</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Thanks
-I have followed your page now</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Thanks
-I have followed your page now</t>
-        </is>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 8:04 AM UTC</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2026-03-24T08:04:00Z</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
         <v>9</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2036352538568802661</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic/status/2036352538568802661</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>acroboatic</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>saudaaaas</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Hi, happy to connect.
-I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
-I’m available now, please feel free to message</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Hi, happy to connect.
-I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
-I’m available now, please feel free to message</t>
-        </is>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2026-03-24T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2036331891541127358</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://x.com/Ben252024/status/2036331891541127358</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://x.com/Ben252024</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Ben252024</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>When ?</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>When ?</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 6:38 AM UTC</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2026-03-24T06:38:00Z</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -759,7 +759,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -845,7 +845,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -933,7 +933,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1019,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2039,7 +2039,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -2127,7 +2127,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
@@ -2213,7 +2213,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2301,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -2723,7 +2723,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
@@ -2813,7 +2813,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2842,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,81 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2036879879950786787</t>
+          <t>2037148064096415790</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae/status/2036879879950786787</t>
+          <t>https://x.com/emiratesislamic/status/2037148064096415790</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>centralbankuae</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Central Bank of the UAE</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>Stay safe and bank easily with EI + and businessONLINE.
+#EmiratesIslamic</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
-Best regards,
-Central Bank of the UAE</t>
+          <t>Stay safe and bank easily with EI + and businessONLINE.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['abuzubayr1987', 'emiratesislamic', 'JamalIslamic']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 6:56 PM UTC</t>
+          <t>Mar 26, 2026 · 12:42 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-03-25T18:56:00Z</t>
+          <t>2026-03-26T12:42:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -628,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -637,81 +627,75 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2036838112907972926</t>
+          <t>2037148052255875186</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/Tiamat531229675/status/2036838112907972926</t>
+          <t>https://x.com/emiratesislamic/status/2037148052255875186</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/Tiamat531229675</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tiamat531229675</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tiamat</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1650968397432373248/bTVP9Hqc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>If you consider the Emirates Islamic cool.
-I think all muslim societies should be that way.
-I never said I disliked it.
-I advocate for it.
-I only go through muslim X and see them horrified by the Emirates allowing 'unIslamic' laws being allowed.</t>
+          <t>ابقّ آمناً وأنجز معاملاتك المصرفية بسهولة مع تطبيق + EI ومنصة businessONLINE.
+#الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>If you consider the Emirates Islamic cool.
-I think all muslim societies should be that way.
-I never said I disliked it.
-I advocate for it.
-I only go through muslim X and see them horrified by the Emirates allowing &amp;#39;unIslamic&amp;#39; laws being allowed.</t>
+          <t>ابقّ آمناً وأنجز معاملاتك المصرفية بسهولة مع تطبيق + EI ومنصة businessONLINE.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['KarrDriver', 'WallStreetMav', 'EndWokeness']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:10 PM UTC</t>
+          <t>Mar 26, 2026 · 12:41 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-03-25T16:10:00Z</t>
+          <t>2026-03-26T12:41:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -720,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -729,77 +713,75 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2036821858868416788</t>
+          <t>2037144761212023024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987/status/2036821858868416788</t>
+          <t>https://x.com/emiratesislamic/status/2037144761212023024</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>abuzubayr1987</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Safwan</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>@centralbankuae 
-I am left in a precarious situation having no living expenses for the coming weeks after @emiratesislamic bank deducted 100% against my credit card dues without notice. After having a call they have been inconsiderate over my situation.
-@JamalIslamic</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>&lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; 
-I am left in a precarious situation having no living expenses for the coming weeks after &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; bank deducted 100% against my credit card dues without notice. After having a call they have been inconsiderate over my situation.
-&lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 3:05 PM UTC</t>
+          <t>Mar 26, 2026 · 12:28 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-03-25T15:05:00Z</t>
+          <t>2026-03-26T12:28:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/centralbankuae', 'https://x.com/emiratesislamic', 'https://x.com/JamalIslamic']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -817,43 +799,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2036796287182647587</t>
+          <t>2037144700109337063</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/dhara_katariya/status/2036796287182647587</t>
+          <t>https://x.com/emiratesislamic/status/2037144700109337063</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/dhara_katariya</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dhara_katariya</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dhara Katariya</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1205157338639978497/HK2x6jCp_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>@Maersk maersk kanoo emirates why dont you check with your bank why you didn't received it? Your executives saying we didnt received 100 times but atleast for once ask your bank. Your client is stressed.</t>
+          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better.. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;a href="/Maersk" title="Maersk"&gt;@Maersk&lt;/a&gt; maersk kanoo emirates why dont you check with your bank why you didn&amp;#39;t received it? Your executives saying we didnt received 100 times but atleast for once ask your bank. Your client is stressed.</t>
+          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better.. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -862,30 +844,26 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>['dhara_katariya', 'emiratesislamic']</t>
+          <t>['abuzubayr1987']</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:24 PM UTC</t>
+          <t>Mar 26, 2026 · 12:28 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-03-25T13:24:00Z</t>
+          <t>2026-03-26T12:28:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/Maersk']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>0</v>
       </c>
@@ -896,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -905,47 +883,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2036794106270413038</t>
+          <t>2037131478010929182</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/dhara_katariya/status/2036794106270413038</t>
+          <t>https://x.com/kdkingdongmedia/status/2037131478010929182</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/dhara_katariya</t>
+          <t>https://x.com/kdkingdongmedia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>dhara_katariya</t>
+          <t>kdkingdongmedia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dhara Katariya</t>
+          <t>KD Kingdong Media</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1205157338639978497/HK2x6jCp_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1778323297215848448/5mY7zvci_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@emiratesislamic A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
- ETE ID EPHCOP07809C8DTA
-The amount is debited but maersk kanoo didn't received it. We dont have any revert from the bank where the payment is .Resolve it</t>
+          <t>KD Media Group brought Emirates Islamic Bank to life across key retail destinations and premium malls in Dubai where strategy meets visibility and every square foot counts.
+#KDMediaGroup #EmiratesIslamicBank #RetailActivation #BrandActivation #Dubai</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
- ETE ID EPHCOP07809C8DTA
-The amount is debited but maersk kanoo didn&amp;#39;t received it. We dont have any revert from the bank where the payment is .Resolve it</t>
+          <t>KD Media Group brought Emirates Islamic Bank to life across key retail destinations and premium malls in Dubai where strategy meets visibility and every square foot counts.
+&lt;a href="/search?f=tweets&amp;amp;q=%23KDMediaGroup"&gt;#KDMediaGroup&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RetailActivation"&gt;#RetailActivation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BrandActivation"&gt;#BrandActivation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -955,27 +931,27 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:15 PM UTC</t>
+          <t>Mar 26, 2026 · 11:36 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-03-25T13:15:00Z</t>
+          <t>2026-03-26T11:36:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23KDMediaGroup', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://x.com/search?f=tweets&amp;q=%23RetailActivation', 'https://x.com/search?f=tweets&amp;q=%23BrandActivation', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -984,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -993,12 +969,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2036783540419903727</t>
+          <t>2037112769967731076</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036783540419903727</t>
+          <t>https://x.com/emiratesislamic/status/2037112769967731076</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1024,46 +1000,42 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['dhara_katariya']</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:33 PM UTC</t>
+          <t>Mar 26, 2026 · 10:21 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-03-25T12:33:00Z</t>
+          <t>2026-03-26T10:21:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1074,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1083,12 +1055,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2036783538087850447</t>
+          <t>2037112693383967013</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036783538087850447</t>
+          <t>https://x.com/emiratesislamic/status/2037112693383967013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1114,46 +1086,42 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
+          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.</t>
+          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['dhara_katariya']</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:33 PM UTC</t>
+          <t>Mar 26, 2026 · 10:21 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-03-25T12:33:00Z</t>
+          <t>2026-03-26T10:21:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1162,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>140</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1171,43 +1139,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2036732548290891833</t>
+          <t>2037102014832730391</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/AirIndiaX/status/2036732548290891833</t>
+          <t>https://x.com/emiratesislamic/status/2037102014832730391</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/AirIndiaX</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AirIndiaX</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1937212217578983424/vF-DUPT9_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Since the booking is done through Air India, we request you to please reach out to them for any assistance.</t>
+          <t>Hello. Thanks for getting in touch. To ensure your privacy, please note that we will connect with you through the direct message. We're happy to assist you</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Since the booking is done through Air India, we request you to please reach out to them for any assistance.</t>
+          <t>Hello. Thanks for getting in touch. To ensure your privacy, please note that we will connect with you through the direct message. We&amp;#39;re happy to assist you</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1216,7 +1184,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>['naanrdk', 'emiratesislamic', 'airindia']</t>
+          <t>['naanrdk']</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1226,18 +1194,18 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 9:10 AM UTC</t>
+          <t>Mar 26, 2026 · 9:39 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-03-25T09:10:00Z</t>
+          <t>2026-03-26T09:39:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1246,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -1255,79 +1223,81 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2036783540419903727</t>
+          <t>2037094634342744234</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036783540419903727</t>
+          <t>https://x.com/abuzubayr1987/status/2037094634342744234</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>abuzubayr1987</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Safwan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud</t>
+          <t>I was expecting a call back from the account manager of @emiratesislamic , got no calls or messages.
+Amazing, how without a notice an unfair 100% deduction is done leaving my family in lurch. I have been a customer since 2016!!!
+@JamalIslamic</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+          <t>I was expecting a call back from the account manager of &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; , got no calls or messages.
+Amazing, how without a notice an unfair 100% deduction is done leaving my family in lurch. I have been a customer since 2016!!!
+&lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['centralbankuae', 'SanadakUAE']</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:33 PM UTC</t>
+          <t>Mar 26, 2026 · 9:09 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-03-25T12:33:00Z</t>
+          <t>2026-03-26T09:09:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/JamalIslamic']</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1336,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1315,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2036783538087850447</t>
+          <t>2037079016033681601</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036783538087850447</t>
+          <t>https://x.com/emiratesislamic/status/2037079016033681601</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1376,16 +1346,20 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
+          <t>Small choices can make a big difference.
+Staying aware of your spending helps you stay in control — today and tomorrow.
+#FinancialWellbeing #Finwell #Spending  #EmiratesIslamic
+To know more, Visit:
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.</t>
+          <t>Small choices can make a big difference.
+Staying aware of your spending helps you stay in control — today and tomorrow.
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Spending"&gt;#Spending&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+To know more, Visit:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1395,36 +1369,36 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:33 PM UTC</t>
+          <t>Mar 26, 2026 · 8:07 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-03-25T12:33:00Z</t>
+          <t>2026-03-26T08:07:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23Spending', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -1433,47 +1407,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2036794106270413038</t>
+          <t>2037072193339691240</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/dhara_katariya/status/2036794106270413038</t>
+          <t>https://x.com/emiratesislamic/status/2037072193339691240</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/dhara_katariya</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>dhara_katariya</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhara Katariya</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1205157338639978497/HK2x6jCp_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>@emiratesislamic A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
- ETE ID EPHCOP07809C8DTA
-The amount is debited but maersk kanoo didn't received it. We dont have any revert from the bank where the payment is .Resolve it</t>
+          <t>القرارات الصغيرة تصنع فرقاً كبيراً.
+الانتباه لإنفاقك يساعدك على الحفاظ على التوازن، اليوم وعلى المدى الطويل
+لمعرفة المزيد:
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
- ETE ID EPHCOP07809C8DTA
-The amount is debited but maersk kanoo didn&amp;#39;t received it. We dont have any revert from the bank where the payment is .Resolve it</t>
+          <t>القرارات الصغيرة تصنع فرقاً كبيراً.
+الانتباه لإنفاقك يساعدك على الحفاظ على التوازن، اليوم وعلى المدى الطويل
+لمعرفة المزيد:
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1483,27 +1459,27 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:15 PM UTC</t>
+          <t>Mar 26, 2026 · 7:40 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-03-25T13:15:00Z</t>
+          <t>2026-03-26T07:40:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1512,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -1521,12 +1497,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2036783540419903727</t>
+          <t>2037046896078856635</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036783540419903727</t>
+          <t>https://x.com/emiratesislamic/status/2037046896078856635</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1552,18 +1528,20 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_022026"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1573,23 +1551,23 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:33 PM UTC</t>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-03-25T12:33:00Z</t>
+          <t>2026-03-26T06:00:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_022026']</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1602,6 +1580,1590 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2037046896061993278</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046896061993278</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;Cs apply
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;amp;Cs apply
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_02202"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_02202']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2037046893448958277</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046893448958277</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي بقيمة 750,000 درهم أو أكثر.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي بقيمة 750,000 درهم أو أكثر.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2037046893415395737</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046893415395737</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance of AED 750,000 or more.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance of AED 750,000 or more.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate.</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2037148064096415790</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037148064096415790</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Stay safe and bank easily with EI + and businessONLINE.
+#EmiratesIslamic</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Stay safe and bank easily with EI + and businessONLINE.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 12:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-03-26T12:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2037148052255875186</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037148052255875186</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ابقّ آمناً وأنجز معاملاتك المصرفية بسهولة مع تطبيق + EI ومنصة businessONLINE.
+#الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ابقّ آمناً وأنجز معاملاتك المصرفية بسهولة مع تطبيق + EI ومنصة businessONLINE.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 12:41 PM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-03-26T12:41:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2037144761212023024</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037144761212023024</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 12:28 PM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-03-26T12:28:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2037144700109337063</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037144700109337063</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better.. We appreciate your patience as we work to assist you effectively.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better.. We appreciate your patience as we work to assist you effectively.</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 12:28 PM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-03-26T12:28:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2037112769967731076</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037112769967731076</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['dhara_katariya']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 10:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-03-26T10:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2037112693383967013</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037112693383967013</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>['dhara_katariya']</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 10:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-03-26T10:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2037102014832730391</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037102014832730391</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Hello. Thanks for getting in touch. To ensure your privacy, please note that we will connect with you through the direct message. We're happy to assist you</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Hello. Thanks for getting in touch. To ensure your privacy, please note that we will connect with you through the direct message. We&amp;#39;re happy to assist you</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['naanrdk']</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 9:39 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-03-26T09:39:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2037079016033681601</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037079016033681601</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Small choices can make a big difference.
+Staying aware of your spending helps you stay in control — today and tomorrow.
+#FinancialWellbeing #Finwell #Spending  #EmiratesIslamic
+To know more, Visit:
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Small choices can make a big difference.
+Staying aware of your spending helps you stay in control — today and tomorrow.
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Spending"&gt;#Spending&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+To know more, Visit:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 8:07 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-03-26T08:07:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23Spending', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2037072193339691240</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037072193339691240</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>القرارات الصغيرة تصنع فرقاً كبيراً.
+الانتباه لإنفاقك يساعدك على الحفاظ على التوازن، اليوم وعلى المدى الطويل
+لمعرفة المزيد:
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>القرارات الصغيرة تصنع فرقاً كبيراً.
+الانتباه لإنفاقك يساعدك على الحفاظ على التوازن، اليوم وعلى المدى الطويل
+لمعرفة المزيد:
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 7:40 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-03-26T07:40:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2037046896078856635</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046896078856635</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_022026"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_022026']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2037046896061993278</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046896061993278</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;Cs apply
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;amp;Cs apply
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_02202"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_02202']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2037046893448958277</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046893448958277</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي بقيمة 750,000 درهم أو أكثر.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي بقيمة 750,000 درهم أو أكثر.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2037046893415395737</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046893415395737</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance of AED 750,000 or more.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance of AED 750,000 or more.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate.</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2037046896078856635</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046896078856635</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_022026"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_022026']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2037046896061993278</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037046896061993278</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;Cs apply
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;amp;Cs apply
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_02202"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_02202']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>72</v>
       </c>
     </row>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -589,7 +589,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -765,7 +765,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -849,7 +849,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -931,7 +931,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1369,7 +1369,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1398,7 +1398,7 @@
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -1459,7 +1459,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -1551,7 +1551,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1645,7 +1645,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -1735,7 +1735,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -1901,7 +1901,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
@@ -1987,7 +1987,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2016,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -2503,7 +2503,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2532,7 +2532,7 @@
         <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
@@ -2593,7 +2593,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
@@ -2685,7 +2685,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
@@ -2779,7 +2779,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28">
@@ -2869,7 +2869,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29">
@@ -2953,7 +2953,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30">
@@ -3041,7 +3041,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31">
@@ -3135,7 +3135,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,45 +541,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2037484085459750931</t>
+          <t>2037499728318116157</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
+          <t>https://x.com/SanadakUAE/status/2037499728318116157</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/SanadakUAE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>SanadakUAE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Sanadak</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2012879499768049664/EHCzbImW_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website sanadak.gov.ae/en/.  
+Best regards,
+Sanadak Team</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website &lt;a href="https://www.sanadak.gov.ae/en/"&gt;sanadak.gov.ae/en/&lt;/a&gt;.  
+Best regards,
+Sanadak Team</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -588,26 +594,30 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['abuzubayr1987']</t>
+          <t>['abuzubayr1987', 'emiratesislamic', 'JamalIslamic']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Mar 27, 2026 · 10:57 AM UTC</t>
+          <t>Mar 27, 2026 · 11:59 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-03-27T10:57:00Z</t>
+          <t>2026-03-27T11:59:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://www.sanadak.gov.ae/en/']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -618,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -627,36 +637,300 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2037462241591615667</t>
+          <t>2037485522399236349</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>abuzubayr1987</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Safwan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>All I got was a feedback form!
+No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
+@SanadakUAE @JamalIslamic</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>All I got was a feedback form!
+No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
+&lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt; &lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 11:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-03-27T11:02:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/SanadakUAE', 'https://x.com/JamalIslamic']</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2037484085459750931</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-03-27T10:57:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2037480161797722518</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Safwan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 10:41 AM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-03-27T10:41:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2037462241591615667</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -664,7 +938,7 @@
 Use EI + Mobile &amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -672,217 +946,389 @@
 Use EI + Mobile &amp;amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-03-27T09:30:00Z</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="V3" t="n">
-        <v>88</v>
+      <c r="V6" t="n">
+        <v>90</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2037484085459750931</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-03-27T10:57:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2037462241591615667</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>سلامتكم أولويتنا.
+نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
+Your safety comes first.
+Use EI + Mobile &amp; Online Banking and businessONLINE with ease and security.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>سلامتكم أولويتنا.
+نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
+Your safety comes first.
+Use EI + Mobile &amp;amp; Online Banking and businessONLINE with ease and security.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 9:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-03-27T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="V8" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>2037485522399236349</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>abuzubayr1987</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Safwan</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>All I got was a feedback form!
 No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
 @SanadakUAE @JamalIslamic</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>All I got was a feedback form!
 No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
 &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt; &lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:02 AM UTC</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-03-27T11:02:00Z</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>['https://x.com/SanadakUAE', 'https://x.com/JamalIslamic']</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>12</v>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>2037480161797722518</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>abuzubayr1987</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Safwan</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Hello
 I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Hello
 I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:41 AM UTC</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2026-03-27T10:41:00Z</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11</v>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -691,7 +691,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -781,7 +781,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -867,7 +867,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -953,7 +953,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -978,7 +978,7 @@
         <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1125,7 +1125,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1150,7 +1150,7 @@
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,725 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>permalink</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>userUrl</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>isRetweet</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>retweetedBy</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>replyingTo</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>relativeTime</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>displayTime</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>createdAt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>images</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>links</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>retweets</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quotes</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2038584368378331541</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404/status/2038584368378331541</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Osama2404</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>أتوجه بهذا المنشور إلى مصرف الإمارات العربية المتحدة المركزي @centralbankuae  بخصوص موضوع قائم مع مصرف الإمارات الإسلامي @emiratesislamic  ،  آملًا المراجعة والتوجيه.
+تقدّمت بشكوى رسمية نتيجة تجميد حساباتي البنكية بالكامل رغم وجود حكم قضائي واضح، وتم إصدار تفسير رسمي لنطق الحكم من المحكمة لتأكيد مضمونه.
+🔹 حيث أن:
+الحكم القضائي لا يتضمن أي نص على تجميد الحسابات أو حجز الأموال
+ومع ذلك، تم تطبيق تجميد كامل على الحسابات
+⚠️ كما أن هناك نقطة تستدعي التوضيح:
+يتم منع العميل من استخدام أمواله
+بينما يقوم البنك في المقابل بالخصم منها لسداد التزاماته
+وعند الاستفسار، يتم توضيح أن ذلك "حق للبنك"
+وهذا يطرح تساؤلًا حول:
+مدى اتساق هذه الإجراءات
+ومدى توافقها مع تفسير الحكم القضائي
+وآليات حماية حقوق العميل في مثل هذه الحالات
+وقد ترتب على ذلك تأثيرات:
+نفسية
+اجتماعية
+مالية
+بسبب تعذر الوصول إلى الموارد المالية.
+لذا آمل من مصرف الإمارات العربية المتحدة المركزي:
+✔️ مراجعة هذه الحالة
+✔️ التحقق من مدى توافق الإجراءات مع الأنظمة
+✔️ التوجيه بما يضمن وضوح التطبيق وحماية حقوق جميع الأطراف
+مع خالص التقدير لجهودكم في تعزيز الشفافية والعدالة في القطاع المصرفي.
+#مصرف_الإمارات_المركزي #حماية_المستهلك #القطاع_المصرفي #الإمارات #emiratesislamic #centralbankuae</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>أتوجه بهذا المنشور إلى مصرف الإمارات العربية المتحدة المركزي &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt;  بخصوص موضوع قائم مع مصرف الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  ،  آملًا المراجعة والتوجيه.
+تقدّمت بشكوى رسمية نتيجة تجميد حساباتي البنكية بالكامل رغم وجود حكم قضائي واضح، وتم إصدار تفسير رسمي لنطق الحكم من المحكمة لتأكيد مضمونه.
+🔹 حيث أن:
+الحكم القضائي لا يتضمن أي نص على تجميد الحسابات أو حجز الأموال
+ومع ذلك، تم تطبيق تجميد كامل على الحسابات
+⚠️ كما أن هناك نقطة تستدعي التوضيح:
+يتم منع العميل من استخدام أمواله
+بينما يقوم البنك في المقابل بالخصم منها لسداد التزاماته
+وعند الاستفسار، يتم توضيح أن ذلك &amp;#34;حق للبنك&amp;#34;
+وهذا يطرح تساؤلًا حول:
+مدى اتساق هذه الإجراءات
+ومدى توافقها مع تفسير الحكم القضائي
+وآليات حماية حقوق العميل في مثل هذه الحالات
+وقد ترتب على ذلك تأثيرات:
+نفسية
+اجتماعية
+مالية
+بسبب تعذر الوصول إلى الموارد المالية.
+لذا آمل من مصرف الإمارات العربية المتحدة المركزي:
+✔️ مراجعة هذه الحالة
+✔️ التحقق من مدى توافق الإجراءات مع الأنظمة
+✔️ التوجيه بما يضمن وضوح التطبيق وحماية حقوق جميع الأطراف
+مع خالص التقدير لجهودكم في تعزيز الشفافية والعدالة في القطاع المصرفي.
+&lt;a href="/search?f=tweets&amp;amp;q=%23مصرف_الإمارات_المركزي"&gt;#مصرف_الإمارات_المركزي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حماية_المستهلك"&gt;#حماية_المستهلك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23القطاع_المصرفي"&gt;#القطاع_المصرفي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23centralbankuae"&gt;#centralbankuae&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 11:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-03-30T11:49:00Z</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/centralbankuae', 'https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23مصرف_الإمارات_المركزي', 'https://x.com/search?f=tweets&amp;q=%23حماية_المستهلك', 'https://x.com/search?f=tweets&amp;q=%23القطاع_المصرفي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23centralbankuae']</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2038583610916397370</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404/status/2038583610916397370</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Osama2404</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>أكتب هذا المنشور بعد استنفاد جميع محاولات التواصل دون أي نتيجة تُذكر مع مصرف الإمارات الإسلامي @emiratesislamic  وفي حالة من الاستغراب والاستياء مما أواجهه.
+تقدّمت بشكوى رسمية بخصوص تجميد حساباتي البنكية بالكامل، رغم وجود حكم قضائي واضح، بل وقد قامت المحكمة مشكورة بإصدار تفسير صريح لنطق الحكم لإزالة أي لبس.
+ومع ذلك، لا يزال البنك مستمرًا في اتخاذ إجراءات لا تتماشى مع منطوق الحكم ولا تفسيره.
+🔹 للتوضيح:
+الحكم القضائي لا يتضمن إطلاقًا أي بند لتجميد الحسابات أو حجز الأموال
+ورغم ذلك تم:تجميد حساباتي بالكامل
+حجز أموالي دون سند قضائي
+الاستمرار في ذلك رغم وضوح الحكم
+⚠️ التناقض الأبرز:
+يتم منعي من التصرف بأموالي
+وفي نفس الوقت، يقوم البنك بالخصم التلقائي لسداد القروض والبطاقات
+وعند الاستفسار، يكون الرد: "هذا حق البنك"
+وهنا يبرز التساؤل المشروع:
+❗ إذا كانت الأموال خاضعة للتجميد، كيف يتم الخصم منها؟
+❗ وإذا لم تكن كذلك، لماذا يُمنع صاحب الحساب من استخدامها؟
+هذا الوضع يعكس — بكل أسف — خللًا في فهم أو تطبيق الحكم القضائي أو عدم اتساق في الإجراءات.
+ما أتعرض له لم يعد مجرد إجراء بنكي، بل أثر بشكل مباشر على:
+وضعي النفسي
+استقراري الاجتماعي
+التزاماتي المالية والمعيشية
+كما أن غياب جهة واضحة تتحمل المسؤولية، وعدم وجود معالجة جدية، يزيد من تعقيد الوضع.
+أطالب الإدارة العليا في مصرف الإمارات الإسلامي بـ:
+✔️ الالتزام بالحكم القضائي وتفسيره
+✔️ وقف أي إجراءات غير متسقة معه
+✔️ رفع التجميد غير المبرر
+✔️ توضيح رسمي للحالة ومعالجتها بشكل عاجل
+آمل أن يتم التعامل مع الموضوع بالجدية اللازمة، حيث أن الوضع لم يعد يحتمل المزيد من التأخير.
+#شكوى #تصعيد #مصرف_الإمارات_الإسلامي #العدالة #حقوق #الإمارات #emiratesislamic</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>أكتب هذا المنشور بعد استنفاد جميع محاولات التواصل دون أي نتيجة تُذكر مع مصرف الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  وفي حالة من الاستغراب والاستياء مما أواجهه.
+تقدّمت بشكوى رسمية بخصوص تجميد حساباتي البنكية بالكامل، رغم وجود حكم قضائي واضح، بل وقد قامت المحكمة مشكورة بإصدار تفسير صريح لنطق الحكم لإزالة أي لبس.
+ومع ذلك، لا يزال البنك مستمرًا في اتخاذ إجراءات لا تتماشى مع منطوق الحكم ولا تفسيره.
+🔹 للتوضيح:
+الحكم القضائي لا يتضمن إطلاقًا أي بند لتجميد الحسابات أو حجز الأموال
+ورغم ذلك تم:تجميد حساباتي بالكامل
+حجز أموالي دون سند قضائي
+الاستمرار في ذلك رغم وضوح الحكم
+⚠️ التناقض الأبرز:
+يتم منعي من التصرف بأموالي
+وفي نفس الوقت، يقوم البنك بالخصم التلقائي لسداد القروض والبطاقات
+وعند الاستفسار، يكون الرد: &amp;#34;هذا حق البنك&amp;#34;
+وهنا يبرز التساؤل المشروع:
+❗ إذا كانت الأموال خاضعة للتجميد، كيف يتم الخصم منها؟
+❗ وإذا لم تكن كذلك، لماذا يُمنع صاحب الحساب من استخدامها؟
+هذا الوضع يعكس — بكل أسف — خللًا في فهم أو تطبيق الحكم القضائي أو عدم اتساق في الإجراءات.
+ما أتعرض له لم يعد مجرد إجراء بنكي، بل أثر بشكل مباشر على:
+وضعي النفسي
+استقراري الاجتماعي
+التزاماتي المالية والمعيشية
+كما أن غياب جهة واضحة تتحمل المسؤولية، وعدم وجود معالجة جدية، يزيد من تعقيد الوضع.
+أطالب الإدارة العليا في مصرف الإمارات الإسلامي بـ:
+✔️ الالتزام بالحكم القضائي وتفسيره
+✔️ وقف أي إجراءات غير متسقة معه
+✔️ رفع التجميد غير المبرر
+✔️ توضيح رسمي للحالة ومعالجتها بشكل عاجل
+آمل أن يتم التعامل مع الموضوع بالجدية اللازمة، حيث أن الوضع لم يعد يحتمل المزيد من التأخير.
+&lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تصعيد"&gt;#تصعيد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مصرف_الإمارات_الإسلامي"&gt;#مصرف_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23العدالة"&gt;#العدالة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق"&gt;#حقوق&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 11:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-03-30T11:46:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23تصعيد', 'https://x.com/search?f=tweets&amp;q=%23مصرف_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23العدالة', 'https://x.com/search?f=tweets&amp;q=%23حقوق', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2038575380282437864</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038575380282437864</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 11:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-03-30T11:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2038531210058866754</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/ZiadaKhalid/status/2038531210058866754</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/ZiadaKhalid</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ZiadaKhalid</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mohamed Khalid Ziada</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1275391016313520139/YT7jm928_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 8:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-03-30T08:18:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2038575380282437864</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038575380282437864</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 11:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-03-30T11:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2038531210058866754</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/ZiadaKhalid/status/2038531210058866754</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/ZiadaKhalid</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ZiadaKhalid</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mohamed Khalid Ziada</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1275391016313520139/YT7jm928_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 8:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-03-30T08:18:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,36 +541,404 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2038584368378331541</t>
+          <t>2038702486702461222</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404/status/2038584368378331541</t>
+          <t>https://x.com/MNadaver/status/2038702486702461222</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404</t>
+          <t>https://x.com/MNadaver</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Osama2404</t>
+          <t>MNadaver</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Osama</t>
+          <t>Achi Harshath | ಅಚ್ಚಿ ಹರ್ಷತ್</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1254006517419966465/aHDAzOS5_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>@emiratesislamic , your cards services still seem to have impact.
+Bills not getting generated 
+Not been able to switch between cash back and travel 
+Rewards option not working
+Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; , your cards services still seem to have impact.
+Bills not getting generated 
+Not been able to switch between cash back and travel 
+Rewards option not working
+Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 7:38 PM UTC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2038665761175076929</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2038665761175076929</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Safwan</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 5:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-03-30T17:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2038645533879701568</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404/status/2038645533879701568</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Osama2404</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>⸻
+أشكر تفاعلكم وتوجيهكم،
+أود التوضيح أنني بدأت بشكوى لدى مصرف الإمارات الإسلامي، وتم إغلاقها دون حل، ثم تقدّمت بشكوى عبر منصة سندك برقم:
+CAS-271454-S3K5B1
+حالياً، وبسبب طول الإجراءات واستمرار تجميد الحساب، أصبحت بلا مصدر دخل فعلي، وغير قادر على استخدام راتبي أو تغطية التزاماتي الأساسية (إيجار، كهرباء، ماء)، ووصلت لمرحلة الاستدانة لتأمين احتياجات أسرتي.
+🙏 أرجو منكم التكرم بتسريع معالجة الشكوى، لما لذلك من أثر إنساني ومالي بالغ.
+شاكر دعمكم</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>⸻
+أشكر تفاعلكم وتوجيهكم،
+أود التوضيح أنني بدأت بشكوى لدى مصرف الإمارات الإسلامي، وتم إغلاقها دون حل، ثم تقدّمت بشكوى عبر منصة سندك برقم:
+CAS-271454-S3K5B1
+حالياً، وبسبب طول الإجراءات واستمرار تجميد الحساب، أصبحت بلا مصدر دخل فعلي، وغير قادر على استخدام راتبي أو تغطية التزاماتي الأساسية (إيجار، كهرباء، ماء)، ووصلت لمرحلة الاستدانة لتأمين احتياجات أسرتي.
+🙏 أرجو منكم التكرم بتسريع معالجة الشكوى، لما لذلك من أثر إنساني ومالي بالغ.
+شاكر دعمكم</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['centralbankuae', 'emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 3:52 PM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-03-30T15:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2038639887751286944</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae/status/2038639887751286944</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>centralbankuae</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>عزيزي المتعامل،
+نشكر تواصلك مع مصرف الإمارات المركزي، إن استفساراتك وملاحظتك تهمنا.
+للمعلومات أو الشكاوى، يرجى التواصل مع وحدة "سندك" لتسوية المنازعات المصرفية والتأمينية عبر تحميل تطبيق الهاتف المحمول، أو زيارة الموقع الإلكتروني: sanadak.gov.ae
+ مع أطيب التحيات،
+مصرف الإمارات المركزي</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>عزيزي المتعامل،
+نشكر تواصلك مع مصرف الإمارات المركزي، إن استفساراتك وملاحظتك تهمنا.
+للمعلومات أو الشكاوى، يرجى التواصل مع وحدة &amp;#34;سندك&amp;#34; لتسوية المنازعات المصرفية والتأمينية عبر تحميل تطبيق الهاتف المحمول، أو زيارة الموقع الإلكتروني: &lt;a href="https://www.sanadak.gov.ae"&gt;sanadak.gov.ae&lt;/a&gt;
+ مع أطيب التحيات،
+مصرف الإمارات المركزي</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['Osama2404', 'emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 3:29 PM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-03-30T15:29:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://www.sanadak.gov.ae']</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2038584368378331541</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404/status/2038584368378331541</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/Osama2404</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Osama2404</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>أتوجه بهذا المنشور إلى مصرف الإمارات العربية المتحدة المركزي @centralbankuae  بخصوص موضوع قائم مع مصرف الإمارات الإسلامي @emiratesislamic  ،  آملًا المراجعة والتوجيه.
 تقدّمت بشكوى رسمية نتيجة تجميد حساباتي البنكية بالكامل رغم وجود حكم قضائي واضح، وتم إصدار تفسير رسمي لنطق الحكم من المحكمة لتأكيد مضمونه.
@@ -598,7 +966,7 @@
 #مصرف_الإمارات_المركزي #حماية_المستهلك #القطاع_المصرفي #الإمارات #emiratesislamic #centralbankuae</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>أتوجه بهذا المنشور إلى مصرف الإمارات العربية المتحدة المركزي &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt;  بخصوص موضوع قائم مع مصرف الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  ،  آملًا المراجعة والتوجيه.
 تقدّمت بشكوى رسمية نتيجة تجميد حساباتي البنكية بالكامل رغم وجود حكم قضائي واضح، وتم إصدار تفسير رسمي لنطق الحكم من المحكمة لتأكيد مضمونه.
@@ -626,81 +994,81 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23مصرف_الإمارات_المركزي"&gt;#مصرف_الإمارات_المركزي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حماية_المستهلك"&gt;#حماية_المستهلك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23القطاع_المصرفي"&gt;#القطاع_المصرفي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23centralbankuae"&gt;#centralbankuae&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Mar 30, 2026 · 11:49 AM UTC</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-03-30T11:49:00Z</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>['https://x.com/centralbankuae', 'https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23مصرف_الإمارات_المركزي', 'https://x.com/search?f=tweets&amp;q=%23حماية_المستهلك', 'https://x.com/search?f=tweets&amp;q=%23القطاع_المصرفي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23centralbankuae']</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="V2" t="n">
-        <v>9</v>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>84</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>2038583610916397370</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://x.com/Osama2404/status/2038583610916397370</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://x.com/Osama2404</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Osama2404</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Osama</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>أكتب هذا المنشور بعد استنفاد جميع محاولات التواصل دون أي نتيجة تُذكر مع مصرف الإمارات الإسلامي @emiratesislamic  وفي حالة من الاستغراب والاستياء مما أواجهه.
 تقدّمت بشكوى رسمية بخصوص تجميد حساباتي البنكية بالكامل، رغم وجود حكم قضائي واضح، بل وقد قامت المحكمة مشكورة بإصدار تفسير صريح لنطق الحكم لإزالة أي لبس.
@@ -732,7 +1100,7 @@
 #شكوى #تصعيد #مصرف_الإمارات_الإسلامي #العدالة #حقوق #الإمارات #emiratesislamic</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>أكتب هذا المنشور بعد استنفاد جميع محاولات التواصل دون أي نتيجة تُذكر مع مصرف الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  وفي حالة من الاستغراب والاستياء مما أواجهه.
 تقدّمت بشكوى رسمية بخصوص تجميد حساباتي البنكية بالكامل، رغم وجود حكم قضائي واضح، بل وقد قامت المحكمة مشكورة بإصدار تفسير صريح لنطق الحكم لإزالة أي لبس.
@@ -764,383 +1132,559 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تصعيد"&gt;#تصعيد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مصرف_الإمارات_الإسلامي"&gt;#مصرف_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23العدالة"&gt;#العدالة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق"&gt;#حقوق&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Mar 30, 2026 · 11:46 AM UTC</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2026-03-30T11:46:00Z</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23تصعيد', 'https://x.com/search?f=tweets&amp;q=%23مصرف_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23العدالة', 'https://x.com/search?f=tweets&amp;q=%23حقوق', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="V3" t="n">
-        <v>9</v>
+      <c r="V7" t="n">
+        <v>22</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>2038575380282437864</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2038575380282437864</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>['abuzubayr1987']</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>Mar 30, 2026 · 11:13 AM UTC</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2026-03-30T11:13:00Z</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4</v>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>2038531210058866754</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://x.com/ZiadaKhalid/status/2038531210058866754</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://x.com/ZiadaKhalid</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>ZiadaKhalid</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Mohamed Khalid Ziada</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1275391016313520139/YT7jm928_bigger.jpg</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
         </is>
       </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Mar 30, 2026 · 8:18 AM UTC</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-03-30T08:18:00Z</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>2038575380282437864</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2038575380282437864</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>['abuzubayr1987']</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Mar 30, 2026 · 11:13 AM UTC</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2026-03-30T11:13:00Z</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4</v>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2038702486702461222</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/MNadaver/status/2038702486702461222</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/MNadaver</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MNadaver</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Achi Harshath | ಅಚ್ಚಿ ಹರ್ಷತ್</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1254006517419966465/aHDAzOS5_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>@emiratesislamic , your cards services still seem to have impact.
+Bills not getting generated 
+Not been able to switch between cash back and travel 
+Rewards option not working
+Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; , your cards services still seem to have impact.
+Bills not getting generated 
+Not been able to switch between cash back and travel 
+Rewards option not working
+Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 7:38 PM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2038665761175076929</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2038665761175076929</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Safwan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 5:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-03-30T17:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>2038531210058866754</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://x.com/ZiadaKhalid/status/2038531210058866754</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://x.com/ZiadaKhalid</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>ZiadaKhalid</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Mohamed Khalid Ziada</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1275391016313520139/YT7jm928_bigger.jpg</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
         </is>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Mar 30, 2026 · 8:18 AM UTC</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2026-03-30T08:18:00Z</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,79 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2038702486702461222</t>
+          <t>2039159510951170144</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/MNadaver/status/2038702486702461222</t>
+          <t>https://x.com/383c9b71f3e5451/status/2039159510951170144</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/MNadaver</t>
+          <t>https://x.com/383c9b71f3e5451</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MNadaver</t>
+          <t>383c9b71f3e5451</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Achi Harshath | ಅಚ್ಚಿ ಹರ್ಷತ್</t>
+          <t>Mohamed Wakeb</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1254006517419966465/aHDAzOS5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>@emiratesislamic , your cards services still seem to have impact.
-Bills not getting generated 
-Not been able to switch between cash back and travel 
-Rewards option not working
-Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; , your cards services still seem to have impact.
-Bills not getting generated 
-Not been able to switch between cash back and travel 
-Rewards option not working
-Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 7:38 PM UTC</t>
+          <t>Apr 1, 2026 · 1:54 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:00Z</t>
+          <t>2026-04-01T01:54:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -624,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -633,54 +625,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2038665761175076929</t>
+          <t>2039029089705591194</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987/status/2038665761175076929</t>
+          <t>https://x.com/emiratesislamic/status/2039029089705591194</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>abuzubayr1987</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Safwan</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- &lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>10h</t>
@@ -688,16 +678,20 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 5:12 PM UTC</t>
+          <t>Mar 31, 2026 · 5:16 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-03-30T17:12:00Z</t>
+          <t>2026-03-31T17:16:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -705,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -717,94 +711,84 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2038645533879701568</t>
+          <t>2039029079148536148</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404/status/2038645533879701568</t>
+          <t>https://x.com/emiratesislamic/status/2039029079148536148</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Osama2404</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Osama</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>⸻
-أشكر تفاعلكم وتوجيهكم،
-أود التوضيح أنني بدأت بشكوى لدى مصرف الإمارات الإسلامي، وتم إغلاقها دون حل، ثم تقدّمت بشكوى عبر منصة سندك برقم:
-CAS-271454-S3K5B1
-حالياً، وبسبب طول الإجراءات واستمرار تجميد الحساب، أصبحت بلا مصدر دخل فعلي، وغير قادر على استخدام راتبي أو تغطية التزاماتي الأساسية (إيجار، كهرباء، ماء)، ووصلت لمرحلة الاستدانة لتأمين احتياجات أسرتي.
-🙏 أرجو منكم التكرم بتسريع معالجة الشكوى، لما لذلك من أثر إنساني ومالي بالغ.
-شاكر دعمكم</t>
+          <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
+اقرأ المقال هنا:  emiratesislamic.ae/ar/news-a…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>⸻
-أشكر تفاعلكم وتوجيهكم،
-أود التوضيح أنني بدأت بشكوى لدى مصرف الإمارات الإسلامي، وتم إغلاقها دون حل، ثم تقدّمت بشكوى عبر منصة سندك برقم:
-CAS-271454-S3K5B1
-حالياً، وبسبب طول الإجراءات واستمرار تجميد الحساب، أصبحت بلا مصدر دخل فعلي، وغير قادر على استخدام راتبي أو تغطية التزاماتي الأساسية (إيجار، كهرباء، ماء)، ووصلت لمرحلة الاستدانة لتأمين احتياجات أسرتي.
-🙏 أرجو منكم التكرم بتسريع معالجة الشكوى، لما لذلك من أثر إنساني ومالي بالغ.
-شاكر دعمكم</t>
+          <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
+اقرأ المقال هنا:  &lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['centralbankuae', 'emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 3:52 PM UTC</t>
+          <t>Mar 31, 2026 · 5:16 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-03-30T15:52:00Z</t>
+          <t>2026-03-31T17:16:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -813,94 +797,88 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2038639887751286944</t>
+          <t>2039017522863669449</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae/status/2038639887751286944</t>
+          <t>https://x.com/nasnews_e/status/2039017522863669449</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae</t>
+          <t>https://x.com/nasnews_e</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>centralbankuae</t>
+          <t>nasnews_e</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Central Bank of the UAE</t>
+          <t>Nas News Emirates</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034790571630575616/O8W30no3_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>عزيزي المتعامل،
-نشكر تواصلك مع مصرف الإمارات المركزي، إن استفساراتك وملاحظتك تهمنا.
-للمعلومات أو الشكاوى، يرجى التواصل مع وحدة "سندك" لتسوية المنازعات المصرفية والتأمينية عبر تحميل تطبيق الهاتف المحمول، أو زيارة الموقع الإلكتروني: sanadak.gov.ae
- مع أطيب التحيات،
-مصرف الإمارات المركزي</t>
+          <t>#Emirates #NBD has successfully closed a US$2.25 billion long-term financing transaction, reinforcing its strong credit profile and market confidence.
+The deal includes a US$1.75 billion oversubscribed sustainability-linked loan and a US$500 million Murabaha facility arranged through Emirates Islamic.
+This milestone strengthens liquidity, enhances funding diversification, and supports long-term growth.
+#UAE | #nas_news_emirates</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>عزيزي المتعامل،
-نشكر تواصلك مع مصرف الإمارات المركزي، إن استفساراتك وملاحظتك تهمنا.
-للمعلومات أو الشكاوى، يرجى التواصل مع وحدة &amp;#34;سندك&amp;#34; لتسوية المنازعات المصرفية والتأمينية عبر تحميل تطبيق الهاتف المحمول، أو زيارة الموقع الإلكتروني: &lt;a href="https://www.sanadak.gov.ae"&gt;sanadak.gov.ae&lt;/a&gt;
- مع أطيب التحيات،
-مصرف الإمارات المركزي</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates"&gt;#Emirates&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBD"&gt;#NBD&lt;/a&gt; has successfully closed a US$2.25 billion long-term financing transaction, reinforcing its strong credit profile and market confidence.
+The deal includes a US$1.75 billion oversubscribed sustainability-linked loan and a US$500 million Murabaha facility arranged through Emirates Islamic.
+This milestone strengthens liquidity, enhances funding diversification, and supports long-term growth.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; | &lt;a href="/search?f=tweets&amp;amp;q=%23nas_news_emirates"&gt;#nas_news_emirates&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['Osama2404', 'emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 3:29 PM UTC</t>
+          <t>Mar 31, 2026 · 4:30 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-03-30T15:29:00Z</t>
+          <t>2026-03-31T16:30:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.sanadak.gov.ae']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Emirates', 'https://x.com/search?f=tweets&amp;q=%23NBD', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23nas_news_emirates']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -909,89 +887,51 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2038584368378331541</t>
+          <t>2038995248009842862</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404/status/2038584368378331541</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038995248009842862</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Osama2404</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Osama</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>أتوجه بهذا المنشور إلى مصرف الإمارات العربية المتحدة المركزي @centralbankuae  بخصوص موضوع قائم مع مصرف الإمارات الإسلامي @emiratesislamic  ،  آملًا المراجعة والتوجيه.
-تقدّمت بشكوى رسمية نتيجة تجميد حساباتي البنكية بالكامل رغم وجود حكم قضائي واضح، وتم إصدار تفسير رسمي لنطق الحكم من المحكمة لتأكيد مضمونه.
-🔹 حيث أن:
-الحكم القضائي لا يتضمن أي نص على تجميد الحسابات أو حجز الأموال
-ومع ذلك، تم تطبيق تجميد كامل على الحسابات
-⚠️ كما أن هناك نقطة تستدعي التوضيح:
-يتم منع العميل من استخدام أمواله
-بينما يقوم البنك في المقابل بالخصم منها لسداد التزاماته
-وعند الاستفسار، يتم توضيح أن ذلك "حق للبنك"
-وهذا يطرح تساؤلًا حول:
-مدى اتساق هذه الإجراءات
-ومدى توافقها مع تفسير الحكم القضائي
-وآليات حماية حقوق العميل في مثل هذه الحالات
-وقد ترتب على ذلك تأثيرات:
-نفسية
-اجتماعية
-مالية
-بسبب تعذر الوصول إلى الموارد المالية.
-لذا آمل من مصرف الإمارات العربية المتحدة المركزي:
-✔️ مراجعة هذه الحالة
-✔️ التحقق من مدى توافق الإجراءات مع الأنظمة
-✔️ التوجيه بما يضمن وضوح التطبيق وحماية حقوق جميع الأطراف
-مع خالص التقدير لجهودكم في تعزيز الشفافية والعدالة في القطاع المصرفي.
-#مصرف_الإمارات_المركزي #حماية_المستهلك #القطاع_المصرفي #الإمارات #emiratesislamic #centralbankuae</t>
+          <t>Emirates NBD Group has successfully closed a USD 2.25 billion long‑term financing - one of the largest syndicated borrowings in the GCC.
+The transaction includes a USD 1.75 billion sustainability‑linked syndicated loan, alongside a USD 500 million five‑year Club Commodity Murabaha facility by @emiratesislamic .
+With participation from 15 leading global financial institutions, it reflects a strong market confidence while supporting funding diversification, liquidity and long-term growth.
+Read more here: emiratesnbd.com/en/media-cen…
+#EmiratesNBD #Banking #CapitalMarkets #SustainableFinance #UAE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>أتوجه بهذا المنشور إلى مصرف الإمارات العربية المتحدة المركزي &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt;  بخصوص موضوع قائم مع مصرف الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  ،  آملًا المراجعة والتوجيه.
-تقدّمت بشكوى رسمية نتيجة تجميد حساباتي البنكية بالكامل رغم وجود حكم قضائي واضح، وتم إصدار تفسير رسمي لنطق الحكم من المحكمة لتأكيد مضمونه.
-🔹 حيث أن:
-الحكم القضائي لا يتضمن أي نص على تجميد الحسابات أو حجز الأموال
-ومع ذلك، تم تطبيق تجميد كامل على الحسابات
-⚠️ كما أن هناك نقطة تستدعي التوضيح:
-يتم منع العميل من استخدام أمواله
-بينما يقوم البنك في المقابل بالخصم منها لسداد التزاماته
-وعند الاستفسار، يتم توضيح أن ذلك &amp;#34;حق للبنك&amp;#34;
-وهذا يطرح تساؤلًا حول:
-مدى اتساق هذه الإجراءات
-ومدى توافقها مع تفسير الحكم القضائي
-وآليات حماية حقوق العميل في مثل هذه الحالات
-وقد ترتب على ذلك تأثيرات:
-نفسية
-اجتماعية
-مالية
-بسبب تعذر الوصول إلى الموارد المالية.
-لذا آمل من مصرف الإمارات العربية المتحدة المركزي:
-✔️ مراجعة هذه الحالة
-✔️ التحقق من مدى توافق الإجراءات مع الأنظمة
-✔️ التوجيه بما يضمن وضوح التطبيق وحماية حقوق جميع الأطراف
-مع خالص التقدير لجهودكم في تعزيز الشفافية والعدالة في القطاع المصرفي.
-&lt;a href="/search?f=tweets&amp;amp;q=%23مصرف_الإمارات_المركزي"&gt;#مصرف_الإمارات_المركزي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حماية_المستهلك"&gt;#حماية_المستهلك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23القطاع_المصرفي"&gt;#القطاع_المصرفي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23centralbankuae"&gt;#centralbankuae&lt;/a&gt;</t>
+          <t>Emirates NBD Group has successfully closed a USD 2.25 billion long‑term financing - one of the largest syndicated borrowings in the GCC.
+The transaction includes a USD 1.75 billion sustainability‑linked syndicated loan, alongside a USD 500 million five‑year Club Commodity Murabaha facility by &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; .
+With participation from 15 leading global financial institutions, it reflects a strong market confidence while supporting funding diversification, liquidity and long-term growth.
+Read more here: &lt;a href="https://www.emiratesnbd.com/en/media-center/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CapitalMarkets"&gt;#CapitalMarkets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SustainableFinance"&gt;#SustainableFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -1001,36 +941,36 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 11:49 AM UTC</t>
+          <t>Mar 31, 2026 · 3:02 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-03-30T11:49:00Z</t>
+          <t>2026-03-31T15:02:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://x.com/centralbankuae', 'https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23مصرف_الإمارات_المركزي', 'https://x.com/search?f=tweets&amp;q=%23حماية_المستهلك', 'https://x.com/search?f=tweets&amp;q=%23القطاع_المصرفي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23centralbankuae']</t>
+          <t>['https://x.com/emiratesislamic', 'https://www.emiratesnbd.com/en/media-center/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23CapitalMarkets', 'https://x.com/search?f=tweets&amp;q=%23SustainableFinance', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="V6" t="n">
-        <v>84</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="7">
@@ -1039,97 +979,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2038583610916397370</t>
+          <t>2038972592858534070</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404/status/2038583610916397370</t>
+          <t>https://x.com/gold_hadas/status/2038972592858534070</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/Osama2404</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Osama2404</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Osama</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1463821500763496452/FBo5GgNS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>أكتب هذا المنشور بعد استنفاد جميع محاولات التواصل دون أي نتيجة تُذكر مع مصرف الإمارات الإسلامي @emiratesislamic  وفي حالة من الاستغراب والاستياء مما أواجهه.
-تقدّمت بشكوى رسمية بخصوص تجميد حساباتي البنكية بالكامل، رغم وجود حكم قضائي واضح، بل وقد قامت المحكمة مشكورة بإصدار تفسير صريح لنطق الحكم لإزالة أي لبس.
-ومع ذلك، لا يزال البنك مستمرًا في اتخاذ إجراءات لا تتماشى مع منطوق الحكم ولا تفسيره.
-🔹 للتوضيح:
-الحكم القضائي لا يتضمن إطلاقًا أي بند لتجميد الحسابات أو حجز الأموال
-ورغم ذلك تم:تجميد حساباتي بالكامل
-حجز أموالي دون سند قضائي
-الاستمرار في ذلك رغم وضوح الحكم
-⚠️ التناقض الأبرز:
-يتم منعي من التصرف بأموالي
-وفي نفس الوقت، يقوم البنك بالخصم التلقائي لسداد القروض والبطاقات
-وعند الاستفسار، يكون الرد: "هذا حق البنك"
-وهنا يبرز التساؤل المشروع:
-❗ إذا كانت الأموال خاضعة للتجميد، كيف يتم الخصم منها؟
-❗ وإذا لم تكن كذلك، لماذا يُمنع صاحب الحساب من استخدامها؟
-هذا الوضع يعكس — بكل أسف — خللًا في فهم أو تطبيق الحكم القضائي أو عدم اتساق في الإجراءات.
-ما أتعرض له لم يعد مجرد إجراء بنكي، بل أثر بشكل مباشر على:
-وضعي النفسي
-استقراري الاجتماعي
-التزاماتي المالية والمعيشية
-كما أن غياب جهة واضحة تتحمل المسؤولية، وعدم وجود معالجة جدية، يزيد من تعقيد الوضع.
-أطالب الإدارة العليا في مصرف الإمارات الإسلامي بـ:
-✔️ الالتزام بالحكم القضائي وتفسيره
-✔️ وقف أي إجراءات غير متسقة معه
-✔️ رفع التجميد غير المبرر
-✔️ توضيح رسمي للحالة ومعالجتها بشكل عاجل
-آمل أن يتم التعامل مع الموضوع بالجدية اللازمة، حيث أن الوضع لم يعد يحتمل المزيد من التأخير.
-#شكوى #تصعيد #مصرف_الإمارات_الإسلامي #العدالة #حقوق #الإمارات #emiratesislamic</t>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility zawya.com/en/press-release/c…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>أكتب هذا المنشور بعد استنفاد جميع محاولات التواصل دون أي نتيجة تُذكر مع مصرف الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  وفي حالة من الاستغراب والاستياء مما أواجهه.
-تقدّمت بشكوى رسمية بخصوص تجميد حساباتي البنكية بالكامل، رغم وجود حكم قضائي واضح، بل وقد قامت المحكمة مشكورة بإصدار تفسير صريح لنطق الحكم لإزالة أي لبس.
-ومع ذلك، لا يزال البنك مستمرًا في اتخاذ إجراءات لا تتماشى مع منطوق الحكم ولا تفسيره.
-🔹 للتوضيح:
-الحكم القضائي لا يتضمن إطلاقًا أي بند لتجميد الحسابات أو حجز الأموال
-ورغم ذلك تم:تجميد حساباتي بالكامل
-حجز أموالي دون سند قضائي
-الاستمرار في ذلك رغم وضوح الحكم
-⚠️ التناقض الأبرز:
-يتم منعي من التصرف بأموالي
-وفي نفس الوقت، يقوم البنك بالخصم التلقائي لسداد القروض والبطاقات
-وعند الاستفسار، يكون الرد: &amp;#34;هذا حق البنك&amp;#34;
-وهنا يبرز التساؤل المشروع:
-❗ إذا كانت الأموال خاضعة للتجميد، كيف يتم الخصم منها؟
-❗ وإذا لم تكن كذلك، لماذا يُمنع صاحب الحساب من استخدامها؟
-هذا الوضع يعكس — بكل أسف — خللًا في فهم أو تطبيق الحكم القضائي أو عدم اتساق في الإجراءات.
-ما أتعرض له لم يعد مجرد إجراء بنكي، بل أثر بشكل مباشر على:
-وضعي النفسي
-استقراري الاجتماعي
-التزاماتي المالية والمعيشية
-كما أن غياب جهة واضحة تتحمل المسؤولية، وعدم وجود معالجة جدية، يزيد من تعقيد الوضع.
-أطالب الإدارة العليا في مصرف الإمارات الإسلامي بـ:
-✔️ الالتزام بالحكم القضائي وتفسيره
-✔️ وقف أي إجراءات غير متسقة معه
-✔️ رفع التجميد غير المبرر
-✔️ توضيح رسمي للحالة ومعالجتها بشكل عاجل
-آمل أن يتم التعامل مع الموضوع بالجدية اللازمة، حيث أن الوضع لم يعد يحتمل المزيد من التأخير.
-&lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تصعيد"&gt;#تصعيد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مصرف_الإمارات_الإسلامي"&gt;#مصرف_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23العدالة"&gt;#العدالة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق"&gt;#حقوق&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility &lt;a href="https://www.zawya.com/en/press-release/companies-news/emirates-islamic-successfully-concludes-its-five-year-club-commodity-murabaha-term-facility-ah1svn56"&gt;zawya.com/en/press-release/c…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1139,36 +1025,36 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 11:46 AM UTC</t>
+          <t>Mar 31, 2026 · 1:32 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-03-30T11:46:00Z</t>
+          <t>2026-03-31T13:32:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23تصعيد', 'https://x.com/search?f=tweets&amp;q=%23مصرف_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23العدالة', 'https://x.com/search?f=tweets&amp;q=%23حقوق', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+          <t>['https://www.zawya.com/en/press-release/companies-news/emirates-islamic-successfully-concludes-its-five-year-club-commodity-murabaha-term-facility-ah1svn56']</t>
         </is>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1177,12 +1063,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2038575380282437864</t>
+          <t>2038970467663368198</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2038575380282437864</t>
+          <t>https://x.com/emiratesislamic/status/2038970467663368198</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1208,53 +1094,57 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>Protect yourself and those around you.
+Never share your PIN, password, or OTP.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud #TogetherAgainstFraud</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>Protect yourself and those around you.
+Never share your PIN, password, or OTP.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['abuzubayr1987']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 11:13 AM UTC</t>
+          <t>Mar 31, 2026 · 1:23 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-03-30T11:13:00Z</t>
+          <t>2026-03-31T13:23:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -1263,82 +1153,88 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2038531210058866754</t>
+          <t>2038970465432011060</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/ZiadaKhalid/status/2038531210058866754</t>
+          <t>https://x.com/emiratesislamic/status/2038970465432011060</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/ZiadaKhalid</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ZiadaKhalid</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mohamed Khalid Ziada</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1275391016313520139/YT7jm928_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+          <t>احمي نفسك ومن حولك
+لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+          <t>احمي نفسك ومن حولك
+لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 8:18 AM UTC</t>
+          <t>Mar 31, 2026 · 1:23 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-03-30T08:18:00Z</t>
+          <t>2026-03-31T13:23:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1347,12 +1243,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2038575380282437864</t>
+          <t>2038956701974503591</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2038575380282437864</t>
+          <t>https://x.com/emiratesislamic/status/2038956701974503591</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1378,14 +1274,12 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1394,28 +1288,28 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>['abuzubayr1987']</t>
+          <t>['Saeed_20212']</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 11:13 AM UTC</t>
+          <t>Mar 31, 2026 · 12:28 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-03-30T11:13:00Z</t>
+          <t>2026-03-31T12:28:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1424,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -1433,81 +1327,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2038702486702461222</t>
+          <t>2038941653596324169</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/MNadaver/status/2038702486702461222</t>
+          <t>https://x.com/Saeed_20212/status/2038941653596324169</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/MNadaver</t>
+          <t>https://x.com/Saeed_20212</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MNadaver</t>
+          <t>Saeed_20212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Achi Harshath | ಅಚ್ಚಿ ಹರ್ಷತ್</t>
+          <t>سعيد UAE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1254006517419966465/aHDAzOS5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1525071063662661637/25A1SNZT_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>@emiratesislamic , your cards services still seem to have impact.
-Bills not getting generated 
-Not been able to switch between cash back and travel 
-Rewards option not working
-Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; , your cards services still seem to have impact.
-Bills not getting generated 
-Not been able to switch between cash back and travel 
-Rewards option not working
-Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 7:38 PM UTC</t>
+          <t>Mar 31, 2026 · 11:29 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:00Z</t>
+          <t>2026-03-31T11:29:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1516,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1525,43 +1411,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2038665761175076929</t>
+          <t>2038924469515739647</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987/status/2038665761175076929</t>
+          <t>https://x.com/emiratesislamic/status/2038924469515739647</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>abuzubayr1987</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Safwan</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nothing useful. I already have done that on 25th March.After which the account manager promised to send an email to the management and also call back.I got nothing from Ms Mahra (account manager).Etisalat blocked, rent is due, medical bills in debt all because of your actions.</t>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1570,22 +1456,22 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['altamashhkhann']</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 5:12 PM UTC</t>
+          <t>Mar 31, 2026 · 10:20 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-03-30T17:12:00Z</t>
+          <t>2026-03-31T10:20:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1600,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1609,43 +1495,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2038531210058866754</t>
+          <t>2038888716849029128</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/ZiadaKhalid/status/2038531210058866754</t>
+          <t>https://x.com/emiratesislamic/status/2038888716849029128</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/ZiadaKhalid</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ZiadaKhalid</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mohamed Khalid Ziada</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1275391016313520139/YT7jm928_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1654,22 +1542,22 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['abuzubayr1987']</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 8:18 AM UTC</t>
+          <t>Mar 31, 2026 · 7:58 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-03-30T08:18:00Z</t>
+          <t>2026-03-31T07:58:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1684,7 +1572,1125 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2038864454222262474</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038864454222262474</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['ZiadaKhalid']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 6:22 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-03-31T06:22:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2039029089705591194</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2039029089705591194</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- emiratesislamic.ae/en/news-a…</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- &lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 5:16 PM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-03-31T17:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2039029079148536148</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2039029079148536148</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
+اقرأ المقال هنا:  emiratesislamic.ae/ar/news-a…</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
+اقرأ المقال هنا:  &lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 5:16 PM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-03-31T17:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2038970467663368198</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038970467663368198</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Protect yourself and those around you.
+Never share your PIN, password, or OTP.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud #TogetherAgainstFraud</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Protect yourself and those around you.
+Never share your PIN, password, or OTP.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 1:23 PM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-03-31T13:23:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2038970465432011060</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038970465432011060</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>احمي نفسك ومن حولك
+لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>احمي نفسك ومن حولك
+لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 1:23 PM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-03-31T13:23:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2038956701974503591</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038956701974503591</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['Saeed_20212']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 12:28 PM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-03-31T12:28:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2038924469515739647</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038924469515739647</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['altamashhkhann']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 10:20 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-03-31T10:20:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2038888716849029128</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038888716849029128</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 7:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:58:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2038864454222262474</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038864454222262474</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>['ZiadaKhalid']</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 6:22 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-03-31T06:22:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2039159510951170144</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451/status/2039159510951170144</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mohamed Wakeb</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 1, 2026 · 1:54 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-01T01:54:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2039029089705591194</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2039029089705591194</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- emiratesislamic.ae/en/news-a…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- &lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 5:16 PM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-03-31T17:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2038970467663368198</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038970467663368198</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Protect yourself and those around you.
+Never share your PIN, password, or OTP.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud #TogetherAgainstFraud</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Protect yourself and those around you.
+Never share your PIN, password, or OTP.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 1:23 PM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-03-31T13:23:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2038941653596324169</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/Saeed_20212/status/2038941653596324169</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/Saeed_20212</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Saeed_20212</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>سعيد UAE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1525071063662661637/25A1SNZT_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 11:29 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-03-31T11:29:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,258 @@
       </c>
       <c r="V9" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2039227761034985566</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451/status/2039227761034985566</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mohamed Wakeb</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>In addition, customer care, has autoreply, I sent two emails and no one called or acknowledge. Very sad service. I need a resolution today Or close the accounts and give us our money to go to another bank with better service</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>In addition, customer care, has autoreply, I sent two emails and no one called or acknowledge. Very sad service. I need a resolution today Or close the accounts and give us our money to go to another bank with better service</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Apr 1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Apr 1, 2026 · 6:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-04-01T06:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2039224717811519782</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451/status/2039224717811519782</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mohamed Wakeb</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>We have our corporate account with you SIG Middle East, with two authorized signatories for payments, I took care of one and the second for our Chief legal officer during to technical OTP issue can not authorize, so we have a delay to pay suppliers and payrol, CC autoreply</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>We have our corporate account with you SIG Middle East, with two authorized signatories for payments, I took care of one and the second for our Chief legal officer during to technical OTP issue can not authorize, so we have a delay to pay suppliers and payrol, CC autoreply</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Apr 1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 1, 2026 · 6:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-01T06:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2039159510951170144</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451/status/2039159510951170144</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>383c9b71f3e5451</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mohamed Wakeb</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Apr 1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 1, 2026 · 1:54 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-01T01:54:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,56 +541,54 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2039275249779290256</t>
+          <t>2039637656037134542</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039275249779290256</t>
+          <t>https://x.com/383c9b71f3e5451/status/2039637656037134542</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/383c9b71f3e5451</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>383c9b71f3e5451</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mohamed Wakeb</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ليس كل ما ينتشر يستحق أن نتبعه.
-أحياناً، القرار الأذكى هو الالتزام بخطتك الخاصة.
-لمعرفة المزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ليس كل ما ينتشر يستحق أن نتبعه.
-أحياناً، القرار الأذكى هو الالتزام بخطتك الخاصة.
-لمعرفة المزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>18h</t>
@@ -598,20 +596,16 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 9:34 AM UTC</t>
+          <t>Apr 2, 2026 · 9:34 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-01T09:34:00Z</t>
+          <t>2026-04-02T09:34:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -622,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -631,50 +625,54 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2039266761464549553</t>
+          <t>2039616881259409516</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2039266761464549553</t>
+          <t>https://x.com/383c9b71f3e5451/status/2039616881259409516</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance</t>
+          <t>https://x.com/383c9b71f3e5451</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ForumRemittance</t>
+          <t>383c9b71f3e5451</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>World Remittance Action Forum</t>
+          <t>Mohamed Wakeb</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1942959686417891328/FNdImGgE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a leading Islamic financial institution in the UAE, has successfully completed its USD 500 million, five-year Club Commodity Murabaha term facility—marking a strong milestone in its funding journey.#UAE #IslamicFinance #Banking #Murabaha #FinanceNews</t>
+          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a leading Islamic financial institution in the UAE, has successfully completed its USD 500 million, five-year Club Commodity Murabaha term facility—marking a strong milestone in its funding journey.&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicFinance"&gt;#IslamicFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Murabaha"&gt;#Murabaha&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinanceNews"&gt;#FinanceNews&lt;/a&gt;</t>
+          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>19h</t>
@@ -682,20 +680,16 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 9:00 AM UTC</t>
+          <t>Apr 2, 2026 · 8:12 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-01T09:00:00Z</t>
+          <t>2026-04-02T08:12:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23IslamicFinance', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Murabaha', 'https://x.com/search?f=tweets&amp;q=%23FinanceNews']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -706,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -715,12 +709,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2039227761034985566</t>
+          <t>2039604342672797930</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039227761034985566</t>
+          <t>https://x.com/383c9b71f3e5451/status/2039604342672797930</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -746,12 +740,12 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>In addition, customer care, has autoreply, I sent two emails and no one called or acknowledge. Very sad service. I need a resolution today Or close the accounts and give us our money to go to another bank with better service</t>
+          <t>The worth bank ever. Useless IT and technical support.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>In addition, customer care, has autoreply, I sent two emails and no one called or acknowledge. Very sad service. I need a resolution today Or close the accounts and give us our money to go to another bank with better service</t>
+          <t>The worth bank ever. Useless IT and technical support.</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -765,23 +759,23 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 6:25 AM UTC</t>
+          <t>Apr 2, 2026 · 7:22 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-01T06:25:00Z</t>
+          <t>2026-04-02T07:22:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -790,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -799,71 +793,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2039224717811519782</t>
+          <t>2039583608361435158</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039224717811519782</t>
+          <t>https://x.com/emiratesislamic/status/2039583608361435158</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>We have our corporate account with you SIG Middle East, with two authorized signatories for payments, I took care of one and the second for our Chief legal officer during to technical OTP issue can not authorize, so we have a delay to pay suppliers and payrol, CC autoreply</t>
+          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
+#FinancialWellbeing #Finwell #EmiratesIslamic #Investing 
+To know more: 
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>We have our corporate account with you SIG Middle East, with two authorized signatories for payments, I took care of one and the second for our Chief legal officer during to technical OTP issue can not authorize, so we have a delay to pay suppliers and payrol, CC autoreply</t>
+          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt; 
+To know more: 
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 6:13 AM UTC</t>
+          <t>Apr 2, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-01T06:13:00Z</t>
+          <t>2026-04-02T06:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -883,12 +883,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2039220375951675799</t>
+          <t>2039612700003586256</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039220375951675799</t>
+          <t>https://x.com/emiratesislamic/status/2039612700003586256</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 5:56 AM UTC</t>
+          <t>Apr 2, 2026 · 7:55 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-01T05:56:00Z</t>
+          <t>2026-04-02T07:55:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -967,71 +967,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2039159510951170144</t>
+          <t>2039583608441045072</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039159510951170144</t>
+          <t>https://x.com/emiratesislamic/status/2039583608441045072</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
+          <t>كل رحلة استثمار تبدأ بسؤال بسيط: لماذا؟
+وعندما يكون الهدف واضحاً، يمكن للبدايات الصغيرة أن تنمو بثبات مع الوقت.
+لتعرف على المزيد: 
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
+          <t>كل رحلة استثمار تبدأ بسؤال بسيط: لماذا؟
+وعندما يكون الهدف واضحاً، يمكن للبدايات الصغيرة أن تنمو بثبات مع الوقت.
+لتعرف على المزيد: 
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Apr 1</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 1:54 AM UTC</t>
+          <t>Apr 2, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-01T01:54:00Z</t>
+          <t>2026-04-02T06:00:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
@@ -1042,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -1051,12 +1057,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2039275249779290256</t>
+          <t>2039583608361435158</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039275249779290256</t>
+          <t>https://x.com/emiratesislamic/status/2039583608361435158</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1082,18 +1088,18 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ليس كل ما ينتشر يستحق أن نتبعه.
-أحياناً، القرار الأذكى هو الالتزام بخطتك الخاصة.
-لمعرفة المزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
+#FinancialWellbeing #Finwell #EmiratesIslamic #Investing 
+To know more: 
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ليس كل ما ينتشر يستحق أن نتبعه.
-أحياناً، القرار الأذكى هو الالتزام بخطتك الخاصة.
-لمعرفة المزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt; 
+To know more: 
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1103,23 +1109,23 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 9:34 AM UTC</t>
+          <t>Apr 2, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-01T09:34:00Z</t>
+          <t>2026-04-02T06:00:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1132,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -1141,43 +1147,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2039220375951675799</t>
+          <t>2039637656037134542</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039220375951675799</t>
+          <t>https://x.com/383c9b71f3e5451/status/2039637656037134542</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/383c9b71f3e5451</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>383c9b71f3e5451</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mohamed Wakeb</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1186,28 +1192,28 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>['383c9b71f3e5451']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 5:56 AM UTC</t>
+          <t>Apr 2, 2026 · 9:34 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-01T05:56:00Z</t>
+          <t>2026-04-02T09:34:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1216,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1225,12 +1231,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2039227761034985566</t>
+          <t>2039616881259409516</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039227761034985566</t>
+          <t>https://x.com/383c9b71f3e5451/status/2039616881259409516</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1256,12 +1262,12 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>In addition, customer care, has autoreply, I sent two emails and no one called or acknowledge. Very sad service. I need a resolution today Or close the accounts and give us our money to go to another bank with better service</t>
+          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>In addition, customer care, has autoreply, I sent two emails and no one called or acknowledge. Very sad service. I need a resolution today Or close the accounts and give us our money to go to another bank with better service</t>
+          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1275,17 +1281,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Apr 1</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 6:25 AM UTC</t>
+          <t>Apr 2, 2026 · 8:12 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-01T06:25:00Z</t>
+          <t>2026-04-02T08:12:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1300,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1309,12 +1315,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2039224717811519782</t>
+          <t>2039604342672797930</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039224717811519782</t>
+          <t>https://x.com/383c9b71f3e5451/status/2039604342672797930</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1340,12 +1346,12 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>We have our corporate account with you SIG Middle East, with two authorized signatories for payments, I took care of one and the second for our Chief legal officer during to technical OTP issue can not authorize, so we have a delay to pay suppliers and payrol, CC autoreply</t>
+          <t>The worth bank ever. Useless IT and technical support.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>We have our corporate account with you SIG Middle East, with two authorized signatories for payments, I took care of one and the second for our Chief legal officer during to technical OTP issue can not authorize, so we have a delay to pay suppliers and payrol, CC autoreply</t>
+          <t>The worth bank ever. Useless IT and technical support.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1359,23 +1365,23 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Apr 1</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 6:13 AM UTC</t>
+          <t>Apr 2, 2026 · 7:22 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-01T06:13:00Z</t>
+          <t>2026-04-02T07:22:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1384,91 +1390,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2039159510951170144</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039159510951170144</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://x.com/383c9b71f3e5451</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>383c9b71f3e5451</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mohamed Wakeb</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>I had thebworst experience with this bank. Customer care is useless, technical team is useless, the OTP not working , all my payments are delayed because if incompetence. Very sad. Time to close all my corporate accounts.</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Apr 1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apr 1, 2026 · 1:54 AM UTC</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-04-01T01:54:00Z</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,43 +541,59 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2039637656037134542</t>
+          <t>2040271345058209886</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039637656037134542</t>
+          <t>https://x.com/mubi_111/status/2040271345058209886</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/mubi_111</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>mubi_111</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>Mubarak Albreiki</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
+          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
+تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
+هذا التصرف يثير الكثير من علامات الاستفهام:
+هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
+أين الشفافية في التعامل؟
+وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
+ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
+أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
+#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
+          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
+تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
+هذا التصرف يثير الكثير من علامات الاستفهام:
+هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
+أين الشفافية في التعامل؟
+وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
+ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
+أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
+&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -591,21 +607,25 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>27m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 9:34 AM UTC</t>
+          <t>Apr 4, 2026 · 3:32 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-02T09:34:00Z</t>
+          <t>2026-04-04T03:32:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -625,43 +645,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2039616881259409516</t>
+          <t>2040108266739638620</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039616881259409516</t>
+          <t>https://x.com/mfaizanpatel1/status/2040108266739638620</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/mfaizanpatel1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>mfaizanpatel1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>Muhammad Faizan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1515613556649119744/hD4s4pZv_bigger.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
+          <t>Since when I am getting the same response… its a clear fraud company
+@emiratesislamic you are promoting to your card holders you should atleast check the company</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
+          <t>Since when I am getting the same response… its a clear fraud company
+&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; you are promoting to your card holders you should atleast check the company</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -670,26 +692,30 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['CleartripAE', 'Cleartrip']</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 8:12 AM UTC</t>
+          <t>Apr 3, 2026 · 4:44 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-02T08:12:00Z</t>
+          <t>2026-04-03T16:44:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -700,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -709,43 +735,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2039604342672797930</t>
+          <t>2040103090209308947</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039604342672797930</t>
+          <t>https://x.com/CleartripAE/status/2040103090209308947</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/CleartripAE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>CleartripAE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>Cleartrip Arabia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1986324933459517447/bzXaTqX-_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The worth bank ever. Useless IT and technical support.</t>
+          <t>Hello dear🌹
+We regret the inconvenience caused. Please note that we have escalated this matter to our higher authorities, and you will receive an update from our team soon</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The worth bank ever. Useless IT and technical support.</t>
+          <t>Hello dear🌹
+We regret the inconvenience caused. Please note that we have escalated this matter to our higher authorities, and you will receive an update from our team soon</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -754,22 +782,22 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['mfaizanpatel1', 'Cleartrip', 'emiratesislamic']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 7:22 AM UTC</t>
+          <t>Apr 3, 2026 · 4:24 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-02T07:22:00Z</t>
+          <t>2026-04-03T16:24:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -784,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -793,12 +821,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2039583608361435158</t>
+          <t>2040020307231035761</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039583608361435158</t>
+          <t>https://x.com/emiratesislamic/status/2040020307231035761</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -824,18 +852,20 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
-#FinancialWellbeing #Finwell #EmiratesIslamic #Investing 
-To know more: 
-emiratesislamic.ae/en/key-in…</t>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;Cs apply.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt; 
-To know more: 
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -845,23 +875,23 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 6:00 AM UTC</t>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-02T06:00:00Z</t>
+          <t>2026-04-03T10:55:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -874,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -883,12 +913,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2039612700003586256</t>
+          <t>2040020304446026150</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039612700003586256</t>
+          <t>https://x.com/emiratesislamic/status/2040020304446026150</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -914,51 +944,53 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['383c9b71f3e5451']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 7:55 AM UTC</t>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-02T07:55:00Z</t>
+          <t>2026-04-03T10:55:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -967,12 +999,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2039583608441045072</t>
+          <t>2040020294450958389</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039583608441045072</t>
+          <t>https://x.com/emiratesislamic/status/2040020294450958389</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -998,18 +1030,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>كل رحلة استثمار تبدأ بسؤال بسيط: لماذا؟
-وعندما يكون الهدف واضحاً، يمكن للبدايات الصغيرة أن تنمو بثبات مع الوقت.
-لتعرف على المزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>كل رحلة استثمار تبدأ بسؤال بسيط: لماذا؟
-وعندما يكون الهدف واضحاً، يمكن للبدايات الصغيرة أن تنمو بثبات مع الوقت.
-لتعرف على المزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1019,27 +1053,27 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 6:00 AM UTC</t>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-02T06:00:00Z</t>
+          <t>2026-04-03T10:55:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1048,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1057,12 +1091,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2039583608361435158</t>
+          <t>2040020291217248399</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039583608361435158</t>
+          <t>https://x.com/emiratesislamic/status/2040020291217248399</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1088,18 +1122,18 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
-#FinancialWellbeing #Finwell #EmiratesIslamic #Investing 
-To know more: 
-emiratesislamic.ae/en/key-in…</t>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Every investment journey starts with a simple question: why? When your goal is clear, starting small can grow into something meaningful over time.
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt; 
-To know more: 
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1109,27 +1143,23 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 6:00 AM UTC</t>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-02T06:00:00Z</t>
+          <t>2026-04-03T10:55:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1138,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
@@ -1147,43 +1177,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2039637656037134542</t>
+          <t>2039972991535313329</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039637656037134542</t>
+          <t>https://x.com/mfaizanpatel1/status/2039972991535313329</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/mfaizanpatel1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>mfaizanpatel1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>Muhammad Faizan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1515613556649119744/hD4s4pZv_bigger.png</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
+          <t>I followed you now</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>This is what I have receiving from you all along. Autoreply instead of solving your customers problem. Very sad.</t>
+          <t>I followed you now</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1197,17 +1227,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 9:34 AM UTC</t>
+          <t>Apr 3, 2026 · 7:47 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-02T09:34:00Z</t>
+          <t>2026-04-03T07:47:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1222,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1231,43 +1261,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2039616881259409516</t>
+          <t>2039972726580896171</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039616881259409516</t>
+          <t>https://x.com/emiratesislamic/status/2039972726580896171</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back to assist you better.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>It has been one week. Worth service ever. We can not pay our suppliers and staff. Customer service talk to IT and IT can not do anything. Hopeless case. Please close my accounts and prepare a cashier check until you get your act together.</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back to assist you better.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1276,28 +1306,28 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['mfaizanpatel1']</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 2, 2026 · 8:12 AM UTC</t>
+          <t>Apr 3, 2026 · 7:46 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-02T08:12:00Z</t>
+          <t>2026-04-03T07:46:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1306,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1315,82 +1345,898 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2039604342672797930</t>
+          <t>2039963428429926790</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451/status/2039604342672797930</t>
+          <t>https://x.com/mfaizanpatel1/status/2039963428429926790</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/383c9b71f3e5451</t>
+          <t>https://x.com/mfaizanpatel1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>383c9b71f3e5451</t>
+          <t>mfaizanpatel1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mohamed Wakeb</t>
+          <t>Muhammad Faizan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/981940207653093377/5xwlh2YW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1515613556649119744/hD4s4pZv_bigger.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The worth bank ever. Useless IT and technical support.</t>
+          <t>@CleartripAE @Cleartrip 
+Dear #ClearTrap I am still waiting for my refund… no one yet contacted me
+@emiratesislamic you promote fraud cleartrip to your credit card customers. I used them and now I am traped. You should do proper business check before promoting to any company..</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>The worth bank ever. Useless IT and technical support.</t>
+          <t>&lt;a href="/CleartripAE" title="Cleartrip Arabia"&gt;@CleartripAE&lt;/a&gt; &lt;a href="/Cleartrip" title="Cleartrip"&gt;@Cleartrip&lt;/a&gt; 
+Dear &lt;a href="/search?f=tweets&amp;amp;q=%23ClearTrap"&gt;#ClearTrap&lt;/a&gt; I am still waiting for my refund… no one yet contacted me
+&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; you promote fraud cleartrip to your credit card customers. I used them and now I am traped. You should do proper business check before promoting to any company..</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 7:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-03T07:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/CleartripAE', 'https://x.com/Cleartrip', 'https://x.com/search?f=tweets&amp;q=%23ClearTrap', 'https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2040020307231035761</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2040020307231035761</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;Cs apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2040020304446026150</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2040020304446026150</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2040020294450958389</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2040020294450958389</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2040020291217248399</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2040020291217248399</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2039972726580896171</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2039972726580896171</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back to assist you better.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back to assist you better.</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>['mfaizanpatel1']</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 7:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-03T07:46:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2040271345058209886</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/mubi_111/status/2040271345058209886</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/mubi_111</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>mubi_111</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mubarak Albreiki</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
+تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
+هذا التصرف يثير الكثير من علامات الاستفهام:
+هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
+أين الشفافية في التعامل؟
+وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
+ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
+أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
+#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
+تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
+هذا التصرف يثير الكثير من علامات الاستفهام:
+هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
+أين الشفافية في التعامل؟
+وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
+ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
+أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
+&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>28m</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 4, 2026 · 3:32 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-04T03:32:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2040020307231035761</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2040020307231035761</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;Cs apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2040020294450958389</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2040020294450958389</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2039972991535313329</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/mfaizanpatel1/status/2039972991535313329</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/mfaizanpatel1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>mfaizanpatel1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Muhammad Faizan</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1515613556649119744/hD4s4pZv_bigger.png</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>I followed you now</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>I followed you now</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Apr 2, 2026 · 7:22 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-04-02T07:22:00Z</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 3, 2026 · 7:47 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-03T07:47:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,67 +541,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2040328252468940931</t>
+          <t>2040844356056473711</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040328252468940931</t>
+          <t>https://x.com/SanjivRanjanJh1/status/2040844356056473711</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/SanjivRanjanJh1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>SanjivRanjanJh1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>Sanjiv Ranjan Jha</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1578903407347519488/U1NS9YTz_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
+          <t>Exposed Incredibly 🇮🇳
+Assam State's Ruling Chief Minister's Wife Holds 4 Country's Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp; Barbuda.
+Statuary Law Permits One Passport.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
+          <t>Exposed Incredibly 🇮🇳
+Assam State&amp;#39;s Ruling Chief Minister&amp;#39;s Wife Holds 4 Country&amp;#39;s Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp;amp; Barbuda.
+Statuary Law Permits One Passport.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:18 AM UTC</t>
+          <t>Apr 5, 2026 · 5:29 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-04T07:18:00Z</t>
+          <t>2026-04-05T17:29:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -625,43 +625,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2040327735621656747</t>
+          <t>2041040982007861527</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040327735621656747</t>
+          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -670,22 +670,22 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['mubi_111']</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>38m</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
+          <t>Apr 6, 2026 · 6:31 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-04T07:16:00Z</t>
+          <t>2026-04-06T06:31:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -709,43 +709,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2040327679250153863</t>
+          <t>2041040843369320743</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040327679250153863</t>
+          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -754,22 +756,22 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['mubi_111']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>38m</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-04T07:16:00Z</t>
+          <t>2026-04-06T06:30:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -784,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -793,59 +795,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2040280370994889131</t>
+          <t>2041040799563915686</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111/status/2040280370994889131</t>
+          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mubi_111</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mubarak Albreiki</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -854,30 +840,26 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['mubi_111']</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>39m</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 4:08 AM UTC</t>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-04T04:08:00Z</t>
+          <t>2026-04-06T06:30:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>0</v>
       </c>
@@ -888,571 +870,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2040271345058209886</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://x.com/mubi_111/status/2040271345058209886</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://x.com/mubi_111</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>mubi_111</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mubarak Albreiki</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Apr 4</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Apr 4, 2026 · 3:32 AM UTC</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-04-04T03:32:00Z</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2040328252468940931</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://x.com/MatarAlAl/status/2040328252468940931</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/MatarAlAl</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MatarAlAl</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Matar Al Ali</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Apr 4, 2026 · 7:18 AM UTC</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-04-04T07:18:00Z</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2040327735621656747</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/MatarAlAl/status/2040327735621656747</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/MatarAlAl</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MatarAlAl</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Matar Al Ali</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-04-04T07:16:00Z</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2040327679250153863</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/MatarAlAl/status/2040327679250153863</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/MatarAlAl</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MatarAlAl</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Matar Al Ali</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-04-04T07:16:00Z</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2040280370994889131</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://x.com/mubi_111/status/2040280370994889131</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/mubi_111</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mubi_111</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mubarak Albreiki</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Apr 4, 2026 · 4:08 AM UTC</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-04-04T04:08:00Z</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2040271345058209886</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://x.com/mubi_111/status/2040271345058209886</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/mubi_111</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>mubi_111</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Mubarak Albreiki</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Apr 4</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Apr 4, 2026 · 3:32 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-04-04T03:32:00Z</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>589</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,47 +541,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2040844356056473711</t>
+          <t>2041055155320152414</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/SanjivRanjanJh1/status/2040844356056473711</t>
+          <t>https://x.com/emiratesislamic/status/2041055155320152414</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/SanjivRanjanJh1</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SanjivRanjanJh1</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sanjiv Ranjan Jha</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1578903407347519488/U1NS9YTz_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Exposed Incredibly 🇮🇳
-Assam State's Ruling Chief Minister's Wife Holds 4 Country's Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp; Barbuda.
-Statuary Law Permits One Passport.</t>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Exposed Incredibly 🇮🇳
-Assam State&amp;#39;s Ruling Chief Minister&amp;#39;s Wife Holds 4 Country&amp;#39;s Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp;amp; Barbuda.
-Statuary Law Permits One Passport.</t>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -591,21 +591,25 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>14m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 5, 2026 · 5:29 PM UTC</t>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-05T17:29:00Z</t>
+          <t>2026-04-06T07:27:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -625,12 +629,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2041040982007861527</t>
+          <t>2041055153344651481</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -656,42 +660,38 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>Whether you're budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>Whether you&amp;#39;re budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['mubi_111']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>38m</t>
+          <t>14m</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:31 AM UTC</t>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-06T06:31:00Z</t>
+          <t>2026-04-06T07:27:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -709,12 +709,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2041040843369320743</t>
+          <t>2041055144217915495</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
+          <t>https://x.com/emiratesislamic/status/2041055144217915495</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -740,44 +740,46 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['mubi_111']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>38m</t>
+          <t>14m</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-06T06:30:00Z</t>
+          <t>2026-04-06T07:27:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -786,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -795,12 +797,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2041040799563915686</t>
+          <t>2041055106427183208</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+          <t>https://x.com/emiratesislamic/status/2041055106427183208</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -826,42 +828,38 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['mubi_111']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>39m</t>
+          <t>14m</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-06T06:30:00Z</t>
+          <t>2026-04-06T07:27:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -870,6 +868,688 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2041054585297740229</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/kmz1993/status/2041054585297740229</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/kmz1993</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>kmz1993</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t> خالد</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1475344667810349059/JlxW8n_8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['ADIBTweets']</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2041040982007861527</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:31 AM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:31:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2041040843369320743</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2041040799563915686</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2040844356056473711</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/SanjivRanjanJh1/status/2040844356056473711</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/SanjivRanjanJh1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SanjivRanjanJh1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sanjiv Ranjan Jha</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1578903407347519488/U1NS9YTz_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Exposed Incredibly 🇮🇳
+Assam State's Ruling Chief Minister's Wife Holds 4 Country's Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp; Barbuda.
+Statuary Law Permits One Passport.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Exposed Incredibly 🇮🇳
+Assam State&amp;#39;s Ruling Chief Minister&amp;#39;s Wife Holds 4 Country&amp;#39;s Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp;amp; Barbuda.
+Statuary Law Permits One Passport.</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Apr 5, 2026 · 5:29 PM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-04-05T17:29:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2041040982007861527</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>38m</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:31 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:31:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2041040843369320743</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>38m</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2041040799563915686</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>39m</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
         <v>1</v>
       </c>
     </row>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,77 +541,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2041055155320152414</t>
+          <t>2041070222657151340</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041055155320152414</t>
+          <t>https://x.com/kmz1993/status/2041070222657151340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/kmz1993</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>kmz1993</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t> خالد</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1475344667810349059/JlxW8n_8_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
-Strong financial well-being begins with consistent saving, no matter the amount.
-To know more visit  emiratesislamic.ae/en/Person…</t>
+          <t>الكلمات توفي حقكم بالنظر إلى عملكم الجاد شكراً من القلب ❤️🌹</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
-Strong financial well-being begins with consistent saving, no matter the amount.
-To know more visit  &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>الكلمات توفي حقكم بالنظر إلى عملكم الجاد شكراً من القلب ❤️🌹</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>14m</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+          <t>Apr 6, 2026 · 8:27 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-06T07:27:00Z</t>
+          <t>2026-04-06T08:27:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -620,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -629,67 +625,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2041055153344651481</t>
+          <t>2041054585297740229</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
+          <t>https://x.com/kmz1993/status/2041054585297740229</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/kmz1993</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>kmz1993</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t> خالد</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1475344667810349059/JlxW8n_8_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Whether you're budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Whether you&amp;#39;re budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['ADIBTweets']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>14m</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+          <t>Apr 6, 2026 · 7:25 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-06T07:27:00Z</t>
+          <t>2026-04-06T07:25:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
@@ -700,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -709,12 +715,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2041055144217915495</t>
+          <t>2041148131039953343</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041055144217915495</t>
+          <t>https://x.com/emiratesislamic/status/2041148131039953343</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -740,16 +746,24 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
+          <t>🍔 50% discount on talabat
+🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 30 April 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>🍔 50% discount on talabat
+🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 30 April 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -759,27 +773,27 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>14m</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-06T07:27:00Z</t>
+          <t>2026-04-06T13:36:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -788,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -797,12 +811,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2041055106427183208</t>
+          <t>2041148122731004026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041055106427183208</t>
+          <t>https://x.com/emiratesislamic/status/2041148122731004026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,12 +842,16 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spend</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spend</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -843,17 +861,17 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>14m</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-06T07:27:00Z</t>
+          <t>2026-04-06T13:36:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -868,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -877,75 +895,81 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2041054585297740229</t>
+          <t>2041148111138029956</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/kmz1993/status/2041054585297740229</t>
+          <t>https://x.com/emiratesislamic/status/2041148111138029956</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/kmz1993</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>kmz1993</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t> خالد</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1475344667810349059/JlxW8n_8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
-أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+          <t>🍔 خصم لغاية %50 على طلبات
+ 🚗 خدمة صف السيارات
+ 🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 30 أبريل 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
-أما &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+          <t>🍔 خصم لغاية %50 على طلبات
+ 🚗 خدمة صف السيارات
+ 🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 30 أبريل 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['ADIBTweets']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>16m</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 7:25 AM UTC</t>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-06T07:25:00Z</t>
+          <t>2026-04-06T13:36:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -958,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -967,12 +991,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2041040982007861527</t>
+          <t>2041148101944074609</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+          <t>https://x.com/emiratesislamic/status/2041148101944074609</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -998,42 +1022,42 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['mubi_111']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:31 AM UTC</t>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-06T06:31:00Z</t>
+          <t>2026-04-06T13:36:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1042,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -1051,12 +1075,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2041040843369320743</t>
+          <t>2041113449439117594</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
+          <t>https://x.com/emiratesislamic/status/2041113449439117594</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1082,14 +1106,12 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1098,22 +1120,22 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['mubi_111']</t>
+          <t>['mfaizanpatel1']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+          <t>Apr 6, 2026 · 11:19 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-06T06:30:00Z</t>
+          <t>2026-04-06T11:19:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1128,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1137,12 +1159,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2041040799563915686</t>
+          <t>2041106421236801624</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+          <t>https://x.com/emiratesislamic/status/2041106421236801624</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1168,12 +1190,12 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1182,22 +1204,22 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>['mubi_111']</t>
+          <t>['kmz1993']</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+          <t>Apr 6, 2026 · 10:51 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-06T06:30:00Z</t>
+          <t>2026-04-06T10:51:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1212,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1221,73 +1243,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2040844356056473711</t>
+          <t>2041069339676221766</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/SanjivRanjanJh1/status/2040844356056473711</t>
+          <t>https://x.com/emiratesislamic/status/2041069339676221766</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/SanjivRanjanJh1</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SanjivRanjanJh1</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sanjiv Ranjan Jha</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1578903407347519488/U1NS9YTz_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Exposed Incredibly 🇮🇳
-Assam State's Ruling Chief Minister's Wife Holds 4 Country's Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp; Barbuda.
-Statuary Law Permits One Passport.</t>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Exposed Incredibly 🇮🇳
-Assam State&amp;#39;s Ruling Chief Minister&amp;#39;s Wife Holds 4 Country&amp;#39;s Passports: India, Untied Arab Emirates, Islamic Republic of Egypt, Antigua &amp;amp; Barbuda.
-Statuary Law Permits One Passport.</t>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['kmz1993']</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 5, 2026 · 5:29 PM UTC</t>
+          <t>Apr 6, 2026 · 8:23 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-05T17:29:00Z</t>
+          <t>2026-04-06T08:23:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1296,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1305,12 +1327,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2041040982007861527</t>
+          <t>2041060091449823599</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+          <t>https://x.com/emiratesislamic/status/2041060091449823599</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1336,12 +1358,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1350,22 +1374,22 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>['mubi_111']</t>
+          <t>['MatarAlAl']</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>38m</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:31 AM UTC</t>
+          <t>Apr 6, 2026 · 7:47 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-06T06:31:00Z</t>
+          <t>2026-04-06T07:47:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1380,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1389,12 +1413,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2041040843369320743</t>
+          <t>2041060043106246934</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
+          <t>https://x.com/emiratesislamic/status/2041060043106246934</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1436,22 +1460,22 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>['mubi_111']</t>
+          <t>['MatarAlAl']</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>38m</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+          <t>Apr 6, 2026 · 7:46 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-06T06:30:00Z</t>
+          <t>2026-04-06T07:46:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1466,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -1475,12 +1499,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2041040799563915686</t>
+          <t>2041059967227076738</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+          <t>https://x.com/emiratesislamic/status/2041059967227076738</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1520,22 +1544,22 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>['mubi_111']</t>
+          <t>['MatarAlAl']</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>39m</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+          <t>Apr 6, 2026 · 7:46 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-06T06:30:00Z</t>
+          <t>2026-04-06T07:46:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1550,7 +1574,1129 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2041055155320152414</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055155320152414</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2041055153344651481</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Whether you're budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Whether you&amp;#39;re budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2041055144217915495</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055144217915495</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2041055106427183208</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055106427183208</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2041040982007861527</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:31 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:31:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2041040843369320743</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2041040799563915686</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-06T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2041148131039953343</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041148131039953343</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🍔 50% discount on talabat
+🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 30 April 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>🍔 50% discount on talabat
+🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 30 April 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-06T13:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2041148111138029956</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041148111138029956</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🍔 خصم لغاية %50 على طلبات
+ 🚗 خدمة صف السيارات
+ 🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 30 أبريل 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>🍔 خصم لغاية %50 على طلبات
+ 🚗 خدمة صف السيارات
+ 🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 30 أبريل 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-06T13:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2041070222657151340</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/kmz1993/status/2041070222657151340</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/kmz1993</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>kmz1993</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t> خالد</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1475344667810349059/JlxW8n_8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>الكلمات توفي حقكم بالنظر إلى عملكم الجاد شكراً من القلب ❤️🌹</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>الكلمات توفي حقكم بالنظر إلى عملكم الجاد شكراً من القلب ❤️🌹</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 8:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-06T08:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2041055155320152414</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055155320152414</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2041055153344651481</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Whether you're budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Whether you&amp;#39;re budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2041055144217915495</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055144217915495</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-06T07:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,12 +541,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2041429178898395470</t>
+          <t>2041809616133316853</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Nauphal/status/2041429178898395470</t>
+          <t>https://x.com/Nauphal/status/2041809616133316853</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -572,12 +572,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Thanks. But I have not received any direct messages.</t>
+          <t>Sent DM. Please respond.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Thanks. But I have not received any direct messages.</t>
+          <t>Sent DM. Please respond.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -591,17 +591,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 8:13 AM UTC</t>
+          <t>Apr 8, 2026 · 9:25 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-07T08:13:00Z</t>
+          <t>2026-04-08T09:25:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -625,71 +625,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2041418813942665225</t>
+          <t>2041770828887683094</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/NaserBadhafari/status/2041418813942665225</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770828887683094</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/NaserBadhafari</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NaserBadhafari</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Naser Badhafari</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1757298769316499456/eJ3kGFuh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Applying for that credit card was a real quest! They really put me through the wringer with all the documents and steps. Just when I thought I was done, boom, more requirements popped up. It was a real test of patience, I'll tell you that much! Last time to apply in this bank.</t>
+          <t>@emiratesislamic I'm posting here because i don't have an option out, SM team please look into it.》》</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Applying for that credit card was a real quest! They really put me through the wringer with all the documents and steps. Just when I thought I was done, boom, more requirements popped up. It was a real test of patience, I&amp;#39;ll tell you that much! Last time to apply in this bank.</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m posting here because i don&amp;#39;t have an option out, SM team please look into it.》》</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 7:32 AM UTC</t>
+          <t>Apr 8, 2026 · 6:51 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-07T07:32:00Z</t>
+          <t>2026-04-08T06:51:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -709,43 +709,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2041403223161090324</t>
+          <t>2041770661786612135</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/Nauphal/status/2041403223161090324</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770661786612135</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/Nauphal</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nauphal</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nauphal LLC SP</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>@emiratesislamic I was dealing with one of your finance advisors for some purpose since February. He is laid off recently and I am left with no point of contact and updates. He is not answering, not responding to messages, mails bouncing. No call back from customer care.</t>
+          <t>@emiratesislamic also i was told that the money on hold is due to my end of service. Now they're changing the story. As a customer I'm going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I was dealing with one of your finance advisors for some purpose since February. He is laid off recently and I am left with no point of contact and updates. He is not answering, not responding to messages, mails bouncing. No call back from customer care.</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; also i was told that the money on hold is due to my end of service. Now they&amp;#39;re changing the story. As a customer I&amp;#39;m going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -760,12 +760,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 6:30 AM UTC</t>
+          <t>Apr 8, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-07T06:30:00Z</t>
+          <t>2026-04-08T06:50:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -793,49 +793,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2041380450455765160</t>
+          <t>2041770214564753782</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041380450455765160</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770214564753782</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>@emiratesislamic the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -845,23 +839,23 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 5:00 AM UTC</t>
+          <t>Apr 8, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00Z</t>
+          <t>2026-04-08T06:48:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -874,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -883,71 +877,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2041429292442079730</t>
+          <t>2041769750137864312</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041429292442079730</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041769750137864312</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>@emiratesislamic I'm facing a terrible experience with EI. I've been contacting customer service back &amp; forth for the past 2 months for the end of service hold amount in my account. 
+I've been told that the hold amount would be released soon, even received an email mentioning《《</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m facing a terrible experience with EI. I&amp;#39;ve been contacting customer service back &amp;amp; forth for the past 2 months for the end of service hold amount in my account. 
+I&amp;#39;ve been told that the hold amount would be released soon, even received an email mentioning《《</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['NaserBadhafari']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 8:14 AM UTC</t>
+          <t>Apr 8, 2026 · 6:46 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-07T08:14:00Z</t>
+          <t>2026-04-08T06:46:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -967,43 +963,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2041424953585598604</t>
+          <t>2041761819669492128</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041424953585598604</t>
+          <t>https://x.com/Nauphal/status/2041761819669492128</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Nauphal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nauphal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nauphal LLC SP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>Hello, I haven't received any DM. No solution or response from other channels.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>Hello, I haven&amp;#39;t received any DM. No solution or response from other channels.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1012,22 +1008,22 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>['Nauphal']</t>
+          <t>['Nauphal', 'emiratesislamic']</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 7:56 AM UTC</t>
+          <t>Apr 8, 2026 · 6:15 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-07T07:56:00Z</t>
+          <t>2026-04-08T06:15:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1042,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1051,12 +1047,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2041395547878162650</t>
+          <t>2041760360621818126</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041395547878162650</t>
+          <t>https://x.com/emiratesislamic/status/2041760360621818126</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1082,22 +1078,16 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ليس كل قرار يجب أن يكون مثل الآخرين.
-الأهم هو أن تختار ما يناسبك أنت.
-أنفق بحكمة.
-مع الإمارات الإسلامي.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ليس كل قرار يجب أن يكون مثل الآخرين.
-الأهم هو أن تختار ما يناسبك أنت.
-أنفق بحكمة.
-مع الإمارات الإسلامي.
-للمزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1107,36 +1097,32 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 6:00 AM UTC</t>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-07T06:00:00Z</t>
+          <t>2026-04-08T06:09:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9">
@@ -1145,12 +1131,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2041380450455765160</t>
+          <t>2041757945084453281</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041380450455765160</t>
+          <t>https://x.com/emiratesislamic/status/2041757945084453281</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1176,18 +1162,18 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1197,36 +1183,32 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 5:00 AM UTC</t>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00Z</t>
+          <t>2026-04-08T06:00:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -1235,67 +1217,65 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2041429178898395470</t>
+          <t>2041821273811034189</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/Nauphal/status/2041429178898395470</t>
+          <t>https://x.com/emiratesislamic/status/2041821273811034189</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/Nauphal</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nauphal</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nauphal LLC SP</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Thanks. But I have not received any direct messages.</t>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Thanks. But I have not received any direct messages.</t>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 8:13 AM UTC</t>
+          <t>Apr 8, 2026 · 10:11 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-07T08:13:00Z</t>
+          <t>2026-04-08T10:11:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1310,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -1319,67 +1299,65 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2041418813942665225</t>
+          <t>2041821271319593215</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/NaserBadhafari/status/2041418813942665225</t>
+          <t>https://x.com/emiratesislamic/status/2041821271319593215</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/NaserBadhafari</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NaserBadhafari</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Naser Badhafari</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1757298769316499456/eJ3kGFuh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Applying for that credit card was a real quest! They really put me through the wringer with all the documents and steps. Just when I thought I was done, boom, more requirements popped up. It was a real test of patience, I'll tell you that much! Last time to apply in this bank.</t>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Applying for that credit card was a real quest! They really put me through the wringer with all the documents and steps. Just when I thought I was done, boom, more requirements popped up. It was a real test of patience, I&amp;#39;ll tell you that much! Last time to apply in this bank.</t>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 7, 2026 · 7:32 AM UTC</t>
+          <t>Apr 8, 2026 · 10:11 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-07T07:32:00Z</t>
+          <t>2026-04-08T10:11:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1391,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -1403,43 +1381,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2041403223161090324</t>
+          <t>2041818196261372116</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/Nauphal/status/2041403223161090324</t>
+          <t>https://x.com/emiratesislamic/status/2041818196261372116</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/Nauphal</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nauphal</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nauphal LLC SP</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>@emiratesislamic I was dealing with one of your finance advisors for some purpose since February. He is laid off recently and I am left with no point of contact and updates. He is not answering, not responding to messages, mails bouncing. No call back from customer care.</t>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I was dealing with one of your finance advisors for some purpose since February. He is laid off recently and I am left with no point of contact and updates. He is not answering, not responding to messages, mails bouncing. No call back from customer care.</t>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1449,36 +1429,1848 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 9:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:59:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2041803534602027153</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041803534602027153</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dear customer, it looks like your profile settings may be restricting us from sending you a direct message. To assist you further, please send us a DM or contact us via email at customercareunit@emiratesislamic.ae with your registered details, and we will be happy to support you</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dear customer, it looks like your profile settings may be restricting us from sending you a direct message. To assist you further, please send us a DM or contact us via email at customercareunit@emiratesislamic.ae with your registered details, and we will be happy to support you</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['Nauphal']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 9:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2041782777020829965</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041782777020829965</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['Renn_Stan_Lee']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 7:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-08T07:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2041760363436179910</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760363436179910</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apr 7, 2026 · 6:30 AM UTC</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-04-07T06:30:00Z</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2041760360621818126</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760360621818126</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2041760338308104592</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760338308104592</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2041760334214463800</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760334214463800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>استمتع بمعدلات ربح تنافسية مع تمويل السيارات من الإمارات الإسلامي.
+📊 معدلات ربح تبدأ من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+💳 برنامج الدفع الميسر %0 على نفقات البطاقة الائتمانية من الإمارات الإسلامي</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>استمتع بمعدلات ربح تنافسية مع تمويل السيارات من الإمارات الإسلامي.
+📊 معدلات ربح تبدأ من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+💳 برنامج الدفع الميسر %0 على نفقات البطاقة الائتمانية من الإمارات الإسلامي</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2041757946946666925</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757946946666925</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2041757945084453281</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757945084453281</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2041757941938725257</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757941938725257</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2041757939090829772</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757939090829772</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
+✔️ استرداد نقدي ومكافآت على مشترياتك
+✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
+✔️ استرداد نقدي ومكافآت على مشترياتك
+✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2041821273811034189</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041821273811034189</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 10:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-08T10:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2041809616133316853</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/Nauphal/status/2041809616133316853</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/Nauphal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nauphal</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nauphal LLC SP</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sent DM. Please respond.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sent DM. Please respond.</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 9:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2041770828887683094</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770828887683094</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I'm posting here because i don't have an option out, SM team please look into it.》》</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m posting here because i don&amp;#39;t have an option out, SM team please look into it.》》</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:51:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2041770661786612135</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770661786612135</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>@emiratesislamic also i was told that the money on hold is due to my end of service. Now they're changing the story. As a customer I'm going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; also i was told that the money on hold is due to my end of service. Now they&amp;#39;re changing the story. As a customer I&amp;#39;m going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2041770214564753782</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770214564753782</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>@emiratesislamic the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:48:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2041769750137864312</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041769750137864312</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I'm facing a terrible experience with EI. I've been contacting customer service back &amp; forth for the past 2 months for the end of service hold amount in my account. 
+I've been told that the hold amount would be released soon, even received an email mentioning《《</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m facing a terrible experience with EI. I&amp;#39;ve been contacting customer service back &amp;amp; forth for the past 2 months for the end of service hold amount in my account. 
+I&amp;#39;ve been told that the hold amount would be released soon, even received an email mentioning《《</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>58</v>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2041760363436179910</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760363436179910</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2041760338308104592</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760338308104592</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2041757946946666925</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757946946666925</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2041757945084453281</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757945084453281</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2041757941938725257</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757941938725257</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,43 +541,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2042436151131455658</t>
+          <t>2042482710841528699</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
+          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/Neli_Brown_</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neli_Brown_</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cornelia Brown 🇦🇪</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
+          <t>A message says “Get your full flight refund instantly.” What do you do?
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
+          <t>A message says “Get your full flight refund instantly.” What do you do?
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -592,18 +600,18 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 2:54 AM UTC</t>
+          <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-10T02:54:00Z</t>
+          <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -616,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -625,43 +633,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2042436151131455658</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/Neli_Brown_</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>Neli_Brown_</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>Cornelia Brown 🇦🇪</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -671,17 +679,17 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 7:38 AM UTC</t>
+          <t>Apr 10, 2026 · 2:54 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-09T07:38:00Z</t>
+          <t>2026-04-10T02:54:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -691,7 +699,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -700,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -709,73 +717,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2042152553400385940</t>
+          <t>2042145058133307907</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
+          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aswanikumartst5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>TS Aswani Kumar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 8:08 AM UTC</t>
+          <t>Apr 9, 2026 · 7:38 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-09T08:08:00Z</t>
+          <t>2026-04-09T07:38:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -784,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -793,84 +801,96 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2042120326721523923</t>
+          <t>2042184588223746449</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+          <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/HHShkMohd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>HHShkMohd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>HH Sheikh Mohammed</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1547632760927309837/9q-31iBH_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
+          <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
+علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
+فخورين بدولتنا .. فخورين برئيس دولتنا ..فخورين بقواتنا المسلحة .. فخورين بقوة اقتصادنا .. فخورين بفرق عملنا .. فخورين بجميع مواطنينا والمقيمين على أرضنا .. فخورين بعلمنا 🇦🇪.. 
+لنرفع العلم شامخاً فوق كل بيت ومبنى .. دليل محبتنا .. ورمز ولائنا لرئيس دولتنا.. وراية وحدتنا وتوحدنا .. 
+حفظ الله الإمارات وشعبها وأدام بالعز رايتها ومجدها ..
+#فخورين_بالإمارات 🇦🇪</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
+علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
+فخورين بدولتنا .. فخورين برئيس دولتنا ..فخورين بقواتنا المسلحة .. فخورين بقوة اقتصادنا .. فخورين بفرق عملنا .. فخورين بجميع مواطنينا والمقيمين على أرضنا .. فخورين بعلمنا 🇦🇪.. 
+لنرفع العلم شامخاً فوق كل بيت ومبنى .. دليل محبتنا .. ورمز ولائنا لرئيس دولتنا.. وراية وحدتنا وتوحدنا .. 
+حفظ الله الإمارات وشعبها وأدام بالعز رايتها ومجدها ..
+&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt; 🇦🇪</t>
         </is>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+          <t>Apr 9, 2026 · 10:15 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-09T06:00:00Z</t>
+          <t>2026-04-09T10:15:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1402</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>8020</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>15913</v>
       </c>
       <c r="V5" t="n">
-        <v>76</v>
+        <v>873259</v>
       </c>
     </row>
     <row r="6">
@@ -879,12 +899,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2042120323168956518</t>
+          <t>2042482711168737317</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042120323168956518</t>
+          <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -910,16 +930,22 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+          <t>تصلك رسالة تقول:
+"استرد قيمة رحلتك بالكامل فوراً"
+ماذا تفعل؟
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+          <t>تصلك رسالة تقول:
+&amp;#34;استرد قيمة رحلتك بالكامل فوراً&amp;#34;
+ماذا تفعل؟
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -929,23 +955,27 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+          <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-09T06:00:00Z</t>
+          <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -954,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -963,43 +993,51 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2042482710841528699</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
+          <t>A message says “Get your full flight refund instantly.” What do you do?
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>A message says “Get your full flight refund instantly.” What do you do?
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1009,27 +1047,27 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 7:38 AM UTC</t>
+          <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-09T07:38:00Z</t>
+          <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1038,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -1047,12 +1085,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2042120326721523923</t>
+          <t>2042152553400385940</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1078,53 +1116,391 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['aswanikumartst5']</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 8:08 AM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-09T08:08:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2042120326721523923</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>To know more:
 emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>To know more:
 &lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Apr 9</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-04-09T06:00:00Z</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>76</v>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2042120323168956518</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042120323168956518</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Apr 9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-04-09T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>aswanikumartst5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TS Aswani Kumar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 7:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-09T07:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2042120326721523923</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>To know more:
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>To know more:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Apr 9</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-09T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,36 +541,120 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2042482710841528699</t>
+          <t>2042799247435899272</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
+          <t>https://x.com/louder_tweet/status/2042799247435899272</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/louder_tweet</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>louder_tweet</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>أحب الله ثم أحب وطني</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/803607890540068864/vPQO0i-3_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Apr 11, 2026 · 2:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-04-11T02:57:00Z</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2042482710841528699</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -579,7 +663,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -588,90 +672,6 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-04-10T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2042436151131455658</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/Neli_Brown_</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Neli_Brown_</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Cornelia Brown 🇦🇪</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
-        </is>
-      </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
@@ -679,23 +679,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 2:54 AM UTC</t>
+          <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-10T02:54:00Z</t>
+          <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -717,43 +717,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2042436151131455658</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/Neli_Brown_</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>Neli_Brown_</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>Cornelia Brown 🇦🇪</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -763,17 +763,17 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Apr 10</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 7:38 AM UTC</t>
+          <t>Apr 10, 2026 · 2:54 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-09T07:38:00Z</t>
+          <t>2026-04-10T02:54:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -801,36 +801,568 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2042184588223746449</t>
+          <t>2042584000338759956</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
+          <t>https://x.com/emiratesislamic/status/2042584000338759956</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/HHShkMohd</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HHShkMohd</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HH Sheikh Mohammed</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1547632760927309837/9q-31iBH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-04-10T12:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2042583997671178679</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042583997671178679</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
+👍Get AED 500 guaranteed welcome bonus*
+💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp; education spends</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
+👍Get AED 500 guaranteed welcome bonus*
+💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp;amp; education spends</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-04-10T12:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2042583973210063105</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042583973210063105</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-04-10T12:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2042583969762279454</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042583969762279454</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
+👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
+💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
+👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
+💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-10T12:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2042549539198964217</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042549539198964217</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A nation united. A pride we all share. 🇦🇪
+In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
+Join this moment of pride. #ProudOfUAE</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>A nation united. A pride we all share. 🇦🇪
+In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
+Join this moment of pride. &lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 10:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-04-10T10:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2042549536732701083</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042549536732701083</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>وطنٌ يجمعنا. وفخرٌ نعيشه معاً. 🇦🇪
+انسجاماً مع دعوة صاحب السمو الشيخ محمد بن راشد آل مكتوم، لِنرفع علم دولة الإمارات عالياً ونعتز بروح الوحدة والقوة التي تميز وطننا.
+كن جزءاً من هذه اللحظة. #فخورين_بالٍامارات</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>وطنٌ يجمعنا. وفخرٌ نعيشه معاً. 🇦🇪
+انسجاماً مع دعوة صاحب السمو الشيخ محمد بن راشد آل مكتوم، لِنرفع علم دولة الإمارات عالياً ونعتز بروح الوحدة والقوة التي تميز وطننا.
+كن جزءاً من هذه اللحظة. &lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالٍامارات"&gt;#فخورين_بالٍامارات&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 10:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-04-10T10:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالٍامارات']</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2042184588223746449</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/HHShkMohd</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HHShkMohd</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HH Sheikh Mohammed</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1547632760927309837/9q-31iBH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
 علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
@@ -840,7 +1372,7 @@
 #فخورين_بالإمارات 🇦🇪</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
 علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
@@ -850,85 +1382,85 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt; 🇦🇪</t>
         </is>
       </c>
-      <c r="K5" t="b">
+      <c r="K11" t="b">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Apr 9</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 10:15 AM UTC</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2026-04-09T10:15:00Z</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>1402</v>
-      </c>
-      <c r="T5" t="n">
-        <v>8020</v>
-      </c>
-      <c r="U5" t="n">
-        <v>15913</v>
-      </c>
-      <c r="V5" t="n">
-        <v>873259</v>
+      <c r="S11" t="n">
+        <v>1523</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8458</v>
+      </c>
+      <c r="U11" t="n">
+        <v>17361</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1030679</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>2042482711168737317</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -938,7 +1470,7 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 &amp;#34;استرد قيمة رحلتك بالكامل فوراً&amp;#34;
@@ -948,81 +1480,81 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>60</v>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>99</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>2042482710841528699</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -1031,7 +1563,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -1040,467 +1572,319 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>39</v>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>79</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2042584000338759956</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042584000338759956</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 8:08 AM UTC</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-04-09T08:08:00Z</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>10</v>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-10T12:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>63</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2042120326721523923</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2042583973210063105</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042583973210063105</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Apr 9</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-04-09T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>86</v>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-10T12:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>78</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2042120323168956518</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042120323168956518</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2042549539198964217</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042549539198964217</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Apr 9</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-04-09T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>aswanikumartst5</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>TS Aswani Kumar</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 7:38 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-04-09T07:38:00Z</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2042120326721523923</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Apr 9</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-04-09T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>86</v>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>A nation united. A pride we all share. 🇦🇪
+In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
+Join this moment of pride. #ProudOfUAE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>A nation united. A pride we all share. 🇦🇪
+In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
+Join this moment of pride. &lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 10:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-10T10:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,54 +541,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2042799247435899272</t>
+          <t>2043160438330839389</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/louder_tweet/status/2042799247435899272</t>
+          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/louder_tweet</t>
+          <t>https://x.com/Charbel96960993</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>louder_tweet</t>
+          <t>Charbel96960993</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>أحب الله ثم أحب وطني</t>
+          <t>Charbel Helou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/803607890540068864/vPQO0i-3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
+          <t>@emiratesislamic 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>1h</t>
@@ -596,16 +594,20 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 11, 2026 · 2:57 AM UTC</t>
+          <t>Apr 12, 2026 · 2:53 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-11T02:57:00Z</t>
+          <t>2026-04-12T02:53:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -625,79 +627,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2042482710841528699</t>
+          <t>2042920052572213332</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
+          <t>https://x.com/meth_soltan/status/2042920052572213332</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/meth_soltan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>meth_soltan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>issa cheikh</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1871650861241278464/eE9Wved7_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>A message says “Get your full flight refund instantly.” What do you do?
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>خطوة زينة ومبشرة بالمزيد من النجاح</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A message says “Get your full flight refund instantly.” What do you do?
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>خطوة زينة ومبشرة بالمزيد من النجاح</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 6:00 AM UTC</t>
+          <t>Apr 11, 2026 · 10:57 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-10T06:00:00Z</t>
+          <t>2026-04-11T10:57:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -708,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -717,82 +711,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2042436151131455658</t>
+          <t>2042863824273879163</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
+          <t>https://x.com/towards_unit/status/2042863824273879163</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/Neli_Brown_</t>
+          <t>https://x.com/towards_unit</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neli_Brown_</t>
+          <t>towards_unit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cornelia Brown 🇦🇪</t>
+          <t>علي الرواحي</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1932396375217405952/I31kzAI__bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
+          <t>إنجاز مستحق الصراحة. القطاع المصرفي في الإمارات صار معيار بالمنطقة، ووجود 6 بنوك في تصنيف فوربس يبين قوة الاقتصاد. ومع التكامل بين عمان والإمارات الفرص التجارية والاستثمارية بتكبر أكثر.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
+          <t>إنجاز مستحق الصراحة. القطاع المصرفي في الإمارات صار معيار بالمنطقة، ووجود 6 بنوك في تصنيف فوربس يبين قوة الاقتصاد. ومع التكامل بين عمان والإمارات الفرص التجارية والاستثمارية بتكبر أكثر.</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Apr 10</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 2:54 AM UTC</t>
+          <t>Apr 11, 2026 · 7:14 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-10T02:54:00Z</t>
+          <t>2026-04-11T07:14:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -801,81 +795,71 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2042584000338759956</t>
+          <t>2042853514049917277</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042584000338759956</t>
+          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aswanikumartst5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>TS Aswani Kumar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp; conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+          <t>Apr 11, 2026 · 6:33 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-10T12:42:00Z</t>
+          <t>2026-04-11T06:33:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>0</v>
       </c>
@@ -886,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -895,73 +879,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2042583997671178679</t>
+          <t>2042799247435899272</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042583997671178679</t>
+          <t>https://x.com/louder_tweet/status/2042799247435899272</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/louder_tweet</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>louder_tweet</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>أحب الله ثم أحب وطني</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/803607890540068864/vPQO0i-3_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
-👍Get AED 500 guaranteed welcome bonus*
-💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp; education spends</t>
+          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
-👍Get AED 500 guaranteed welcome bonus*
-💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp;amp; education spends</t>
+          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>Apr 11</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+          <t>Apr 11, 2026 · 2:57 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-10T12:42:00Z</t>
+          <t>2026-04-11T02:57:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -970,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -979,53 +963,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2042583973210063105</t>
+          <t>2043160438330839389</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042583973210063105</t>
+          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Charbel96960993</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Charbel96960993</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Charbel Helou</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>@emiratesislamic 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1035,23 +1011,23 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+          <t>Apr 12, 2026 · 2:53 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-10T12:42:00Z</t>
+          <t>2026-04-12T02:53:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1064,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1073,818 +1049,82 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2042583969762279454</t>
+          <t>2042853514049917277</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042583969762279454</t>
+          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aswanikumartst5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>TS Aswani Kumar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
-👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
-💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
-👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
-💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 · 12:42 PM UTC</t>
+          <t>Apr 11, 2026 · 6:33 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-10T12:42:00Z</t>
+          <t>2026-04-11T06:33:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2042549539198964217</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042549539198964217</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. &lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 10:25 AM UTC</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-04-10T10:25:00Z</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2042549536732701083</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042549536732701083</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>وطنٌ يجمعنا. وفخرٌ نعيشه معاً. 🇦🇪
-انسجاماً مع دعوة صاحب السمو الشيخ محمد بن راشد آل مكتوم، لِنرفع علم دولة الإمارات عالياً ونعتز بروح الوحدة والقوة التي تميز وطننا.
-كن جزءاً من هذه اللحظة. #فخورين_بالٍامارات</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>وطنٌ يجمعنا. وفخرٌ نعيشه معاً. 🇦🇪
-انسجاماً مع دعوة صاحب السمو الشيخ محمد بن راشد آل مكتوم، لِنرفع علم دولة الإمارات عالياً ونعتز بروح الوحدة والقوة التي تميز وطننا.
-كن جزءاً من هذه اللحظة. &lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالٍامارات"&gt;#فخورين_بالٍامارات&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 10:25 AM UTC</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-04-10T10:25:00Z</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالٍامارات']</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2042184588223746449</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/HHShkMohd</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HHShkMohd</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>HH Sheikh Mohammed</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1547632760927309837/9q-31iBH_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
-علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
-فخورين بدولتنا .. فخورين برئيس دولتنا ..فخورين بقواتنا المسلحة .. فخورين بقوة اقتصادنا .. فخورين بفرق عملنا .. فخورين بجميع مواطنينا والمقيمين على أرضنا .. فخورين بعلمنا 🇦🇪.. 
-لنرفع العلم شامخاً فوق كل بيت ومبنى .. دليل محبتنا .. ورمز ولائنا لرئيس دولتنا.. وراية وحدتنا وتوحدنا .. 
-حفظ الله الإمارات وشعبها وأدام بالعز رايتها ومجدها ..
-#فخورين_بالإمارات 🇦🇪</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
-علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
-فخورين بدولتنا .. فخورين برئيس دولتنا ..فخورين بقواتنا المسلحة .. فخورين بقوة اقتصادنا .. فخورين بفرق عملنا .. فخورين بجميع مواطنينا والمقيمين على أرضنا .. فخورين بعلمنا 🇦🇪.. 
-لنرفع العلم شامخاً فوق كل بيت ومبنى .. دليل محبتنا .. ورمز ولائنا لرئيس دولتنا.. وراية وحدتنا وتوحدنا .. 
-حفظ الله الإمارات وشعبها وأدام بالعز رايتها ومجدها ..
-&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt; 🇦🇪</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Apr 9</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 10:15 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-04-09T10:15:00Z</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>1523</v>
-      </c>
-      <c r="T11" t="n">
-        <v>8458</v>
-      </c>
-      <c r="U11" t="n">
-        <v>17361</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1030679</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2042482711168737317</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>تصلك رسالة تقول:
-"استرد قيمة رحلتك بالكامل فوراً"
-ماذا تفعل؟
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>تصلك رسالة تقول:
-&amp;#34;استرد قيمة رحلتك بالكامل فوراً&amp;#34;
-ماذا تفعل؟
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-04-10T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2042482710841528699</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>A message says “Get your full flight refund instantly.” What do you do?
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>A message says “Get your full flight refund instantly.” What do you do?
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2026-04-10T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2042584000338759956</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042584000338759956</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp; conditions apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 12:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2026-04-10T12:42:00Z</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2042583973210063105</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042583973210063105</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 12:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2026-04-10T12:42:00Z</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2042549539198964217</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042549539198964217</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. &lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 10:25 AM UTC</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2026-04-10T10:25:00Z</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,45 +541,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2043160438330839389</t>
+          <t>2043207487977918492</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
+          <t>https://x.com/emiratesislamic/status/2043207487977918492</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/Charbel96960993</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Charbel96960993</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Charbel Helou</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>Seeing progress keeps you going.
+💡 Tip:
+Track what you’ve paid off not just what’s left
+It keeps motivation high.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>Seeing progress keeps you going.
+💡 Tip:
+Track what you’ve paid off not just what’s left
+It keeps motivation high.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -589,23 +597,23 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 12, 2026 · 2:53 AM UTC</t>
+          <t>Apr 12, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-12T02:53:00Z</t>
+          <t>2026-04-12T06:00:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -618,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -627,71 +635,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2042920052572213332</t>
+          <t>2043160438330839389</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/meth_soltan/status/2042920052572213332</t>
+          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/meth_soltan</t>
+          <t>https://x.com/Charbel96960993</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>meth_soltan</t>
+          <t>Charbel96960993</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>issa cheikh</t>
+          <t>Charbel Helou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1871650861241278464/eE9Wved7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>خطوة زينة ومبشرة بالمزيد من النجاح</t>
+          <t>@emiratesislamic 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>خطوة زينة ومبشرة بالمزيد من النجاح</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 11, 2026 · 10:57 AM UTC</t>
+          <t>Apr 12, 2026 · 2:53 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-11T10:57:00Z</t>
+          <t>2026-04-12T02:53:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -702,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -711,54 +721,60 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2042863824273879163</t>
+          <t>2043207487977918492</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/towards_unit/status/2042863824273879163</t>
+          <t>https://x.com/emiratesislamic/status/2043207487977918492</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/towards_unit</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>towards_unit</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>علي الرواحي</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1932396375217405952/I31kzAI__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>إنجاز مستحق الصراحة. القطاع المصرفي في الإمارات صار معيار بالمنطقة، ووجود 6 بنوك في تصنيف فوربس يبين قوة الاقتصاد. ومع التكامل بين عمان والإمارات الفرص التجارية والاستثمارية بتكبر أكثر.</t>
+          <t>Seeing progress keeps you going.
+💡 Tip:
+Track what you’ve paid off not just what’s left
+It keeps motivation high.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>إنجاز مستحق الصراحة. القطاع المصرفي في الإمارات صار معيار بالمنطقة، ووجود 6 بنوك في تصنيف فوربس يبين قوة الاقتصاد. ومع التكامل بين عمان والإمارات الفرص التجارية والاستثمارية بتكبر أكثر.</t>
+          <t>Seeing progress keeps you going.
+💡 Tip:
+Track what you’ve paid off not just what’s left
+It keeps motivation high.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>20h</t>
@@ -766,16 +782,20 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 11, 2026 · 7:14 AM UTC</t>
+          <t>Apr 12, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-11T07:14:00Z</t>
+          <t>2026-04-12T06:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -786,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -795,71 +815,79 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2042853514049917277</t>
+          <t>2043207487927554424</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
+          <t>https://x.com/emiratesislamic/status/2043207487927554424</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
+          <t>رؤية خطواتك تتقدم تحفّزك على الاستمرار.
+💡نصيحة: تابع ما قمت بسداده، وليس فقط ما تبقّى.
+الإنجاز البسيط يمنحك دافعاً أكبر للاستمرار.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
+          <t>رؤية خطواتك تتقدم تحفّزك على الاستمرار.
+💡نصيحة: تابع ما قمت بسداده، وليس فقط ما تبقّى.
+الإنجاز البسيط يمنحك دافعاً أكبر للاستمرار.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 11, 2026 · 6:33 AM UTC</t>
+          <t>Apr 12, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-11T06:33:00Z</t>
+          <t>2026-04-12T06:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
@@ -870,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -879,252 +907,84 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2042799247435899272</t>
+          <t>2043160438330839389</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/louder_tweet/status/2042799247435899272</t>
+          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/louder_tweet</t>
+          <t>https://x.com/Charbel96960993</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>louder_tweet</t>
+          <t>Charbel96960993</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>أحب الله ثم أحب وطني</t>
+          <t>Charbel Helou</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/803607890540068864/vPQO0i-3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>اللهم بارك لهذه الدولة الحمدلله على فضله وجوده</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['Forsan_UAE', 'FABConnects', 'OfficialADCB', 'EmiratesNBD_AE', 'emiratesislamic', 'CBDUAE']</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Apr 11</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Apr 11, 2026 · 2:57 AM UTC</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-04-11T02:57:00Z</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2043160438330839389</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/Charbel96960993</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Charbel96960993</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Charbel Helou</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
           <t>@emiratesislamic 
 تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
 تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Apr 12, 2026 · 2:53 AM UTC</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-04-12T02:53:00Z</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2042853514049917277</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>aswanikumartst5</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TS Aswani Kumar</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>So far nobody has contacted me in connection with this query nor any mail from your end .</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Apr 11, 2026 · 6:33 AM UTC</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-04-11T06:33:00Z</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,83 +541,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2043207487977918492</t>
+          <t>2043618934671208880</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043207487977918492</t>
+          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Mohadsaleem89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mohadsaleem89</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mohd Saleem</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1026443277493575680/Tn_rrbBC_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Seeing progress keeps you going.
-💡 Tip:
-Track what you’ve paid off not just what’s left
-It keeps motivation high.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Seeing progress keeps you going.
-💡 Tip:
-Track what you’ve paid off not just what’s left
-It keeps motivation high.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 12, 2026 · 6:00 AM UTC</t>
+          <t>Apr 13, 2026 · 9:14 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-12T06:00:00Z</t>
+          <t>2026-04-13T09:14:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -626,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -635,45 +625,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2043160438330839389</t>
+          <t>2043569881270951992</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
+          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/Charbel96960993</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Charbel96960993</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Charbel Helou</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -683,27 +673,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 12, 2026 · 2:53 AM UTC</t>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-12T02:53:00Z</t>
+          <t>2026-04-13T06:00:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -712,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -721,12 +707,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2043207487977918492</t>
+          <t>2043569875726053574</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043207487977918492</t>
+          <t>https://x.com/emiratesislamic/status/2043569875726053574</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -752,22 +738,20 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Seeing progress keeps you going.
-💡 Tip:
-Track what you’ve paid off not just what’s left
-It keeps motivation high.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Would you click a delivery link from an unknown number?
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Seeing progress keeps you going.
-💡 Tip:
-Track what you’ve paid off not just what’s left
-It keeps motivation high.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Would you click a delivery link from an unknown number?
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -777,23 +761,23 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 12, 2026 · 6:00 AM UTC</t>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-12T06:00:00Z</t>
+          <t>2026-04-13T06:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -806,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -815,77 +799,81 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2043207487927554424</t>
+          <t>2043524253220569256</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043207487927554424</t>
+          <t>https://x.com/centralbankuae/status/2043524253220569256</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/centralbankuae</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>centralbankuae</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Central Bank of the UAE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>رؤية خطواتك تتقدم تحفّزك على الاستمرار.
-💡نصيحة: تابع ما قمت بسداده، وليس فقط ما تبقّى.
-الإنجاز البسيط يمنحك دافعاً أكبر للاستمرار.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>رؤية خطواتك تتقدم تحفّزك على الاستمرار.
-💡نصيحة: تابع ما قمت بسداده، وليس فقط ما تبقّى.
-الإنجاز البسيط يمنحك دافعاً أكبر للاستمرار.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['altamashhkhann', 'amazon', 'AmazonHelp', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 13</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 12, 2026 · 6:00 AM UTC</t>
+          <t>Apr 13, 2026 · 2:58 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-12T06:00:00Z</t>
+          <t>2026-04-13T02:58:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -898,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>91</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -907,73 +895,71 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2043160438330839389</t>
+          <t>2043657206629851210</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/Charbel96960993/status/2043160438330839389</t>
+          <t>https://x.com/emiratesislamic/status/2043657206629851210</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/Charbel96960993</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Charbel96960993</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charbel Helou</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['Mohadsaleem89']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 12, 2026 · 2:53 AM UTC</t>
+          <t>Apr 13, 2026 · 11:47 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-12T02:53:00Z</t>
+          <t>2026-04-13T11:47:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -985,6 +971,1372 @@
       </c>
       <c r="V6" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2043657059342643303</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043657059342643303</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['Mohadsaleem89']</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 11:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-04-13T11:46:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2043620884234096765</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043620884234096765</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['Charbel96960993']</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 9:22 AM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-13T09:22:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2043620711407743228</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043620711407743228</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['Charbel96960993']</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 9:22 AM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-04-13T09:22:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2043579224183722461</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043579224183722461</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['altamashhkhann']</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:37 AM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:37:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2043579137785217188</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043579137785217188</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['altamashhkhann']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2043569882944454660</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569882944454660</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
+Start them young!
+To know more visit emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
+Start them young!
+To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2043569881270951992</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2043569879236678057</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569879236678057</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>علمهم صغار!
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>علمهم صغار!
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2043569875763826695</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569875763826695</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2043569875734401177</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569875734401177</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>هل ستضغط على رابط توصيل من رقم غير معروف؟ 
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>هل ستضغط على رابط توصيل من رقم غير معروف؟ 
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2043569875726053574</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569875726053574</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Would you click a delivery link from an unknown number?
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Would you click a delivery link from an unknown number?
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2043560931511189651</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['aswanikumartst5']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 5:24 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-13T05:24:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2043618934671208880</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/Mohadsaleem89</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mohadsaleem89</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mohd Saleem</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1026443277493575680/Tn_rrbBC_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 9:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-13T09:14:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2043569882944454660</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569882944454660</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
+Start them young!
+To know more visit emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
+Start them young!
+To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2043569881270951992</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2043569879236678057</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569879236678057</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>علمهم صغار!
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>علمهم صغار!
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,73 +541,75 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2043618934671208880</t>
+          <t>2044143965486948528</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
+          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/Mohadsaleem89</t>
+          <t>https://x.com/GidwaniHero</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mohadsaleem89</t>
+          <t>GidwaniHero</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mohd Saleem</t>
+          <t>Hero Gidwani</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1026443277493575680/Tn_rrbBC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1924556859526283267/UcvezR38_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
+Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+          <t>&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; &lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
+Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 9:14 AM UTC</t>
+          <t>Apr 14, 2026 · 8:01 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-13T09:14:00Z</t>
+          <t>2026-04-14T20:01:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/HHShkMohd', 'https://x.com/ENBDdeals', 'https://x.com/FABConnects', 'https://x.com/MashreqTweets', 'https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -616,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -625,45 +627,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2043569881270951992</t>
+          <t>2044011613422834071</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
+          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/ZaharaMMalik</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ZaharaMMalik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Zahara Sadiq</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1123139785072304129/0KaXZD52_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+          <t>Really struggling to get hold of &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -673,21 +673,25 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+          <t>Apr 14, 2026 · 11:15 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-13T06:00:00Z</t>
+          <t>2026-04-14T11:15:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
@@ -695,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -707,81 +711,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2043569875726053574</t>
+          <t>2043951228640747823</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569875726053574</t>
+          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aswanikumartst5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>TS Aswani Kumar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Would you click a delivery link from an unknown number?
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Would you click a delivery link from an unknown number?
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+          <t>Apr 14, 2026 · 7:15 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-13T06:00:00Z</t>
+          <t>2026-04-14T07:15:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -790,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -799,81 +795,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2043524253220569256</t>
+          <t>2043932263390310621</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae/status/2043524253220569256</t>
+          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>centralbankuae</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Central Bank of the UAE</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>How do you usually pay for your expenses?
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
-Best regards,
-Central Bank of the UAE</t>
+          <t>How do you usually pay for your expenses?
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['altamashhkhann', 'amazon', 'AmazonHelp', 'emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Apr 13</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 2:58 AM UTC</t>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-13T02:58:00Z</t>
+          <t>2026-04-14T06:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -886,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -895,12 +883,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2043657206629851210</t>
+          <t>2043917165502316982</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043657206629851210</t>
+          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -926,40 +914,46 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+Your Weekly Perspective. A step toward a more mindful financial week.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+Your Weekly Perspective. A step toward a more mindful financial week.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['Mohadsaleem89']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 11:47 AM UTC</t>
+          <t>Apr 14, 2026 · 5:00 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-13T11:47:00Z</t>
+          <t>2026-04-14T05:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -970,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -979,12 +973,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2043657059342643303</t>
+          <t>2044023053797953761</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043657059342643303</t>
+          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1010,12 +1004,12 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1024,22 +1018,22 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>['Mohadsaleem89']</t>
+          <t>['ZaharaMMalik']</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 11:46 AM UTC</t>
+          <t>Apr 14, 2026 · 12:00 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-13T11:46:00Z</t>
+          <t>2026-04-14T12:00:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1054,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -1063,12 +1057,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2043620884234096765</t>
+          <t>2043955058459467807</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043620884234096765</t>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1094,12 +1088,12 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1108,22 +1102,22 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['Charbel96960993']</t>
+          <t>['aswanikumartst5']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 9:22 AM UTC</t>
+          <t>Apr 14, 2026 · 7:30 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-13T09:22:00Z</t>
+          <t>2026-04-14T07:30:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1138,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1147,12 +1141,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2043620711407743228</t>
+          <t>2043932266456367150</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043620711407743228</t>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1178,40 +1172,42 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>To know more:
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>To know more:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['Charbel96960993']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 9:22 AM UTC</t>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-13T09:22:00Z</t>
+          <t>2026-04-14T06:00:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1222,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -1231,12 +1227,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043579224183722461</t>
+          <t>2043932263725854816</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043579224183722461</t>
+          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1262,42 +1258,42 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['altamashhkhann']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:37 AM UTC</t>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-13T06:37:00Z</t>
+          <t>2026-04-14T06:00:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1306,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -1315,12 +1311,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043579137785217188</t>
+          <t>2043932263449006494</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043579137785217188</t>
+          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1346,40 +1342,44 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>كيف تدفع نفقاتك عادةً؟
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['altamashhkhann']</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:36 AM UTC</t>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-13T06:36:00Z</t>
+          <t>2026-04-14T06:00:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043569882944454660</t>
+          <t>2043932263390310621</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569882944454660</t>
+          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1430,16 +1430,16 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
-Start them young!
-To know more visit emiratesislamic.ae/en/Person…</t>
+          <t>How do you usually pay for your expenses?
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
-Start them young!
-To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>How do you usually pay for your expenses?
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1449,23 +1449,23 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-13T06:00:00Z</t>
+          <t>2026-04-14T06:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043569881270951992</t>
+          <t>2043932263386157239</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1518,14 +1518,20 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
+تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
+خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
+للمزيد: 
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
+          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
+تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
+خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
+للمزيد: 
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1535,23 +1541,27 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-13T06:00:00Z</t>
+          <t>2026-04-14T06:00:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1560,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -1569,12 +1579,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2043569879236678057</t>
+          <t>2043917165502316982</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569879236678057</t>
+          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1600,16 +1610,18 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+Your Weekly Perspective. A step toward a more mindful financial week.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+Your Weekly Perspective. A step toward a more mindful financial week.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1619,27 +1631,27 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+          <t>Apr 14, 2026 · 5:00 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-13T06:00:00Z</t>
+          <t>2026-04-14T05:00:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1648,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -1657,69 +1669,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043569875763826695</t>
+          <t>2043951228640747823</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569875763826695</t>
+          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aswanikumartst5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>TS Aswani Kumar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
+          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
+          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+          <t>Apr 14, 2026 · 7:15 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-13T06:00:00Z</t>
+          <t>2026-04-14T07:15:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1728,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1737,12 +1753,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2043569875734401177</t>
+          <t>2043932266456367150</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569875734401177</t>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1768,18 +1784,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>هل ستضغط على رابط توصيل من رقم غير معروف؟ 
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
+          <t>To know more:
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>هل ستضغط على رابط توصيل من رقم غير معروف؟ 
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>To know more:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1789,23 +1801,23 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-13T06:00:00Z</t>
+          <t>2026-04-14T06:00:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -1818,525 +1830,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2043569875726053574</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043569875726053574</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Would you click a delivery link from an unknown number?
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Would you click a delivery link from an unknown number?
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2026-04-13T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 5:24 AM UTC</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2026-04-13T05:24:00Z</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2043618934671208880</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/Mohadsaleem89</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Mohadsaleem89</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mohd Saleem</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1026443277493575680/Tn_rrbBC_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 9:14 AM UTC</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2026-04-13T09:14:00Z</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2043569882944454660</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043569882944454660</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
-Start them young!
-To know more visit emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Accessible through the EI + Mobile App, it’s a simple way to give your child a confident start.
-Start them young!
-To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-04-13T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2043569881270951992</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-04-13T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2043569879236678057</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043569879236678057</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-04-13T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,45 +541,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GidwaniHero</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hero Gidwani</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1924556859526283267/UcvezR38_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  arabianbusiness.com/finance/…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; &lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  &lt;a href="https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers"&gt;arabianbusiness.com/finance/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -589,23 +587,23 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 8:01 PM UTC</t>
+          <t>Apr 15, 2026 · 4:07 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-14T20:01:00Z</t>
+          <t>2026-04-15T16:07:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://x.com/HHShkMohd', 'https://x.com/ENBDdeals', 'https://x.com/FABConnects', 'https://x.com/MashreqTweets', 'https://x.com/emiratesislamic']</t>
+          <t>['https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -618,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -627,43 +625,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik</t>
+          <t>https://x.com/EntAlArabiya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ZaharaMMalik</t>
+          <t>EntAlArabiya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zahara Sadiq</t>
+          <t>Entrepreneur العربية</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1123139785072304129/0KaXZD52_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514308412343033862/Cl9tt_tx_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+entrepreneuralarabiya.com/20…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنوك"&gt;#بنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شركات"&gt;#شركات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مشاريع_صغيرة"&gt;#مشاريع_صغيرة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23اقتصاد"&gt;#اقتصاد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نمو"&gt;#نمو&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23entalarabiya"&gt;#entalarabiya&lt;/a&gt;
+&lt;a href="https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/"&gt;entrepreneuralarabiya.com/20…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -673,36 +675,36 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 11:15 AM UTC</t>
+          <t>Apr 15, 2026 · 9:05 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-14T11:15:00Z</t>
+          <t>2026-04-15T09:05:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23بنوك', 'https://x.com/search?f=tweets&amp;q=%23شركات', 'https://x.com/search?f=tweets&amp;q=%23مشاريع_صغيرة', 'https://x.com/search?f=tweets&amp;q=%23تمويل', 'https://x.com/search?f=tweets&amp;q=%23اقتصاد', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23نمو', 'https://x.com/search?f=tweets&amp;q=%23entalarabiya', 'https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/']</t>
         </is>
       </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -711,82 +713,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/dcgguide</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>dcgguide</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign blog.dubaicityguide.com/site…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign &lt;a href="https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:15 AM UTC</t>
+          <t>Apr 15, 2026 · 9:02 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-14T07:15:00Z</t>
+          <t>2026-04-15T09:02:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -795,47 +797,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/EntMagazineME</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EntMagazineME</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Entrepreneur Middle East</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514494189895049219/SrZOixX4_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: mena.entrepreneur.com/busine…</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening &lt;a href="/search?f=tweets&amp;amp;q=%23business"&gt;#business&lt;/a&gt; resilience across the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: &lt;a href="https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes"&gt;mena.entrepreneur.com/busine…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -850,31 +854,31 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:11:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23business', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes']</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -883,12 +887,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2043917165502316982</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -914,18 +918,20 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -935,23 +941,23 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 5:00 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-14T05:00:00Z</t>
+          <t>2026-04-15T06:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -964,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>56</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -973,12 +979,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044023053797953761</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1004,40 +1010,50 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['ZaharaMMalik']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:00 PM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-14T12:00:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1048,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>65</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
@@ -1057,12 +1073,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2043955058459467807</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1088,51 +1104,49 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:30 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-14T07:30:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
@@ -1141,12 +1155,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2043932266456367150</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1172,14 +1186,20 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1189,23 +1209,23 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1218,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -1227,12 +1247,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043932263725854816</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1258,16 +1278,16 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1277,17 +1297,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1302,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -1311,12 +1331,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1342,16 +1362,18 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1366,18 +1388,18 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1390,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>73</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -1399,12 +1421,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1430,16 +1452,16 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1454,31 +1476,27 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>49</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -1487,12 +1505,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043932263386157239</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1518,20 +1536,18 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1546,18 +1562,18 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1570,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -1579,12 +1595,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2043917165502316982</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1610,18 +1626,18 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1631,36 +1647,32 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 5:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-14T05:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>56</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -1669,73 +1681,81 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:15 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-14T07:15:00Z</t>
+          <t>2026-04-15T06:00:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1744,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1753,12 +1773,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2043932266456367150</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1784,14 +1804,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1801,27 +1821,27 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T06:00:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1830,7 +1850,725 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>71</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2044294653097156714</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-15T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2044471342880170391</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-15T17:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2044471329382900119</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-15T17:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2044322414310367621</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-15T07:50:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2044322403761697193</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-15T07:50:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2044312732879728677</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/EntMagazineME</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EntMagazineME</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Entrepreneur Middle East</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1514494189895049219/SrZOixX4_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: mena.entrepreneur.com/busine…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening &lt;a href="/search?f=tweets&amp;amp;q=%23business"&gt;#business&lt;/a&gt; resilience across the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: &lt;a href="https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes"&gt;mena.entrepreneur.com/busine…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 7:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-15T07:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23business', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2044294659795513346</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-15T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2044294656716836969</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-15T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,71 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2044447495619547616</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas</t>
+          <t>https://x.com/RakeshMavath</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>gold_hadas</t>
+          <t>RakeshMavath</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nicholas MOLODYKO, writer</t>
+          <t>Rakesh Mavath</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2013866142125957122/nsrKPIws_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Emirates Islamic launches AED1m campaign for SME customers  arabianbusiness.com/finance/…</t>
+          <t>Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Emirates Islamic launches AED1m campaign for SME customers  &lt;a href="https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers"&gt;arabianbusiness.com/finance/…&lt;/a&gt;</t>
+          <t>Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['aaditsh', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 4:07 PM UTC</t>
+          <t>Apr 16, 2026 · 5:38 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-15T16:07:00Z</t>
+          <t>2026-04-16T17:38:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -625,86 +625,84 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2044341445717610661</t>
+          <t>2044805287459398125</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
+          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/EntAlArabiya</t>
+          <t>https://x.com/1ss9490ss1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EntAlArabiya</t>
+          <t>1ss9490ss1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entrepreneur العربية</t>
+          <t>بوالسلطان</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1514308412343033862/Cl9tt_tx_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/777077466515079168/MKR49yEx_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
-#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
-entrepreneuralarabiya.com/20…</t>
+          <t>السلام عليكم ورحمه الله وبركاته 
+الرجاء التواصل بي باحد من خدمة العملاء.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  يعزز قطاع الأعمال بحملة للشركات الصغيرة
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنوك"&gt;#بنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شركات"&gt;#شركات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مشاريع_صغيرة"&gt;#مشاريع_صغيرة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23اقتصاد"&gt;#اقتصاد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نمو"&gt;#نمو&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23entalarabiya"&gt;#entalarabiya&lt;/a&gt;
-&lt;a href="https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/"&gt;entrepreneuralarabiya.com/20…&lt;/a&gt;</t>
+          <t>السلام عليكم ورحمه الله وبركاته 
+الرجاء التواصل بي باحد من خدمة العملاء.</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 9:05 AM UTC</t>
+          <t>Apr 16, 2026 · 3:49 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-15T09:05:00Z</t>
+          <t>2026-04-16T15:49:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23بنوك', 'https://x.com/search?f=tweets&amp;q=%23شركات', 'https://x.com/search?f=tweets&amp;q=%23مشاريع_صغيرة', 'https://x.com/search?f=tweets&amp;q=%23تمويل', 'https://x.com/search?f=tweets&amp;q=%23اقتصاد', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23نمو', 'https://x.com/search?f=tweets&amp;q=%23entalarabiya', 'https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -713,71 +711,71 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2044340590037655768</t>
+          <t>2044784107352445179</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044340590037655768</t>
+          <t>https://x.com/aaditsh/status/2044784107352445179</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign blog.dubaicityguide.com/site…</t>
+          <t>Just unacceptable. They just auto-charge you without your permission?</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign &lt;a href="https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+          <t>Just unacceptable. They just auto-charge you without your permission?</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['huss23', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 9:02 AM UTC</t>
+          <t>Apr 16, 2026 · 2:24 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-15T09:02:00Z</t>
+          <t>2026-04-16T14:24:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -785,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -797,88 +795,86 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2044312732879728677</t>
+          <t>2044781883184316706</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME</t>
+          <t>https://x.com/huss23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EntMagazineME</t>
+          <t>huss23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entrepreneur Middle East</t>
+          <t>Huss</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1514494189895049219/SrZOixX4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2691682144/840d131cc8397f1c15b0a611bec833b2_bigger.png</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
-Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
-The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
-🔗Read more HERE: mena.entrepreneur.com/busine…</t>
+          <t>I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening &lt;a href="/search?f=tweets&amp;amp;q=%23business"&gt;#business&lt;/a&gt; resilience across the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;.
-Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
-The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
-🔗Read more HERE: &lt;a href="https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes"&gt;mena.entrepreneur.com/busine…&lt;/a&gt;</t>
+          <t>I had the same issue. &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['aaditsh']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:11 AM UTC</t>
+          <t>Apr 16, 2026 · 2:16 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-15T07:11:00Z</t>
+          <t>2026-04-16T14:16:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23business', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -887,90 +883,84 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044759599656689929</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-emiratesislamic.ae/en/Person…</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['RakeshMavath', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+          <t>Apr 16, 2026 · 12:47 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-15T06:00:00Z</t>
+          <t>2026-04-16T12:47:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
@@ -979,92 +969,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044471342880170391</t>
+          <t>2044758862017007662</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/RakeshMavath</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>RakeshMavath</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Rakesh Mavath</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2013866142125957122/nsrKPIws_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
-الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
-الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['aaditsh', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+          <t>Apr 16, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-15T17:42:00Z</t>
+          <t>2026-04-16T12:44:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8">
@@ -1073,45 +1053,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1121,32 +1103,36 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+          <t>Apr 16, 2026 · 10:59 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-15T17:42:00Z</t>
+          <t>2026-04-16T10:59:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>147</v>
+        <v>5653</v>
       </c>
     </row>
     <row r="9">
@@ -1155,12 +1141,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2044471329382900119</t>
+          <t>2044717394669502695</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1186,20 +1172,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Second cash prize: AED 100,000 each (2 winners)
-Monthly cash prizes: up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Second cash prize: AED 100,000 each (2 winners)
-Monthly cash prizes: up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1209,27 +1189,23 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-15T17:42:00Z</t>
+          <t>2026-04-16T09:59:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1238,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>73</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -1247,47 +1223,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044704123199554019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
+          <t>https://x.com/startupsceneme/status/2044704123199554019</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/startupsceneme</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>startupsceneme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Startup Scene ME</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1221420632044462085/G_yAYsR8_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
-55 businesses will be winners. Will you be one of them?
-Grand cash prize: AED 250,000 (1 winner)</t>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
+thestartupscene.me/OPPORTUNI…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
-55 businesses will be winners. Will you be one of them?
-Grand cash prize: AED 250,000 (1 winner)</t>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
+&lt;a href="https://thestartupscene.me/OPPORTUNITIES/Emirates-Islamic-Bank-Launches-AED-1M-Campaign-for-SMEs"&gt;thestartupscene.me/OPPORTUNI…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1297,32 +1271,36 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+          <t>Apr 16, 2026 · 9:07 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-15T17:42:00Z</t>
+          <t>2026-04-16T09:07:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://thestartupscene.me/OPPORTUNITIES/Emirates-Islamic-Bank-Launches-AED-1M-Campaign-for-SMEs']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -1331,12 +1309,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2044322414310367621</t>
+          <t>2044701412848705623</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1362,18 +1340,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-emiratesislamic.ae/en/person…</t>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+#SME #businessbanking #emiratesislamic</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+&lt;a href="/search?f=tweets&amp;amp;q=%23SME"&gt;#SME&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23businessbanking"&gt;#businessbanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1383,23 +1357,23 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+          <t>Apr 16, 2026 · 8:56 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-15T07:50:00Z</t>
+          <t>2026-04-16T08:56:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23SME', 'https://x.com/search?f=tweets&amp;q=%23businessbanking', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1412,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>142</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -1421,12 +1395,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044657039872237722</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
+          <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1452,16 +1426,20 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
-⭐️Shariah-compliant offering</t>
+          <t>You don’t have a spending problem, you have invisible spending.
+Track what feels “too small to matter.”
+Because that’s usually where your money goes.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…"</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
-⭐️Shariah-compliant offering</t>
+          <t>You don’t have a spending problem, you have invisible spending.
+Track what feels “too small to matter.”
+Because that’s usually where your money goes.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;&amp;#34;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1476,27 +1454,31 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+          <t>Apr 16, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-15T07:50:00Z</t>
+          <t>2026-04-16T06:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>204</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -1505,12 +1487,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2044322403761697193</t>
+          <t>2044836542028320968</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
+          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1536,18 +1518,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/person…</t>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1557,25 +1535,21 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+          <t>Apr 16, 2026 · 5:53 PM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-15T07:50:00Z</t>
+          <t>2026-04-16T17:53:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -1586,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1595,12 +1569,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044836538958200892</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1626,18 +1600,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً.</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1647,17 +1617,17 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+          <t>Apr 16, 2026 · 5:53 PM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-15T07:50:00Z</t>
+          <t>2026-04-16T17:53:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -1669,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>201</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1681,12 +1651,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044734739718824109</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1712,48 +1682,40 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-emiratesislamic.ae/en/Person…</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+          <t>Apr 16, 2026 · 11:08 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-15T06:00:00Z</t>
+          <t>2026-04-16T11:08:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -1764,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1773,12 +1735,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044717396758303206</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1804,14 +1766,20 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
-emiratesislamic.ae/ar/Person…</t>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp; Conditions apply
+emiratesislamic.ae/en/accoun…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp;amp; Conditions apply
+&lt;a href="https://www.emiratesislamic.ae/en/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad_guest_account"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1821,27 +1789,27 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-15T06:00:00Z</t>
+          <t>2026-04-16T09:59:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+          <t>['https://www.emiratesislamic.ae/en/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad_guest_account']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1850,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17">
@@ -1859,12 +1827,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044717394669502695</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1890,16 +1858,14 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>من “يوماً ما” إلى يوم الانتقال!
-التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
-استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>من “يوماً ما” إلى يوم الانتقال!
-التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
-استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1909,23 +1875,23 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-15T06:00:00Z</t>
+          <t>2026-04-16T09:59:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1934,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>194</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18">
@@ -1943,12 +1909,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2044471342880170391</t>
+          <t>2044717367842816367</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
+          <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1974,22 +1940,20 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
-الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/accoun…</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
-الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+&lt;a href="https://www.emiratesislamic.ae/ar/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad_guest_account"&gt;emiratesislamic.ae/ar/accoun…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -1999,23 +1963,23 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-15T17:42:00Z</t>
+          <t>2026-04-16T09:59:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+          <t>['https://www.emiratesislamic.ae/ar/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad_guest_account']</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2028,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>147</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -2037,12 +2001,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2044471329382900119</t>
+          <t>2044717365380739467</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2068,20 +2032,14 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Second cash prize: AED 100,000 each (2 winners)
-Monthly cash prizes: up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Second cash prize: AED 100,000 each (2 winners)
-Monthly cash prizes: up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2091,36 +2049,32 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 5:42 PM UTC</t>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-15T17:42:00Z</t>
+          <t>2026-04-16T09:59:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
@@ -2129,12 +2083,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2044322414310367621</t>
+          <t>2044701412848705623</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2160,18 +2114,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-emiratesislamic.ae/en/person…</t>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+#SME #businessbanking #emiratesislamic</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+&lt;a href="/search?f=tweets&amp;amp;q=%23SME"&gt;#SME&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23businessbanking"&gt;#businessbanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2181,23 +2131,23 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+          <t>Apr 16, 2026 · 8:56 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-15T07:50:00Z</t>
+          <t>2026-04-16T08:56:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23SME', 'https://x.com/search?f=tweets&amp;q=%23businessbanking', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2210,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>142</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -2219,12 +2169,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2044322403761697193</t>
+          <t>2044701403591983546</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
+          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2250,18 +2200,16 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/person…</t>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم.</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2271,27 +2219,23 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:50 AM UTC</t>
+          <t>Apr 16, 2026 · 8:56 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-15T07:50:00Z</t>
+          <t>2026-04-16T08:56:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2300,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22">
@@ -2309,49 +2253,51 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2044312732879728677</t>
+          <t>2044657039872237722</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
+          <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EntMagazineME</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Entrepreneur Middle East</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1514494189895049219/SrZOixX4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
-Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
-The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
-🔗Read more HERE: mena.entrepreneur.com/busine…</t>
+          <t>You don’t have a spending problem, you have invisible spending.
+Track what feels “too small to matter.”
+Because that’s usually where your money goes.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…"</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening &lt;a href="/search?f=tweets&amp;amp;q=%23business"&gt;#business&lt;/a&gt; resilience across the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;.
-Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
-The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
-🔗Read more HERE: &lt;a href="https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes"&gt;mena.entrepreneur.com/busine…&lt;/a&gt;</t>
+          <t>You don’t have a spending problem, you have invisible spending.
+Track what feels “too small to matter.”
+Because that’s usually where your money goes.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;&amp;#34;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2366,31 +2312,31 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 7:11 AM UTC</t>
+          <t>Apr 16, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-15T07:11:00Z</t>
+          <t>2026-04-16T06:00:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23business', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -2399,12 +2345,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044657039859757511</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2430,20 +2376,18 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-emiratesislamic.ae/en/Person…</t>
+          <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
+فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
+فالمبالغ الصغيرة التي نظنها &amp;#34;غير مهمّة&amp;#34;، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2453,23 +2397,23 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+          <t>Apr 16, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-04-15T06:00:00Z</t>
+          <t>2026-04-16T06:00:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2482,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
@@ -2491,12 +2435,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044836542028320968</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2522,14 +2466,14 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
-emiratesislamic.ae/ar/Person…</t>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -2539,27 +2483,23 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+          <t>Apr 16, 2026 · 5:53 PM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-04-15T06:00:00Z</t>
+          <t>2026-04-16T17:53:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2568,7 +2508,451 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>127</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2044805287459398125</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/1ss9490ss1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1ss9490ss1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>بوالسلطان</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/777077466515079168/MKR49yEx_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته 
+الرجاء التواصل بي باحد من خدمة العملاء.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته 
+الرجاء التواصل بي باحد من خدمة العملاء.</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 3:49 PM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-16T15:49:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>aaditsh</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aadit Sheth</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 10:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-16T10:59:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5653</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2044717396758303206</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp; Conditions apply
+emiratesislamic.ae/en/accoun…</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp;amp; Conditions apply
+&lt;a href="https://www.emiratesislamic.ae/en/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad_guest_account"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-16T09:59:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad_guest_account']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2044717367842816367</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/accoun…</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+&lt;a href="https://www.emiratesislamic.ae/ar/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad_guest_account"&gt;emiratesislamic.ae/ar/accoun…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-16T09:59:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad_guest_account']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2044701412848705623</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+#SME #businessbanking #emiratesislamic</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+&lt;a href="/search?f=tweets&amp;amp;q=%23SME"&gt;#SME&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23businessbanking"&gt;#businessbanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 8:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-16T08:56:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23SME', 'https://x.com/search?f=tweets&amp;q=%23businessbanking', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,51 +541,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2045019425548452068</t>
+          <t>2045771180469272971</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548452068</t>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/firstdiver4ever</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>firstdiver4ever</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>اماراتى وافتخر</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -595,23 +589,23 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 6:00 AM UTC</t>
+          <t>Apr 19, 2026 · 7:47 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-17T06:00:00Z</t>
+          <t>2026-04-19T07:47:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -624,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -633,12 +627,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2045083221952532551</t>
+          <t>2045744202382807549</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -664,18 +658,22 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -685,23 +683,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-17T10:13:00Z</t>
+          <t>2026-04-19T06:00:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -714,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -723,12 +721,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2045083218303402442</t>
+          <t>2045744202651226430</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
+          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -754,18 +752,20 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -775,32 +775,36 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-17T10:13:00Z</t>
+          <t>2026-04-19T06:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -809,12 +813,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2045083209231221028</t>
+          <t>2045744202382807549</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045083209231221028</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -840,18 +844,22 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -861,23 +869,23 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-17T10:13:00Z</t>
+          <t>2026-04-19T06:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -890,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -899,49 +907,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2045083206936908088</t>
+          <t>2045771180469272971</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045083206936908088</t>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/firstdiver4ever</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>firstdiver4ever</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>اماراتى وافتخر</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -951,23 +955,27 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
+          <t>Apr 19, 2026 · 7:47 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-17T10:13:00Z</t>
+          <t>2026-04-19T07:47:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -976,623 +984,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2045041921689530456</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045041921689530456</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['huss23']</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 7:29 AM UTC</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-04-17T07:29:00Z</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2045035981535912006</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['alsajwani1']</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 7:05 AM UTC</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-04-17T07:05:00Z</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2045034534274540029</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045034534274540029</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['1ss9490ss1']</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 7:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-04-17T07:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2045019425548460066</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548460066</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-04-17T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2045019425548452068</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548452068</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-04-17T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2045083221952532551</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-04-17T10:13:00Z</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2045083209231221028</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083209231221028</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2026-04-17T10:13:00Z</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,73 +541,75 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever</t>
+          <t>https://x.com/mohmd_moh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>firstdiver4ever</t>
+          <t>mohmd_moh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>اماراتى وافتخر</t>
+          <t>Mohamed Mohamed</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/581880425234059264/lFW7trTI_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 7:47 AM UTC</t>
+          <t>Apr 20, 2026 · 1:46 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-19T07:47:00Z</t>
+          <t>2026-04-20T13:46:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -618,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -627,81 +629,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2045744202382807549</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['RakeshMavath', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 6:00 AM UTC</t>
+          <t>Apr 20, 2026 · 1:20 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-19T06:00:00Z</t>
+          <t>2026-04-20T13:20:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -709,10 +701,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -721,79 +713,71 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2045744202651226430</t>
+          <t>2046215734481834418</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gassann20203</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gassann20203</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gazan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1979011185929342976/BA4ftLDA_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 6:00 AM UTC</t>
+          <t>Apr 20, 2026 · 1:13 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-19T06:00:00Z</t>
+          <t>2026-04-20T13:13:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -804,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -813,12 +797,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2045744202382807549</t>
+          <t>2046148194392740002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -844,22 +828,14 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Your child&amp;#39;s smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AlphaYouth"&gt;#AlphaYouth&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -869,23 +845,23 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 6:00 AM UTC</t>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-19T06:00:00Z</t>
+          <t>2026-04-20T08:45:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23AlphaYouth']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -898,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -907,45 +883,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046106598221746656</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>firstdiver4ever</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>اماراتى وافتخر</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -960,22 +936,18 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 7:47 AM UTC</t>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-19T07:47:00Z</t>
+          <t>2026-04-20T06:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -984,7 +956,2563 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2046200603928338537</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['firstdiver4ever']</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 9:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-20T09:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Your child&amp;#39;s smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AlphaYouth"&gt;#AlphaYouth&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23AlphaYouth']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['mohmd_moh']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['gassann20203']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['gassann20203']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
         <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2046106592135831614</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2046224051438526663</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>mohmd_moh</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mohamed Mohamed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/581880425234059264/lFW7trTI_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:46 PM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:46:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2046215734481834418</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>gassann20203</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>gazan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1979011185929342976/BA4ftLDA_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Your child&amp;#39;s smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AlphaYouth"&gt;#AlphaYouth&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23AlphaYouth']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,49 +541,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2046617355866996757</t>
+          <t>2046976426990268451</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/mond33/status/2046617355866996757</t>
+          <t>https://x.com/UpendraS83806/status/2046976426990268451</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/mond33</t>
+          <t>https://x.com/UpendraS83806</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>mond33</t>
+          <t>UpendraS83806</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mohanad I. H. Almeshal</t>
+          <t>Upendra Singh</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2015119597855211520/eTupLxld_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>كان في السابق الامارات الاسلامي يعطي tier miles + sky awards هالحين بس sky awards للاسف.
- بدفع رسوم سنوية لبطاقة visa infinite درهم  2000 سنويا.
-@emiratesislamic
-@emirates</t>
+          <t>Please check your inbox.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>كان في السابق الامارات الاسلامي يعطي tier miles + sky awards هالحين بس sky awards للاسف.
- بدفع رسوم سنوية لبطاقة visa infinite درهم  2000 سنويا.
-&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
-&lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt;</t>
+          <t>Please check your inbox.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -592,30 +586,26 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['alsuwaidi_ae']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 3:49 PM UTC</t>
+          <t>Apr 22, 2026 · 3:36 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-21T15:49:00Z</t>
+          <t>2026-04-22T15:36:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic', 'https://x.com/emirates']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -623,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>943</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -635,45 +625,51 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2046584718758707650</t>
+          <t>2046831372824674407</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806/status/2046584718758707650</t>
+          <t>https://x.com/emiratesislamic/status/2046831372824674407</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UpendraS83806</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Upendra Singh</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
-Please advise.</t>
+          <t>Groceries. Dining. Shopping.
+Turn every swipe into rewards!
+Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; My client transferred payment from your bank but still not credited into my account.
-Please advise.</t>
+          <t>Groceries. Dining. Shopping.
+Turn every swipe into rewards!
+Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -683,23 +679,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 1:39 PM UTC</t>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-21T13:39:00Z</t>
+          <t>2026-04-22T06:00:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -712,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -721,12 +717,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2046494860136346080</t>
+          <t>2046882012129058966</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046494860136346080</t>
+          <t>https://x.com/emiratesislamic/status/2046882012129058966</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -752,16 +748,20 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -771,23 +771,23 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 7:42 AM UTC</t>
+          <t>Apr 22, 2026 · 9:21 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-21T07:42:00Z</t>
+          <t>2026-04-22T09:21:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -809,45 +809,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2046475853610221799</t>
+          <t>2046882010497524009</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/Shahbazengg1/status/2046475853610221799</t>
+          <t>https://x.com/emiratesislamic/status/2046882010497524009</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/Shahbazengg1</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shahbazengg1</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1448900525093572610/gR4jGser_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>@emiratesislamic do you have customer support? I am unable to connect. 
-I facing unfair charges on my credit card</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; do you have customer support? I am unable to connect. 
-I facing unfair charges on my credit card</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -857,25 +857,21 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 6:27 AM UTC</t>
+          <t>Apr 22, 2026 · 9:21 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-21T06:27:00Z</t>
+          <t>2026-04-22T09:21:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>1</v>
       </c>
@@ -886,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -895,12 +891,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2046468979456106922</t>
+          <t>2046882007976698203</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046468979456106922</t>
+          <t>https://x.com/emiratesislamic/status/2046882007976698203</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -926,16 +922,20 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>How many subscriptions are you paying for?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>How many subscriptions are you paying for?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -945,27 +945,27 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 6:00 AM UTC</t>
+          <t>Apr 22, 2026 · 9:21 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-21T06:00:00Z</t>
+          <t>2026-04-22T09:21:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2046453878388859353</t>
+          <t>2046881064883249563</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046453878388859353</t>
+          <t>https://x.com/emiratesislamic/status/2046881064883249563</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1014,18 +1014,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1035,23 +1037,23 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 5:00 AM UTC</t>
+          <t>Apr 22, 2026 · 9:17 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-21T05:00:00Z</t>
+          <t>2026-04-22T09:17:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1064,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -1073,12 +1075,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2046506497341850082</t>
+          <t>2046881062899355911</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046506497341850082</t>
+          <t>https://x.com/emiratesislamic/status/2046881062899355911</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1104,51 +1106,49 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل , يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبه و نتمني خدمتك دائماً بأفضل صوره ممكنه. شكراًلك و نتمني لك يوماً سعيداً</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل , يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبه و نتمني خدمتك دائماً بأفضل صوره ممكنه. شكراًلك و نتمني لك يوماً سعيداً</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['mohmd_moh']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 8:29 AM UTC</t>
+          <t>Apr 22, 2026 · 9:17 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-21T08:29:00Z</t>
+          <t>2026-04-22T09:17:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2046505927696580713</t>
+          <t>2046881060533727547</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046505927696580713</t>
+          <t>https://x.com/emiratesislamic/status/2046881060533727547</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1188,44 +1188,50 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['gassann20203']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 8:26 AM UTC</t>
+          <t>Apr 22, 2026 · 9:17 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-21T08:26:00Z</t>
+          <t>2026-04-22T09:17:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1234,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1243,12 +1249,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2046494860136346080</t>
+          <t>2046881058352746917</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046494860136346080</t>
+          <t>https://x.com/emiratesislamic/status/2046881058352746917</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1274,16 +1280,18 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1293,27 +1301,23 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 7:42 AM UTC</t>
+          <t>Apr 22, 2026 · 9:17 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-21T07:42:00Z</t>
+          <t>2026-04-22T09:17:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1322,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>70</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -1331,12 +1335,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2046494857888158127</t>
+          <t>2046878598796112328</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046494857888158127</t>
+          <t>https://x.com/emiratesislamic/status/2046878598796112328</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1362,44 +1366,40 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>فخرٌ لا يُحكى… بل يُشعَر. 🇦🇪
-تماشياً مع رؤية صاحب السمو الشيخ محمد بن راشد آل مكتوم، نرفع رايتنا عالياً، ونحتفي بوطنٍ توحّد على القيم، وتماسك بالقوة، وازدهر بروحٍ لا تعرف المستحيل.
-#فخورين_بالإمارات</t>
+          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>فخرٌ لا يُحكى… بل يُشعَر. 🇦🇪
-تماشياً مع رؤية صاحب السمو الشيخ محمد بن راشد آل مكتوم، نرفع رايتنا عالياً، ونحتفي بوطنٍ توحّد على القيم، وتماسك بالقوة، وازدهر بروحٍ لا تعرف المستحيل.
-&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt;</t>
+          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['UpendraS83806']</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 7:42 AM UTC</t>
+          <t>Apr 22, 2026 · 9:07 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-21T07:42:00Z</t>
+          <t>2026-04-22T09:07:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>1</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>121</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2046482022860775619</t>
+          <t>2046861646031651319</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046482022860775619</t>
+          <t>https://x.com/emiratesislamic/status/2046861646031651319</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1464,22 +1464,22 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>['Shahbazengg1']</t>
+          <t>['mond33']</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 6:51 AM UTC</t>
+          <t>Apr 22, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-21T06:51:00Z</t>
+          <t>2026-04-22T08:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2046468979456180602</t>
+          <t>2046831372824674407</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046468979456180602</t>
+          <t>https://x.com/emiratesislamic/status/2046831372824674407</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1534,16 +1534,20 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>كم عدد الاشتراكات التي تدفع مقابلها؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Groceries. Dining. Shopping.
+Turn every swipe into rewards!
+Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>كم عدد الاشتراكات التي تدفع مقابلها؟
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Groceries. Dining. Shopping.
+Turn every swipe into rewards!
+Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1553,23 +1557,23 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 6:00 AM UTC</t>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-21T06:00:00Z</t>
+          <t>2026-04-22T06:00:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1582,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1591,12 +1595,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2046468979456106922</t>
+          <t>2046831371042107554</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046468979456106922</t>
+          <t>https://x.com/emiratesislamic/status/2046831371042107554</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1622,16 +1626,16 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>How many subscriptions are you paying for?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>How many subscriptions are you paying for?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1641,27 +1645,27 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 6:00 AM UTC</t>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-21T06:00:00Z</t>
+          <t>2026-04-22T06:00:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1670,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -1679,12 +1683,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2046453878388859353</t>
+          <t>2046831368349348321</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046453878388859353</t>
+          <t>https://x.com/emiratesislamic/status/2046831368349348321</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1710,18 +1714,12 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1731,27 +1729,23 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 5:00 AM UTC</t>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-21T05:00:00Z</t>
+          <t>2026-04-22T06:00:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1760,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -1769,45 +1763,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2046584718758707650</t>
+          <t>2046831365216235900</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806/status/2046584718758707650</t>
+          <t>https://x.com/emiratesislamic/status/2046831365216235900</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UpendraS83806</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Upendra Singh</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
-Please advise.</t>
+          <t>البقالة. المطاعم. التسوق.
+أنفق واحصل على المكافآت أينما كنت!</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; My client transferred payment from your bank but still not credited into my account.
-Please advise.</t>
+          <t>البقالة. المطاعم. التسوق.
+أنفق واحصل على المكافآت أينما كنت!</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1817,27 +1811,23 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 1:39 PM UTC</t>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-21T13:39:00Z</t>
+          <t>2026-04-22T06:00:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1846,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1855,75 +1845,71 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2046494860136346080</t>
+          <t>2046976426990268451</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046494860136346080</t>
+          <t>https://x.com/UpendraS83806/status/2046976426990268451</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/UpendraS83806</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>UpendraS83806</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Upendra Singh</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
+          <t>Please check your inbox.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>Please check your inbox.</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 7:42 AM UTC</t>
+          <t>Apr 22, 2026 · 3:36 PM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-21T07:42:00Z</t>
+          <t>2026-04-22T15:36:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>0</v>
       </c>
@@ -1934,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1943,45 +1929,51 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2046475853610221799</t>
+          <t>2046882012129058966</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/Shahbazengg1/status/2046475853610221799</t>
+          <t>https://x.com/emiratesislamic/status/2046882012129058966</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/Shahbazengg1</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shahbazengg1</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1448900525093572610/gR4jGser_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>@emiratesislamic do you have customer support? I am unable to connect. 
-I facing unfair charges on my credit card</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; do you have customer support? I am unable to connect. 
-I facing unfair charges on my credit card</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -1991,36 +1983,736 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 21, 2026 · 6:27 AM UTC</t>
+          <t>Apr 22, 2026 · 9:21 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-21T06:27:00Z</t>
+          <t>2026-04-22T09:21:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2046882010497524009</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046882010497524009</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 9:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-22T09:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2046882007976698203</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046882007976698203</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 9:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-22T09:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2046881064883249563</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046881064883249563</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 9:17 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-22T09:17:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2046881062899355911</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046881062899355911</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 9:17 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-22T09:17:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2046881060533727547</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046881060533727547</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 9:17 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-22T09:17:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2046831372824674407</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046831372824674407</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Groceries. Dining. Shopping.
+Turn every swipe into rewards!
+Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Groceries. Dining. Shopping.
+Turn every swipe into rewards!
+Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-22T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2046831371042107554</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046831371042107554</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-22T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2046831368349348321</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046831368349348321</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-22T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,63 +541,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/iDenville</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>iDenville</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>DenvilleCommunity</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
+          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
+          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['stelpetla', 'JDunlap1974']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 12:18 PM UTC</t>
+          <t>Apr 25, 2026 · 12:29 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-23T12:18:00Z</t>
+          <t>2026-04-25T00:29:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -609,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -621,12 +625,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -652,14 +656,22 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt;</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -669,23 +681,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 12:13 PM UTC</t>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-23T12:13:00Z</t>
+          <t>2026-04-24T16:43:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -698,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -707,12 +719,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -738,14 +750,18 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-emiratesislamic.ae/en/news-a…</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -755,27 +771,23 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T11:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -784,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -793,45 +805,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047249884101673033</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/ABCinGCC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ABCinGCC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Arabian Business Community (ABC GCC)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-emiratesislamic.ae/ar/news-a…</t>
+          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
+Read more on abc-gcc.net/News/1/395058
+#ABCNews #Profit #Banking #FinancialInstitution</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-&lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
+          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
+Read more on &lt;a href="https://abc-gcc.net/News/1/395058"&gt;abc-gcc.net/News/1/395058&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23ABCNews"&gt;#ABCNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Profit"&gt;#Profit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialInstitution"&gt;#FinancialInstitution&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -841,27 +855,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 7:15 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T07:15:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
+          <t>['https://abc-gcc.net/News/1/395058', 'https://x.com/search?f=tweets&amp;q=%23ABCNews', 'https://x.com/search?f=tweets&amp;q=%23Profit', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialInstitution']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -870,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -879,12 +893,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047249881757085701</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249881757085701</t>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -910,12 +924,20 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة.</t>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة.</t>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -925,23 +947,27 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T06:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -950,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -959,12 +985,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047241499490807897</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -990,40 +1016,50 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['UpendraS83806']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:09 AM UTC</t>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-23T09:09:00Z</t>
+          <t>2026-04-24T16:43:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1034,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -1043,12 +1079,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047193755975917822</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1074,14 +1110,18 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1091,36 +1131,32 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T16:43:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1129,12 +1165,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047193753073402364</t>
+          <t>2047717920193622257</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073402364</t>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1160,24 +1196,24 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Your spending isn’t random… it has patterns.
-Check your last 10 transactions.
-Look for repeats, not amounts.
-You’ll quickly see what’s costing you the most, 
-it’s habits, not purchases.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+emiratesislamic.ae/ar/offers…
+#الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Your spending isn’t random… it has patterns.
-Check your last 10 transactions.
-Look for repeats, not amounts.
-You’ll quickly see what’s costing you the most, 
-it’s habits, not purchases.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1187,23 +1223,23 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T16:42:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1216,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>49</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -1225,12 +1261,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047193753073357199</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1256,20 +1292,16 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1279,17 +1311,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T16:42:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1304,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -1313,12 +1345,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1344,14 +1376,26 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-emiratesislamic.ae/en/news-a…</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1361,25 +1405,21 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>0</v>
       </c>
@@ -1390,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -1399,12 +1439,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047249884101673033</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1430,14 +1470,14 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-emiratesislamic.ae/ar/news-a…</t>
+          <t>Terms &amp; condition apply.
+To know more, please visit emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-&lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
+          <t>Terms &amp;amp; condition apply.
+To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1447,27 +1487,27 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1476,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1485,12 +1525,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047193755975917822</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1516,14 +1556,24 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp; discounts
+Start them young!</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young!</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1533,27 +1583,23 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1562,7 +1608,2163 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>53</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2047657962978558100</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2047657960227176876</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2047632173461561410</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp; conditions apply.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:02:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2047632164863250935</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:02:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2047632125583605871</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2047632116649689120</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2047631643926483032</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2047631643901390924</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;Cs apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2047631640168374617</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2047631639946093018</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2047556140511162463</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-24T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2047556140431556611</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-24T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2047541045768962304</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+#ProudOfUAE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-24T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2047541041612427486</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
+من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
+#فخورين_بالإمارات</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
+من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
+&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-24T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2047717990762782723</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic #FrontlineHeroes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-24T16:43:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2047717920193622257</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+emiratesislamic.ae/ar/offers…
+#الإمارات_الإسلامي #أبطال_الوطن</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-24T16:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2047657974936604881</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Terms &amp; condition apply.
+To know more, please visit emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Terms &amp;amp; condition apply.
+To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2047657972390560162</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp; discounts
+Start them young!</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young!</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2047657962978558100</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2047632173461561410</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp; conditions apply.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:02:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2047632125583605871</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2047631643926483032</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2047631643901390924</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;Cs apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2047541045768962304</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+#ProudOfUAE</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-24T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,71 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047835274818748466</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>iDenville</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DenvilleCommunity</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['stelpetla', 'JDunlap1974']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 12:29 AM UTC</t>
+          <t>Apr 25, 2026 · 8:54 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-25T00:29:00Z</t>
+          <t>2026-04-25T20:54:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -625,12 +625,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047717990762782723</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -656,22 +656,26 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -681,25 +685,21 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -719,12 +719,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047631640168374617</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -750,18 +750,16 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -771,17 +769,17 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-24T11:00:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -793,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -805,47 +803,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047575014564921667</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ABCinGCC</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arabian Business Community (ABC GCC)</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on abc-gcc.net/News/1/395058
-#ABCNews #Profit #Banking #FinancialInstitution</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on &lt;a href="https://abc-gcc.net/News/1/395058"&gt;abc-gcc.net/News/1/395058&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23ABCNews"&gt;#ABCNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Profit"&gt;#Profit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialInstitution"&gt;#FinancialInstitution&lt;/a&gt;</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -855,27 +853,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 7:15 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-24T07:15:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://abc-gcc.net/News/1/395058', 'https://x.com/search?f=tweets&amp;q=%23ABCNews', 'https://x.com/search?f=tweets&amp;q=%23Profit', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialInstitution']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -893,90 +891,82 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047556140431556611</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/iDenville</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>iDenville</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>DenvilleCommunity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['stelpetla', 'JDunlap1974']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 25</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+          <t>Apr 25, 2026 · 12:29 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-24T06:00:00Z</t>
+          <t>2026-04-25T00:29:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>37</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
@@ -985,12 +975,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047717990762782723</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1016,22 +1006,26 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1041,25 +1035,21 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1070,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -1079,12 +1069,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047717988195852322</t>
+          <t>2047978927205781948</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1110,18 +1100,24 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1131,32 +1127,32 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1165,12 +1161,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047717920193622257</t>
+          <t>2047963837182156928</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1196,24 +1192,18 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1223,23 +1213,23 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-24T16:42:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
+          <t>['https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1252,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>212</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -1261,12 +1251,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047717917324710124</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1292,16 +1282,16 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1311,17 +1301,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-24T16:42:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1333,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1335,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047657988064727443</t>
+          <t>2047963832136433706</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
+          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1376,26 +1366,18 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/campai…</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية &amp;#34;تكافل&amp;#34; لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1405,23 +1387,27 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1430,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1439,12 +1425,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047657974936604881</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
+          <t>https://x.com/emiratesislamic/status/2047963827363299676</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1470,14 +1456,16 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Terms &amp;amp; condition apply.
-To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1487,27 +1475,23 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1516,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1525,12 +1509,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047657972390560162</t>
+          <t>2047933638453366977</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
+          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1556,24 +1540,18 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp; discounts
-Start them young!</t>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp;amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp;amp; discounts
-Start them young!</t>
+          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1583,23 +1561,27 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1608,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -1617,12 +1599,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047657962978558100</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1648,12 +1630,16 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1663,23 +1649,23 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1692,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1701,12 +1687,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047657960227176876</t>
+          <t>2047933633118228811</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
+          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1732,26 +1718,18 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1761,21 +1739,25 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
@@ -1786,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1795,12 +1777,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047632173461561410</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
+          <t>https://x.com/emiratesislamic/status/2047933629662155095</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1826,20 +1808,16 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp; conditions apply.
-emiratesislamic.ae/ar/offers…</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt;)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1849,36 +1827,36 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-24T11:02:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>24</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -1887,12 +1865,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047632164863250935</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1918,16 +1896,12 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1937,23 +1911,23 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-24T11:02:00Z</t>
+          <t>2026-04-25T06:00:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1962,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -1971,12 +1945,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2047632125583605871</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
+          <t>https://x.com/emiratesislamic/status/2047918530113266095</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2002,22 +1976,12 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2027,27 +1991,23 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-24T11:01:00Z</t>
+          <t>2026-04-25T06:00:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2056,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
@@ -2065,12 +2025,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2047632116649689120</t>
+          <t>2047963837182156928</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
+          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2096,16 +2056,18 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2115,23 +2077,27 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-24T11:01:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2140,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -2149,12 +2115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2047631643926483032</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2180,20 +2146,16 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2203,36 +2165,32 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-24T11:00:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
@@ -2241,12 +2199,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2047631643901390924</t>
+          <t>2047963832136433706</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
+          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2272,20 +2230,18 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/campai…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية &amp;#34;تكافل&amp;#34; لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2295,27 +2251,27 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-24T11:00:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+          <t>['https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2324,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2333,12 +2289,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2047631640168374617</t>
+          <t>2047933638453366977</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2364,18 +2320,18 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2385,23 +2341,27 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-24T11:00:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+        </is>
+      </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2410,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -2419,12 +2379,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2047631639946093018</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2450,18 +2410,16 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2471,21 +2429,25 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-04-24T11:00:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['http://noon.com']</t>
+        </is>
+      </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
@@ -2496,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -2505,12 +2467,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2047556140511162463</t>
+          <t>2047933633118228811</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
+          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2536,18 +2498,18 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -2557,27 +2519,27 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-04-24T06:00:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2586,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -2595,12 +2557,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2047556140431556611</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2626,20 +2588,12 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -2649,25 +2603,21 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-04-24T06:00:00Z</t>
+          <t>2026-04-25T06:00:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
         <v>0</v>
       </c>
@@ -2678,1093 +2628,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2047541045768962304</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3</v>
-      </c>
-      <c r="V27" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2047717990762782723</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-04-24T16:43:00Z</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
-        </is>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2047717920193622257</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-04-24T16:42:00Z</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2047657974936604881</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Terms &amp;amp; condition apply.
-To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp;amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp;amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2047657962978558100</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2047632173461561410</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp; conditions apply.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:02:00Z</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:01:00Z</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2047631643901390924</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2047541045768962304</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,12 +541,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2048143516644016239</t>
+          <t>2048954465978339486</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
+          <t>https://x.com/gold_hadas/status/2048954465978339486</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -572,12 +572,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits gulfnews.com/business/bankin…</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals tradingview.com/news/reuters…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/"&gt;tradingview.com/news/reuters…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -587,23 +587,23 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 8:54 PM UTC</t>
+          <t>Apr 28, 2026 · 2:36 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-25T20:54:00Z</t>
+          <t>2026-04-28T02:36:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602']</t>
+          <t>['https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -625,57 +625,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047978927268696148</t>
+          <t>2048953588357963815</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
+          <t>https://x.com/gold_hadas/status/2048953588357963815</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨
-✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp; lifestyle benefits
-And much more.
-Terms &amp; conditions apply.</t>
+          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨
-✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp;amp; lifestyle benefits
-And much more.
-Terms &amp;amp; conditions apply.</t>
+          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -685,21 +671,25 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 2:32 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-25T10:00:00Z</t>
+          <t>2026-04-28T02:32:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -710,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -719,47 +709,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047963834812334213</t>
+          <t>2048928610338144280</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
+          <t>https://x.com/gold_hadas/status/2048928610338144280</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
-Financing up to 85% of the property value.  
-Low processing fees and competitive profit rates.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals mediaoffice.ae/en/news/2026/…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
-Financing up to 85% of the property value.  
-Low processing fees and competitive profit rates.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic"&gt;mediaoffice.ae/en/news/2026/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -769,32 +755,36 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 28, 2026 · 12:53 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-28T00:53:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -803,47 +793,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047933636054245884</t>
+          <t>2048838102010019915</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
+          <t>https://x.com/khaleejinsight/status/2048838102010019915</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/khaleejinsight</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khaleejinsight</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Khaleej Business Insight</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1900814841868394496/B-nstVph_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
-🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
-✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
+          <t>Emirates Islamic Launches Digital Gold Trading via Mobile App khaleejbusinessinsight.com/e… via @khaleejbusinessinsight.com 
+Emirates Islamic introduces digital gold trading via its mobile app, making precious metal investing more accessible and flexible.
+#DigitalGold #EmiratesIslamic</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
-🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
-✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
+          <t>Emirates Islamic Launches Digital Gold Trading via Mobile App &lt;a href="https://khaleejbusinessinsight.com/emirates-islamic-launches-digital-gold-trading-via-mobile-app/"&gt;khaleejbusinessinsight.com/e…&lt;/a&gt; via @khaleejbusinessinsight.com 
+Emirates Islamic introduces digital gold trading via its mobile app, making precious metal investing more accessible and flexible.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DigitalGold"&gt;#DigitalGold&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -853,27 +843,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 6:54 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T18:54:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['http://noon.com']</t>
+          <t>['https://khaleejbusinessinsight.com/emirates-islamic-launches-digital-gold-trading-via-mobile-app/', 'https://x.com/search?f=tweets&amp;q=%23DigitalGold', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -882,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -891,82 +881,82 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047835274818748466</t>
+          <t>2048792635020612079</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/gold_hadas/status/2048792635020612079</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>iDenville</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DenvilleCommunity</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>Emirates Islamic Becomes First Islamic Bank In The UAE To Offer Digital Investment In Precious Metals menafn.com/1111036523/Emirat…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>Emirates Islamic Becomes First Islamic Bank In The UAE To Offer Digital Investment In Precious Metals &lt;a href="https://menafn.com/1111036523/Emirates-Islamic-Becomes-First-Islamic-Bank-In-The-UAE-To-Offer-Digital-Investment-In-Precious-Metals"&gt;menafn.com/1111036523/Emirat…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['stelpetla', 'JDunlap1974']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Apr 25</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 12:29 AM UTC</t>
+          <t>Apr 27, 2026 · 3:53 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-25T00:29:00Z</t>
+          <t>2026-04-27T15:53:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://menafn.com/1111036523/Emirates-Islamic-Becomes-First-Islamic-Bank-In-The-UAE-To-Offer-Digital-Investment-In-Precious-Metals']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>148</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -975,57 +965,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047978927268696148</t>
+          <t>2048773845776310425</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
+          <t>https://x.com/GCCBusinessNews/status/2048773845776310425</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/GCCBusinessNews</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>GCCBusinessNews</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>GCC Business News</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1253796411872862212/h2Q8-9rJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨
-✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp; lifestyle benefits
-And much more.
-Terms &amp; conditions apply.</t>
+          <t>Emirates Islamic to offer digital investment in precious metals
+gccbusinessnews.com/emirates…
+#EmiratesIslamic #GoldInvestment #SilverInvestment #ShariahCompliant #DigitalBanking #PreciousMetals #WealthManagement #GCCBusinessNews @emiratesislamic</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨
-✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp;amp; lifestyle benefits
-And much more.
-Terms &amp;amp; conditions apply.</t>
+          <t>Emirates Islamic to offer digital investment in precious metals
+&lt;a href="https://www.gccbusinessnews.com/emirates-islamic-offers-digital-investment/"&gt;gccbusinessnews.com/emirates…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GoldInvestment"&gt;#GoldInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SilverInvestment"&gt;#SilverInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ShariahCompliant"&gt;#ShariahCompliant&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalBanking"&gt;#DigitalBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PreciousMetals"&gt;#PreciousMetals&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23WealthManagement"&gt;#WealthManagement&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GCCBusinessNews"&gt;#GCCBusinessNews&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1035,21 +1015,25 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 2:38 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-25T10:00:00Z</t>
+          <t>2026-04-27T14:38:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://www.gccbusinessnews.com/emirates-islamic-offers-digital-investment/', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23GoldInvestment', 'https://x.com/search?f=tweets&amp;q=%23SilverInvestment', 'https://x.com/search?f=tweets&amp;q=%23ShariahCompliant', 'https://x.com/search?f=tweets&amp;q=%23DigitalBanking', 'https://x.com/search?f=tweets&amp;q=%23PreciousMetals', 'https://x.com/search?f=tweets&amp;q=%23WealthManagement', 'https://x.com/search?f=tweets&amp;q=%23GCCBusinessNews', 'https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1060,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1069,75 +1053,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047978927205781948</t>
+          <t>2048747126566641772</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
+          <t>https://x.com/gentle_arch/status/2048747126566641772</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gentle_arch</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gentle_arch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mo FiraaS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1867089865558347776/lkpOodzk_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
-سعادة بلا حدود!
-تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
-🌟 استرداد يصل إلى 6%، بلا حدود
-🎁 مكافأة ترحيبية تصل إلى 750 درهم
-💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
+          <t>يعني نشتري وسبيكة تصل عندهم ولا في توصيل؟؟؟</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
-سعادة بلا حدود!
-تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
-🌟 استرداد يصل إلى 6%، بلا حدود
-🎁 مكافأة ترحيبية تصل إلى 750 درهم
-💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
+          <t>يعني نشتري وسبيكة تصل عندهم ولا في توصيل؟؟؟</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['DXBMediaOffice', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 12:52 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-25T10:00:00Z</t>
+          <t>2026-04-27T12:52:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1152,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1161,77 +1137,71 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047963837182156928</t>
+          <t>2048724846792855697</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
+          <t>https://x.com/NazzysCt/status/2048724846792855697</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Quick approvals and easy digital documentation.
-Takaful coverage for yourself and your property.
-Terms &amp; Conditions apply.
-emiratesislamic.ae/en/campai…</t>
+          <t>Number dm’ed as requested</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Quick approvals and easy digital documentation.
-Takaful coverage for yourself and your property.
-Terms &amp;amp; Conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/campai…&lt;/a&gt;</t>
+          <t>Number dm’ed as requested</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 11:24 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-27T11:24:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1242,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1251,47 +1221,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047963834812334213</t>
+          <t>2048711386818084907</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
+          <t>https://x.com/Ldyheart/status/2048711386818084907</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Ldyheart</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Ldyheart</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>RV Global Reset</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016603167585087489/50LxYE_N_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
-Financing up to 85% of the property value.  
-Low processing fees and competitive profit rates.</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE's first digital investment service khaleejtimes.com/business/em…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
-Financing up to 85% of the property value.  
-Low processing fees and competitive profit rates.</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE&amp;#39;s first digital investment service &lt;a href="https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1301,32 +1267,36 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 10:30 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-27T10:30:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1335,49 +1305,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047963832136433706</t>
+          <t>2048699606029234189</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
+          <t>https://x.com/khaleejtimes/status/2048699606029234189</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/khaleejtimes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khaleejtimes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Khaleej Times</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1662009811242831874/ZUTWSfk4_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>موافقات سريعة ووثائق رقمية سهلة
-تغطية "تكافل" لك ولعقارك للحماية وراحة البال
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/campai…</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE's first digital investment service
+khaleejtimes.com/business/em…</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>موافقات سريعة ووثائق رقمية سهلة
-تغطية &amp;#34;تكافل&amp;#34; لك ولعقارك للحماية وراحة البال
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/campai…&lt;/a&gt;</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE&amp;#39;s first digital investment service
+&lt;a href="https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1387,36 +1353,36 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-27T09:43:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+          <t>['https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service']</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="12">
@@ -1425,73 +1391,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047963827363299676</t>
+          <t>2048694049578574033</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963827363299676</t>
+          <t>https://x.com/khalifaa_rashed/status/2048694049578574033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/khalifaa_rashed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khalifaa_rashed</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Khalef Saad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1902376067718848512/dbP8oWQE_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
-تمويل يصل إلى %85 من قيمة العقار
-رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
+          <t>استثمار رقمي فـ الذهب والفضة بطريقة آمنة ومتوافقة مع الشريعة يعطي ثقة أكبر للمتعاملين</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
-تمويل يصل إلى %85 من قيمة العقار
-رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
+          <t>استثمار رقمي فـ الذهب والفضة بطريقة آمنة ومتوافقة مع الشريعة يعطي ثقة أكبر للمتعاملين</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['DXBMediaOffice', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:21 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-27T09:21:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1500,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1509,77 +1475,71 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047933638453366977</t>
+          <t>2048690739530412259</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
+          <t>https://x.com/bde__ir/status/2048690739530412259</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/bde__ir</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>bde__ir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>بدر ال مشاري.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1866799615325929472/IQ77nzLh_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>💸 Miles &amp; instant rewards and multiple redemption options
-👍 Cashback, discounts, golf, valet parking at select locations and much more
-Offer valid till 30 June 2026
-emiratesislamic.ae/en/offers…</t>
+          <t>"الذهب والفضة.. بين يديك بضغطة زر! خطوة ذكية من 'الإمارات الإسلامي' تدمج بين الأمان الشرعي والحلول الرقمية السهلة. الآن أصبح الاستثمار في المعادن الثمينة متاحاً للجميع بسلاسة وموثوقية عالية عبر التطبيق. 📱⚖️ابتكار يعزز مكانة الصيرفة الإسلامية كقائد للتحول الرقمي في المنطقة. 🚀🇦🇪</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
-👍 Cashback, discounts, golf, valet parking at select locations and much more
-Offer valid till 30 June 2026
-&lt;a href="https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>&amp;#34;الذهب والفضة.. بين يديك بضغطة زر! خطوة ذكية من &amp;#39;الإمارات الإسلامي&amp;#39; تدمج بين الأمان الشرعي والحلول الرقمية السهلة. الآن أصبح الاستثمار في المعادن الثمينة متاحاً للجميع بسلاسة وموثوقية عالية عبر التطبيق. 📱⚖️ابتكار يعزز مكانة الصيرفة الإسلامية كقائد للتحول الرقمي في المنطقة. 🚀🇦🇪</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['DXBMediaOffice', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:08 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T09:08:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -1590,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -1599,47 +1559,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047933636054245884</t>
+          <t>2048689865970348293</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
+          <t>https://x.com/DXBMediaOffice/status/2048689865970348293</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/DXBMediaOffice</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>DXBMediaOffice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Dubai Media Office</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526475569885548546/wQzde3FB_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
-🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
-✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering, a first-of-its-kind by an Islamic bank in the UAE, empowers customers to buy and sell certified physical gold and silver bars in a secure environment, providing a convenient way to diversify their portfolios and preserve investment value.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
-🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
-✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering, a first-of-its-kind by an Islamic bank in the UAE, empowers customers to buy and sell certified physical gold and silver bars in a secure environment, providing a convenient way to diversify their portfolios and preserve investment value.</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1649,36 +1605,32 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:05 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T09:05:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['http://noon.com']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V14" t="n">
-        <v>49</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="15">
@@ -1687,49 +1639,51 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047933633118228811</t>
+          <t>2048687555772666020</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
+          <t>https://x.com/FintechGate1/status/2048687555772666020</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
-👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
-يسري العرض لغاية 30 يونيو 2026
-emiratesislamic.ae/ar/offers…</t>
+          <t>«الإمارات الإسلامي» أول مصرف إسلامي في دولة الإمارات العربية المتحدة يطلق حلول رقمية للاستثمار في المعادن الثمينة
+fintechgate.net/sa1g | التفاصيل 
+@emiratesislamic
+#fintech_gate
+#الإمارات_الإسلامي #الإمارات_العربية_المتحدة #حلول_رقمية_للاستثمار  #المعادن_الثمينة</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
-👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
-يسري العرض لغاية 30 يونيو 2026
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>«الإمارات الإسلامي» أول مصرف إسلامي في دولة الإمارات العربية المتحدة يطلق حلول رقمية للاستثمار في المعادن الثمينة
+&lt;a href="https://fintechgate.net/sa1g"&gt;fintechgate.net/sa1g&lt;/a&gt; | التفاصيل 
+&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_العربية_المتحدة"&gt;#الإمارات_العربية_المتحدة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حلول_رقمية_للاستثمار"&gt;#حلول_رقمية_للاستثمار&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23المعادن_الثمينة"&gt;#المعادن_الثمينة&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1739,27 +1693,27 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:55 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T08:55:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+          <t>['https://fintechgate.net/sa1g', 'https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_العربية_المتحدة', 'https://x.com/search?f=tweets&amp;q=%23حلول_رقمية_للاستثمار', 'https://x.com/search?f=tweets&amp;q=%23المعادن_الثمينة']</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1768,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1777,47 +1731,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047933629662155095</t>
+          <t>2048679648536752433</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933629662155095</t>
+          <t>https://x.com/NazzysCt/status/2048679648536752433</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
-🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
-✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
+          <t>@emiratesislamic I would truly appreciate it if you could make an exception and reconsider reversing this charge as a gesture of goodwill. Your support during this time would mean a lot.
+Thank you.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
-🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt;)
-✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I would truly appreciate it if you could make an exception and reconsider reversing this charge as a gesture of goodwill. Your support during this time would mean a lot.
+Thank you.</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1827,36 +1779,36 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:24 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T08:24:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['http://noon.com']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>137</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1865,43 +1817,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047918534362030486</t>
+          <t>2048679565225324653</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
+          <t>https://x.com/NazzysCt/status/2048679565225324653</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
+          <t>I fully understand the policy, however I’m currently facing financial difficulties due to ongoing war-related impacts affecting my payouts. I’ve been a loyal customer for over 10 years and have always maintained my relationship in good faith.
+@emiratesislamic</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
+          <t>I fully understand the policy, however I’m currently facing financial difficulties due to ongoing war-related impacts affecting my payouts. I’ve been a loyal customer for over 10 years and have always maintained my relationship in good faith.
+&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1911,23 +1865,27 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 6:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:24 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-25T06:00:00Z</t>
+          <t>2026-04-27T08:24:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1936,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1945,43 +1903,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2047918530113266095</t>
+          <t>2048679400204644634</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047918530113266095</t>
+          <t>https://x.com/NazzysCt/status/2048679400204644634</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Dear @EmiratesIslamic,
+I kindly request your support in waiving the over-limit charge applied to my card. I contacted customer service, but was informed that a waiver can only be requested once per year since my last request was in July.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Dear &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt;,
+I kindly request your support in waiving the over-limit charge applied to my card. I contacted customer service, but was informed that a waiver can only be requested once per year since my last request was in July.</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -1991,23 +1951,27 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 6:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:23 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-25T06:00:00Z</t>
+          <t>2026-04-27T08:23:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2016,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2025,12 +1989,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2047963837182156928</t>
+          <t>2048643306221957276</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
+          <t>https://x.com/emiratesislamic/status/2048643306221957276</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2056,18 +2020,20 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Quick approvals and easy digital documentation.
-Takaful coverage for yourself and your property.
-Terms &amp; Conditions apply.
-emiratesislamic.ae/en/campai…</t>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Quick approvals and easy digital documentation.
-Takaful coverage for yourself and your property.
-Terms &amp;amp; Conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/campai…&lt;/a&gt;</t>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2077,36 +2043,36 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-27T06:00:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -2115,47 +2081,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2047963834812334213</t>
+          <t>2048641511525585317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
+          <t>https://x.com/Allapichai25998/status/2048641511525585317</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Allapichai25998</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Allapichai25998</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Sahul Allapichai</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
-Financing up to 85% of the property value.  
-Low processing fees and competitive profit rates.</t>
+          <t>@emiratesislamic Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
-Financing up to 85% of the property value.  
-Low processing fees and competitive profit rates.</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2165,21 +2127,25 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 5:52 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-27T05:52:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
@@ -2187,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2199,12 +2165,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2047963832136433706</t>
+          <t>2048854699953021336</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
+          <t>https://x.com/emiratesislamic/status/2048854699953021336</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2230,18 +2196,18 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>موافقات سريعة ووثائق رقمية سهلة
-تغطية "تكافل" لك ولعقارك للحماية وراحة البال
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/campai…</t>
+          <t>إنفاقك الأكبر ليس دائماً كما تعتقد.
+نصيحة: قسّم مصروفاتك الأسبوع الماضي إلى فئات، وقد تتفاجأ بما يتصدر القائمة.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>موافقات سريعة ووثائق رقمية سهلة
-تغطية &amp;#34;تكافل&amp;#34; لك ولعقارك للحماية وراحة البال
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/campai…&lt;/a&gt;</t>
+          <t>إنفاقك الأكبر ليس دائماً كما تعتقد.
+نصيحة: قسّم مصروفاتك الأسبوع الماضي إلى فئات، وقد تتفاجأ بما يتصدر القائمة.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2251,27 +2217,27 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:00 PM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-25T09:00:00Z</t>
+          <t>2026-04-27T20:00:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2280,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -2289,12 +2255,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2047933638453366977</t>
+          <t>2048770536407232972</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
+          <t>https://x.com/emiratesislamic/status/2048770536407232972</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2320,18 +2286,14 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>💸 Miles &amp; instant rewards and multiple redemption options
-👍 Cashback, discounts, golf, valet parking at select locations and much more
-Offer valid till 30 June 2026
-emiratesislamic.ae/en/offers…</t>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+#الإمارات_الإسلامي #الخدمات_المصرفية_للأعمال #الحلول_الرقمية.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
-👍 Cashback, discounts, golf, valet parking at select locations and much more
-Offer valid till 30 June 2026
-&lt;a href="https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_للأعمال"&gt;#الخدمات_المصرفية_للأعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الحلول_الرقمية"&gt;#الحلول_الرقمية&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2341,23 +2303,23 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T14:25:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_للأعمال', 'https://x.com/search?f=tweets&amp;q=%23الحلول_الرقمية']</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2367,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -2379,12 +2341,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2047933636054245884</t>
+          <t>2048770534553301143</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
+          <t>https://x.com/emiratesislamic/status/2048770534553301143</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2410,16 +2372,12 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
-🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
-✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها" الإمارات الإسلامي"، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
-🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
-✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها&amp;#34; الإمارات الإسلامي&amp;#34;، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2429,25 +2387,21 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T14:25:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['http://noon.com']</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>1</v>
       </c>
@@ -2455,10 +2409,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
@@ -2467,12 +2421,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2047933633118228811</t>
+          <t>2048770531961327711</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
+          <t>https://x.com/emiratesislamic/status/2048770531961327711</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2498,18 +2452,12 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
-👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
-يسري العرض لغاية 30 يونيو 2026
-emiratesislamic.ae/ar/offers…</t>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
-👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
-يسري العرض لغاية 30 يونيو 2026
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -2519,25 +2467,21 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 7:00 AM UTC</t>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-04-25T07:00:00Z</t>
+          <t>2026-04-27T14:25:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
         <v>1</v>
       </c>
@@ -2548,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -2557,12 +2501,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2047918534362030486</t>
+          <t>2048770529725681780</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
+          <t>https://x.com/emiratesislamic/status/2048770529725681780</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2588,12 +2532,12 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
+          <t>Emirates Islamic’s API Banking helps businesses optimise operations with seamless integration, real-time control, and smarter cash management, all within their existing systems.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
+          <t>Emirates Islamic’s API Banking helps businesses optimise operations with seamless integration, real-time control, and smarter cash management, all within their existing systems.</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -2603,32 +2547,2224 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 6:00 AM UTC</t>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-04-25T06:00:00Z</t>
+          <t>2026-04-27T14:25:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2048717801733476487</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717801733476487</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>We appreciate your contact. To assist you effectively by phone, we kindly request that you provide your registered mobile number.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>We appreciate your contact. To assist you effectively by phone, we kindly request that you provide your registered mobile number.</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:56:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2048717683068146026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717683068146026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2048717639627751785</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717639627751785</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2048717608422187229</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717608422187229</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2048716097206079817</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048716097206079817</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>['Allapichai25998']</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:49:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2048703707424940064</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707424940064</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2048703707408175195</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707408175195</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2048703704107205039</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703704107205039</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2048703703754932480</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703703754932480</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2048652591291093449</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652591291093449</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2048652578930507953</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652578930507953</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
+👍Get AED 500 guaranteed welcome bonus*
+💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp; education spends</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
+👍Get AED 500 guaranteed welcome bonus*
+💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp;amp; education spends</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2048652535938887711</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652535938887711</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2048652524018651430</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652524018651430</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
+👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
+💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
+👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
+💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2048643306221957276</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048643306221957276</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2048643305903202426</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048643305903202426</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>شركات الطيران وخدمات التوصيل وهيئة الطرق والمواصلات لديها تطبيقات رسمية. استخدمها مباشرة وتجنب الروابط المشبوهة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>شركات الطيران وخدمات التوصيل وهيئة الطرق والمواصلات لديها تطبيقات رسمية. استخدمها مباشرة وتجنب الروابط المشبوهة.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2048630676312768835</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048630676312768835</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>['TariqAziz717052']</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 5:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-04-27T05:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2048770536407232972</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770536407232972</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+#الإمارات_الإسلامي #الخدمات_المصرفية_للأعمال #الحلول_الرقمية.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_للأعمال"&gt;#الخدمات_المصرفية_للأعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الحلول_الرقمية"&gt;#الحلول_الرقمية&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_للأعمال', 'https://x.com/search?f=tweets&amp;q=%23الحلول_الرقمية']</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2048770534553301143</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770534553301143</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها" الإمارات الإسلامي"، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها&amp;#34; الإمارات الإسلامي&amp;#34;، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2048770531961327711</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770531961327711</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2048724846792855697</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt/status/2048724846792855697</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NazzysCt</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Janyt - 10XV</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Number dm’ed as requested</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Number dm’ed as requested</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 11:24 AM UTC</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-04-27T11:24:00Z</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2048703707424940064</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707424940064</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2048703707408175195</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707408175195</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2048652591291093449</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652591291093449</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2048652535938887711</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652535938887711</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2048641511525585317</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://x.com/Allapichai25998/status/2048641511525585317</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/Allapichai25998</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Allapichai25998</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sahul Allapichai</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 5:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-04-27T05:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,43 +541,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2048954465978339486</t>
+          <t>2049111447146303668</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2048954465978339486</t>
+          <t>https://x.com/dubaikeyinsight/status/2049111447146303668</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas</t>
+          <t>https://x.com/dubaikeyinsight</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>gold_hadas</t>
+          <t>dubaikeyinsight</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nicholas MOLODYKO, writer</t>
+          <t>Dubai Key Insights</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2036534120185307136/MfnTsiax_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals tradingview.com/news/reuters…</t>
+          <t>Emirates Islamic launched Sharia-compliant digital gold and silver trading, giving customers secure online access to precious metals through its banking platform.
+#UAE #Gold #IslamicFinance #Investment #News</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/"&gt;tradingview.com/news/reuters…&lt;/a&gt;</t>
+          <t>Emirates Islamic launched Sharia-compliant digital gold and silver trading, giving customers secure online access to precious metals through its banking platform.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Gold"&gt;#Gold&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicFinance"&gt;#IslamicFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investment"&gt;#Investment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23News"&gt;#News&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -587,23 +589,23 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 28, 2026 · 2:36 AM UTC</t>
+          <t>Apr 28, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-28T02:36:00Z</t>
+          <t>2026-04-28T13:00:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Gold', 'https://x.com/search?f=tweets&amp;q=%23IslamicFinance', 'https://x.com/search?f=tweets&amp;q=%23Investment', 'https://x.com/search?f=tweets&amp;q=%23News']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -616,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -625,43 +627,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2048953588357963815</t>
+          <t>2049095187004064146</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2048953588357963815</t>
+          <t>https://x.com/ForumRemittance/status/2049095187004064146</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas</t>
+          <t>https://x.com/ForumRemittance</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>gold_hadas</t>
+          <t>ForumRemittance</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nicholas MOLODYKO, writer</t>
+          <t>World Remittance Action Forum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1942959686417891328/FNdImGgE_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading gulfnews.com/business/bankin…</t>
+          <t>Emirates Islamic, a leading Islamic financial institution in the United Arab Emirates, has launched a Shari’ah-compliant digital investment solution in gold and silver, integrated into its EI+ Mobile Banking App for seamless investing.#Fintech #IslamicBanking #UAE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
+          <t>Emirates Islamic, a leading Islamic financial institution in the United Arab Emirates, has launched a Shari’ah-compliant digital investment solution in gold and silver, integrated into its EI+ Mobile Banking App for seamless investing.&lt;a href="/search?f=tweets&amp;amp;q=%23Fintech"&gt;#Fintech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicBanking"&gt;#IslamicBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -671,27 +673,27 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 28, 2026 · 2:32 AM UTC</t>
+          <t>Apr 28, 2026 · 11:55 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-28T02:32:00Z</t>
+          <t>2026-04-28T11:55:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Fintech', 'https://x.com/search?f=tweets&amp;q=%23IslamicBanking', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -700,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -709,43 +711,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2048928610338144280</t>
+          <t>2049086022823411801</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2048928610338144280</t>
+          <t>https://x.com/IslamFinance/status/2049086022823411801</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas</t>
+          <t>https://x.com/IslamFinance</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>gold_hadas</t>
+          <t>IslamFinance</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nicholas MOLODYKO, writer</t>
+          <t>Michael Gassner</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/143219042/gassner_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals mediaoffice.ae/en/news/2026/…</t>
+          <t>Emirates Islamic launches Sharia-compliant digital gold and silver investment - Gulf News dlvr.it/TSGHQj</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic"&gt;mediaoffice.ae/en/news/2026/…&lt;/a&gt;</t>
+          <t>Emirates Islamic launches Sharia-compliant digital gold and silver investment - Gulf News &lt;a href="http://dlvr.it/TSGHQj"&gt;dlvr.it/TSGHQj&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -755,23 +757,23 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 28, 2026 · 12:53 AM UTC</t>
+          <t>Apr 28, 2026 · 11:19 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-28T00:53:00Z</t>
+          <t>2026-04-28T11:19:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic']</t>
+          <t>['http://dlvr.it/TSGHQj']</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -784,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -793,86 +795,84 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2048838102010019915</t>
+          <t>2049084637171839232</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejinsight/status/2048838102010019915</t>
+          <t>https://x.com/evija_klapare/status/2049084637171839232</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejinsight</t>
+          <t>https://x.com/evija_klapare</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>khaleejinsight</t>
+          <t>evija_klapare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Khaleej Business Insight</t>
+          <t>callmeSafia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1900814841868394496/B-nstVph_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1956274391773265926/8-rf3O3d_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Emirates Islamic Launches Digital Gold Trading via Mobile App khaleejbusinessinsight.com/e… via @khaleejbusinessinsight.com 
-Emirates Islamic introduces digital gold trading via its mobile app, making precious metal investing more accessible and flexible.
-#DigitalGold #EmiratesIslamic</t>
+          <t>Kids in United Kingdom aren’t forced to study Islam they do basic Religious Education covering multiple beliefs. No one’s converting them.
+In United Arab Emirates, Islamic Studies is for Muslim students, and others are exempt. Different system you idiot</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Emirates Islamic Launches Digital Gold Trading via Mobile App &lt;a href="https://khaleejbusinessinsight.com/emirates-islamic-launches-digital-gold-trading-via-mobile-app/"&gt;khaleejbusinessinsight.com/e…&lt;/a&gt; via @khaleejbusinessinsight.com 
-Emirates Islamic introduces digital gold trading via its mobile app, making precious metal investing more accessible and flexible.
-&lt;a href="/search?f=tweets&amp;amp;q=%23DigitalGold"&gt;#DigitalGold&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>Kids in United Kingdom aren’t forced to study Islam they do basic Religious Education covering multiple beliefs. No one’s converting them.
+In United Arab Emirates, Islamic Studies is for Muslim students, and others are exempt. Different system you idiot</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['saif_aldareei']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:54 PM UTC</t>
+          <t>Apr 28, 2026 · 11:13 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-27T18:54:00Z</t>
+          <t>2026-04-28T11:13:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://khaleejbusinessinsight.com/emirates-islamic-launches-digital-gold-trading-via-mobile-app/', 'https://x.com/search?f=tweets&amp;q=%23DigitalGold', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -881,43 +881,55 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2048792635020612079</t>
+          <t>2049071045752111126</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2048792635020612079</t>
+          <t>https://x.com/emiratesislamic/status/2049071045752111126</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>gold_hadas</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nicholas MOLODYKO, writer</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Emirates Islamic Becomes First Islamic Bank In The UAE To Offer Digital Investment In Precious Metals menafn.com/1111036523/Emirat…</t>
+          <t>💸 Weekly cash prize of AED 50,000
+💸 Daily cash prize of AED 1,000 for Kunooz Youth account holders
+🌟Earn quarterly profit
+Terms &amp; Conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Emirates Islamic Becomes First Islamic Bank In The UAE To Offer Digital Investment In Precious Metals &lt;a href="https://menafn.com/1111036523/Emirates-Islamic-Becomes-First-Islamic-Bank-In-The-UAE-To-Offer-Digital-Investment-In-Precious-Metals"&gt;menafn.com/1111036523/Emirat…&lt;/a&gt;</t>
+          <t>💸 Weekly cash prize of AED 50,000
+💸 Daily cash prize of AED 1,000 for Kunooz Youth account holders
+🌟Earn quarterly profit
+Terms &amp;amp; Conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=kunooz_account"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -927,27 +939,27 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 3:53 PM UTC</t>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-27T15:53:00Z</t>
+          <t>2026-04-28T10:19:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://menafn.com/1111036523/Emirates-Islamic-Becomes-First-Islamic-Bank-In-The-UAE-To-Offer-Digital-Investment-In-Precious-Metals']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=kunooz_account', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -956,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -965,77 +977,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2048773845776310425</t>
+          <t>2049065369416159269</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2048773845776310425</t>
+          <t>https://x.com/Thefatim2/status/2049065369416159269</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews</t>
+          <t>https://x.com/Thefatim2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GCCBusinessNews</t>
+          <t>Thefatim2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GCC Business News</t>
+          <t>Fatima.M</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1253796411872862212/h2Q8-9rJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1664194240094543875/XH5sOaq-_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Emirates Islamic to offer digital investment in precious metals
-gccbusinessnews.com/emirates…
-#EmiratesIslamic #GoldInvestment #SilverInvestment #ShariahCompliant #DigitalBanking #PreciousMetals #WealthManagement #GCCBusinessNews @emiratesislamic</t>
+          <t>ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Emirates Islamic to offer digital investment in precious metals
-&lt;a href="https://www.gccbusinessnews.com/emirates-islamic-offers-digital-investment/"&gt;gccbusinessnews.com/emirates…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GoldInvestment"&gt;#GoldInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SilverInvestment"&gt;#SilverInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ShariahCompliant"&gt;#ShariahCompliant&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalBanking"&gt;#DigitalBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PreciousMetals"&gt;#PreciousMetals&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23WealthManagement"&gt;#WealthManagement&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GCCBusinessNews"&gt;#GCCBusinessNews&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
+          <t>ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:38 PM UTC</t>
+          <t>Apr 28, 2026 · 9:57 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-27T14:38:00Z</t>
+          <t>2026-04-28T09:57:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://www.gccbusinessnews.com/emirates-islamic-offers-digital-investment/', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23GoldInvestment', 'https://x.com/search?f=tweets&amp;q=%23SilverInvestment', 'https://x.com/search?f=tweets&amp;q=%23ShariahCompliant', 'https://x.com/search?f=tweets&amp;q=%23DigitalBanking', 'https://x.com/search?f=tweets&amp;q=%23PreciousMetals', 'https://x.com/search?f=tweets&amp;q=%23WealthManagement', 'https://x.com/search?f=tweets&amp;q=%23GCCBusinessNews', 'https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1044,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1053,67 +1061,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2048747126566641772</t>
+          <t>2049058620474593505</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/gentle_arch/status/2048747126566641772</t>
+          <t>https://x.com/emiratesislamic/status/2049058620474593505</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/gentle_arch</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>gentle_arch</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mo FiraaS</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1867089865558347776/lkpOodzk_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>يعني نشتري وسبيكة تصل عندهم ولا في توصيل؟؟؟</t>
+          <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>يعني نشتري وسبيكة تصل عندهم ولا في توصيل؟؟؟</t>
+          <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['DXBMediaOffice', 'emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 12:52 PM UTC</t>
+          <t>Apr 28, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-27T12:52:00Z</t>
+          <t>2026-04-28T09:30:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1128,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1137,12 +1141,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2048724846792855697</t>
+          <t>2049032607812497463</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt/status/2048724846792855697</t>
+          <t>https://x.com/NazzysCt/status/2049032607812497463</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1168,42 +1172,42 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Number dm’ed as requested</t>
+          <t>@emiratesislamic i request senior review and reconsideration. I still hope Emirates Islamic will value long-term customers and show flexibility in exceptional circumstances.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Number dm’ed as requested</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; i request senior review and reconsideration. I still hope Emirates Islamic will value long-term customers and show flexibility in exceptional circumstances.</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 11:24 AM UTC</t>
+          <t>Apr 28, 2026 · 7:46 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-27T11:24:00Z</t>
+          <t>2026-04-28T07:46:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1212,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1221,43 +1225,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2048711386818084907</t>
+          <t>2049032421459521586</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/Ldyheart/status/2048711386818084907</t>
+          <t>https://x.com/NazzysCt/status/2049032421459521586</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/Ldyheart</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ldyheart</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RV Global Reset</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2016603167585087489/50LxYE_N_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Buy, sell gold online: Emirates Islamic launches UAE's first digital investment service khaleejtimes.com/business/em…</t>
+          <t>@emiratesislamic I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Buy, sell gold online: Emirates Islamic launches UAE&amp;#39;s first digital investment service &lt;a href="https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1267,27 +1271,27 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:30 AM UTC</t>
+          <t>Apr 28, 2026 · 7:46 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-27T10:30:00Z</t>
+          <t>2026-04-28T07:46:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>['https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1296,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1305,45 +1309,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2048699606029234189</t>
+          <t>2049032216387428461</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2048699606029234189</t>
+          <t>https://x.com/NazzysCt/status/2049032216387428461</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>khaleejtimes</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Khaleej Times</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1662009811242831874/ZUTWSfk4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Buy, sell gold online: Emirates Islamic launches UAE's first digital investment service
-khaleejtimes.com/business/em…</t>
+          <t>@emiratesislamic I respectfully request Emirates Islamic to review this case beyond a rigid once per year rule. This is a genuine hardship situation, and the charge itself resulted from interest, not overspending.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Buy, sell gold online: Emirates Islamic launches UAE&amp;#39;s first digital investment service
-&lt;a href="https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I respectfully request Emirates Islamic to review this case beyond a rigid once per year rule. This is a genuine hardship situation, and the charge itself resulted from interest, not overspending.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1353,36 +1355,36 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 9:43 AM UTC</t>
+          <t>Apr 28, 2026 · 7:45 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-27T09:43:00Z</t>
+          <t>2026-04-28T07:45:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2309</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1391,73 +1393,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2048694049578574033</t>
+          <t>2049032023512416715</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/khalifaa_rashed/status/2048694049578574033</t>
+          <t>https://x.com/NazzysCt/status/2049032023512416715</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/khalifaa_rashed</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>khalifaa_rashed</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Khalef Saad</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1902376067718848512/dbP8oWQE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>استثمار رقمي فـ الذهب والفضة بطريقة آمنة ومتوافقة مع الشريعة يعطي ثقة أكبر للمتعاملين</t>
+          <t>@emiratesislamic Despite explaining everything in detail, the response I received was purely policy-based with no consideration for customer history, intent, or exceptional hardship. This was very disappointing and felt dismissive.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>استثمار رقمي فـ الذهب والفضة بطريقة آمنة ومتوافقة مع الشريعة يعطي ثقة أكبر للمتعاملين</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Despite explaining everything in detail, the response I received was purely policy-based with no consideration for customer history, intent, or exceptional hardship. This was very disappointing and felt dismissive.</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>['DXBMediaOffice', 'emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 9:21 AM UTC</t>
+          <t>Apr 28, 2026 · 7:44 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-27T09:21:00Z</t>
+          <t>2026-04-28T07:44:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1466,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1475,73 +1477,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2048690739530412259</t>
+          <t>2049031931510345961</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/bde__ir/status/2048690739530412259</t>
+          <t>https://x.com/NazzysCt/status/2049031931510345961</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/bde__ir</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>bde__ir</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>بدر ال مشاري.</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1866799615325929472/IQ77nzLh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>"الذهب والفضة.. بين يديك بضغطة زر! خطوة ذكية من 'الإمارات الإسلامي' تدمج بين الأمان الشرعي والحلول الرقمية السهلة. الآن أصبح الاستثمار في المعادن الثمينة متاحاً للجميع بسلاسة وموثوقية عالية عبر التطبيق. 📱⚖️ابتكار يعزز مكانة الصيرفة الإسلامية كقائد للتحول الرقمي في المنطقة. 🚀🇦🇪</t>
+          <t>@emiratesislamic Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>&amp;#34;الذهب والفضة.. بين يديك بضغطة زر! خطوة ذكية من &amp;#39;الإمارات الإسلامي&amp;#39; تدمج بين الأمان الشرعي والحلول الرقمية السهلة. الآن أصبح الاستثمار في المعادن الثمينة متاحاً للجميع بسلاسة وموثوقية عالية عبر التطبيق. 📱⚖️ابتكار يعزز مكانة الصيرفة الإسلامية كقائد للتحول الرقمي في المنطقة. 🚀🇦🇪</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['DXBMediaOffice', 'emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 9:08 AM UTC</t>
+          <t>Apr 28, 2026 · 7:44 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-27T09:08:00Z</t>
+          <t>2026-04-28T07:44:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1550,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>101</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1559,43 +1561,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2048689865970348293</t>
+          <t>2049031792318161136</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2048689865970348293</t>
+          <t>https://x.com/NazzysCt/status/2049031792318161136</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DXBMediaOffice</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubai Media Office</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526475569885548546/wQzde3FB_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering, a first-of-its-kind by an Islamic bank in the UAE, empowers customers to buy and sell certified physical gold and silver bars in a secure environment, providing a convenient way to diversify their portfolios and preserve investment value.</t>
+          <t>@emiratesislamic I have been your customer for more than 10 years and have never defaulted, never relied on repeated waivers, and always maintained payments responsibly. My track record reflects genuine financial discipline.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering, a first-of-its-kind by an Islamic bank in the UAE, empowers customers to buy and sell certified physical gold and silver bars in a secure environment, providing a convenient way to diversify their portfolios and preserve investment value.</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have been your customer for more than 10 years and have never defaulted, never relied on repeated waivers, and always maintained payments responsibly. My track record reflects genuine financial discipline.</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1605,32 +1607,36 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 9:05 AM UTC</t>
+          <t>Apr 28, 2026 · 7:43 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-27T09:05:00Z</t>
+          <t>2026-04-28T07:43:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4360</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1639,51 +1645,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2048687555772666020</t>
+          <t>2049031681420738907</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2048687555772666020</t>
+          <t>https://x.com/NazzysCt/status/2049031681420738907</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FintechGate1</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» أول مصرف إسلامي في دولة الإمارات العربية المتحدة يطلق حلول رقمية للاستثمار في المعادن الثمينة
-fintechgate.net/sa1g | التفاصيل 
-@emiratesislamic
-#fintech_gate
-#الإمارات_الإسلامي #الإمارات_العربية_المتحدة #حلول_رقمية_للاستثمار  #المعادن_الثمينة</t>
+          <t>@emiratesislamic I clearly explained that this over-limit was not due to additional spending. It occurred because interest was applied to my card, which pushed the balance above the limit. This was not intentional usage, but a technical overrun.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» أول مصرف إسلامي في دولة الإمارات العربية المتحدة يطلق حلول رقمية للاستثمار في المعادن الثمينة
-&lt;a href="https://fintechgate.net/sa1g"&gt;fintechgate.net/sa1g&lt;/a&gt; | التفاصيل 
-&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_العربية_المتحدة"&gt;#الإمارات_العربية_المتحدة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حلول_رقمية_للاستثمار"&gt;#حلول_رقمية_للاستثمار&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23المعادن_الثمينة"&gt;#المعادن_الثمينة&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I clearly explained that this over-limit was not due to additional spending. It occurred because interest was applied to my card, which pushed the balance above the limit. This was not intentional usage, but a technical overrun.</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1698,22 +1696,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 8:55 AM UTC</t>
+          <t>Apr 28, 2026 · 7:43 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-27T08:55:00Z</t>
+          <t>2026-04-28T07:43:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>['https://fintechgate.net/sa1g', 'https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_العربية_المتحدة', 'https://x.com/search?f=tweets&amp;q=%23حلول_رقمية_للاستثمار', 'https://x.com/search?f=tweets&amp;q=%23المعادن_الثمينة']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1722,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -1731,12 +1729,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2048679648536752433</t>
+          <t>2049031529234612558</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt/status/2048679648536752433</t>
+          <t>https://x.com/NazzysCt/status/2049031529234612558</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1762,14 +1760,12 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>@emiratesislamic I would truly appreciate it if you could make an exception and reconsider reversing this charge as a gesture of goodwill. Your support during this time would mean a lot.
-Thank you.</t>
+          <t>Dear @EmiratesIslamic, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I would truly appreciate it if you could make an exception and reconsider reversing this charge as a gesture of goodwill. Your support during this time would mean a lot.
-Thank you.</t>
+          <t>Dear &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt;, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1784,12 +1780,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 8:24 AM UTC</t>
+          <t>Apr 28, 2026 · 7:42 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-27T08:24:00Z</t>
+          <t>2026-04-28T07:42:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -1808,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1817,45 +1813,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2048679565225324653</t>
+          <t>2049031359063310351</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt/status/2048679565225324653</t>
+          <t>https://x.com/mirabusinessfm/status/2049031359063310351</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt</t>
+          <t>https://x.com/mirabusinessfm</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NazzysCt</t>
+          <t>mirabusinessfm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Janyt - 10XV</t>
+          <t>Mira Business FM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1899053705057517571/DRCaJqKX_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>I fully understand the policy, however I’m currently facing financial difficulties due to ongoing war-related impacts affecting my payouts. I’ve been a loyal customer for over 10 years and have always maintained my relationship in good faith.
-@emiratesislamic</t>
+          <t>Emirates Islamic launches digital gold and silver trading. 🪙📱
+Customers can now trade precious metals via the EI+ app in a fully Shariah-compliant service.
+#UAE #Banking #Gold #MiraBusinessFM 🎙️</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I fully understand the policy, however I’m currently facing financial difficulties due to ongoing war-related impacts affecting my payouts. I’ve been a loyal customer for over 10 years and have always maintained my relationship in good faith.
-&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
+          <t>Emirates Islamic launches digital gold and silver trading. 🪙📱
+Customers can now trade precious metals via the EI+ app in a fully Shariah-compliant service.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Gold"&gt;#Gold&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MiraBusinessFM"&gt;#MiraBusinessFM&lt;/a&gt; 🎙️</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1870,22 +1868,22 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 8:24 AM UTC</t>
+          <t>Apr 28, 2026 · 7:41 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-27T08:24:00Z</t>
+          <t>2026-04-28T07:41:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Gold', 'https://x.com/search?f=tweets&amp;q=%23MiraBusinessFM']</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1894,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -1903,45 +1901,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2048679400204644634</t>
+          <t>2049022486218715385</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt/status/2048679400204644634</t>
+          <t>https://x.com/Thefatim2/status/2049022486218715385</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt</t>
+          <t>https://x.com/Thefatim2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NazzysCt</t>
+          <t>Thefatim2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Janyt - 10XV</t>
+          <t>Fatima.M</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1664194240094543875/XH5sOaq-_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Dear @EmiratesIslamic,
-I kindly request your support in waiving the over-limit charge applied to my card. I contacted customer service, but was informed that a waiver can only be requested once per year since my last request was in July.</t>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dear &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt;,
-I kindly request your support in waiving the over-limit charge applied to my card. I contacted customer service, but was informed that a waiver can only be requested once per year since my last request was in July.</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; اسوء بنك ، اسوء بنك ، اسوء بنك</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -1956,12 +1952,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 8:23 AM UTC</t>
+          <t>Apr 28, 2026 · 7:06 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-27T08:23:00Z</t>
+          <t>2026-04-28T07:06:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -1971,7 +1967,7 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1980,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1989,12 +1985,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2048643306221957276</t>
+          <t>2049008966907118061</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048643306221957276</t>
+          <t>https://x.com/emiratesislamic/status/2049008966907118061</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2020,20 +2016,14 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Airlines, courier services, and RTA all have official apps - use them directly.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>Having a clear plan for your money can make everyday decisions easier. Managing spending thoughtfully helps reduce stress and keeps you on track toward your goals.
+#Finwell #FinancialWellbeing #EmiratesIslamic #Budgeting</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Airlines, courier services, and RTA all have official apps - use them directly.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Having a clear plan for your money can make everyday decisions easier. Managing spending thoughtfully helps reduce stress and keeps you on track toward your goals.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Budgeting"&gt;#Budgeting&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2043,36 +2033,36 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:00 AM UTC</t>
+          <t>Apr 28, 2026 · 6:13 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-27T06:00:00Z</t>
+          <t>2026-04-28T06:13:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Budgeting']</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -2081,43 +2071,53 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2048641511525585317</t>
+          <t>2049005694838301088</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/Allapichai25998/status/2048641511525585317</t>
+          <t>https://x.com/emiratesislamic/status/2049005694838301088</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/Allapichai25998</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Allapichai25998</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sahul Allapichai</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>@emiratesislamic Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+          <t>Your biggest expense isn’t always what you think.
+Tip:
+Group your last week’s spending into categories.
+You might be surprised by what comes first.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+          <t>Your biggest expense isn’t always what you think.
+Tip:
+Group your last week’s spending into categories.
+You might be surprised by what comes first.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2127,27 +2127,27 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 5:52 AM UTC</t>
+          <t>Apr 28, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-27T05:52:00Z</t>
+          <t>2026-04-28T06:00:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2048854699953021336</t>
+          <t>2048990595058721180</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048854699953021336</t>
+          <t>https://x.com/emiratesislamic/status/2048990595058721180</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2196,18 +2196,18 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>إنفاقك الأكبر ليس دائماً كما تعتقد.
-نصيحة: قسّم مصروفاتك الأسبوع الماضي إلى فئات، وقد تتفاجأ بما يتصدر القائمة.
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+Your Weekly Perspective. A step toward a more mindful financial week.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>إنفاقك الأكبر ليس دائماً كما تعتقد.
-نصيحة: قسّم مصروفاتك الأسبوع الماضي إلى فئات، وقد تتفاجأ بما يتصدر القائمة.
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
 &lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+Your Weekly Perspective. A step toward a more mindful financial week.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2217,23 +2217,23 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 8:00 PM UTC</t>
+          <t>Apr 28, 2026 · 5:00 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-27T20:00:00Z</t>
+          <t>2026-04-28T05:00:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -2255,45 +2255,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2048770536407232972</t>
+          <t>2048954465978339486</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048770536407232972</t>
+          <t>https://x.com/gold_hadas/status/2048954465978339486</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
-#الإمارات_الإسلامي #الخدمات_المصرفية_للأعمال #الحلول_الرقمية.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals tradingview.com/news/reuters…</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_للأعمال"&gt;#الخدمات_المصرفية_للأعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الحلول_الرقمية"&gt;#الحلول_الرقمية&lt;/a&gt;.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/"&gt;tradingview.com/news/reuters…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2303,23 +2301,23 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>Apr 28</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+          <t>Apr 28, 2026 · 2:36 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-27T14:25:00Z</t>
+          <t>2026-04-28T02:36:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_للأعمال', 'https://x.com/search?f=tweets&amp;q=%23الحلول_الرقمية']</t>
+          <t>['https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/']</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2329,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -2341,43 +2339,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2048770534553301143</t>
+          <t>2048953588357963815</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048770534553301143</t>
+          <t>https://x.com/gold_hadas/status/2048953588357963815</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها" الإمارات الإسلامي"، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها&amp;#34; الإمارات الإسلامي&amp;#34;، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2387,32 +2385,36 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>Apr 28</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+          <t>Apr 28, 2026 · 2:32 AM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-04-27T14:25:00Z</t>
+          <t>2026-04-28T02:32:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234']</t>
+        </is>
+      </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -2421,43 +2423,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2048770531961327711</t>
+          <t>2048928610338144280</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048770531961327711</t>
+          <t>https://x.com/gold_hadas/status/2048928610338144280</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals mediaoffice.ae/en/news/2026/…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic"&gt;mediaoffice.ae/en/news/2026/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -2467,23 +2469,27 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>Apr 28</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+          <t>Apr 28, 2026 · 12:53 AM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-04-27T14:25:00Z</t>
+          <t>2026-04-28T00:53:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic']</t>
+        </is>
+      </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2492,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -2501,12 +2507,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2048770529725681780</t>
+          <t>2049071045752111126</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048770529725681780</t>
+          <t>https://x.com/emiratesislamic/status/2049071045752111126</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2532,12 +2538,24 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s API Banking helps businesses optimise operations with seamless integration, real-time control, and smarter cash management, all within their existing systems.</t>
+          <t>💸 Weekly cash prize of AED 50,000
+💸 Daily cash prize of AED 1,000 for Kunooz Youth account holders
+🌟Earn quarterly profit
+Terms &amp; Conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s API Banking helps businesses optimise operations with seamless integration, real-time control, and smarter cash management, all within their existing systems.</t>
+          <t>💸 Weekly cash prize of AED 50,000
+💸 Daily cash prize of AED 1,000 for Kunooz Youth account holders
+🌟Earn quarterly profit
+Terms &amp;amp; Conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=kunooz_account"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -2547,32 +2565,36 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-04-27T14:25:00Z</t>
+          <t>2026-04-28T10:19:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=kunooz_account', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -2581,12 +2603,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2048717801733476487</t>
+          <t>2049071043898139018</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048717801733476487</t>
+          <t>https://x.com/emiratesislamic/status/2049071043898139018</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2612,42 +2634,44 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>We appreciate your contact. To assist you effectively by phone, we kindly request that you provide your registered mobile number.</t>
+          <t>Open a Kunooz Millionaire Account today!
+💸 Monthly grand cash prize of AED 1,000,000
+💸 Quarterly grand cash prize of AED 1,000,000 for Priority and Private Banking customers
+💸 Monthly cash prize of AED 50,000 for Parents of Kunooz Youth account holders</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>We appreciate your contact. To assist you effectively by phone, we kindly request that you provide your registered mobile number.</t>
+          <t>Open a Kunooz Millionaire Account today!
+💸 Monthly grand cash prize of AED 1,000,000
+💸 Quarterly grand cash prize of AED 1,000,000 for Priority and Private Banking customers
+💸 Monthly cash prize of AED 50,000 for Parents of Kunooz Youth account holders</t>
         </is>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>['NazzysCt']</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:56 AM UTC</t>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-04-27T10:56:00Z</t>
+          <t>2026-04-28T10:19:00Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2656,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
@@ -2665,12 +2689,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2048717683068146026</t>
+          <t>2049071041889055148</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048717683068146026</t>
+          <t>https://x.com/emiratesislamic/status/2049071041889055148</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2696,40 +2720,52 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>💸 جائزة نقدية أسبوعياً بقيمة 50,000 درهم
+💸 جائزة نقدية يومياً بقيمة 1,000 درهم لجميع أصحاب حساب كنوز الذين لديهم أيضاً حساب قاصر
+🌟اكسب أرباحاً كل ربع سنة
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+emiratesislamic.ae/ar/offers…
+#الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>💸 جائزة نقدية أسبوعياً بقيمة 50,000 درهم
+💸 جائزة نقدية يومياً بقيمة 1,000 درهم لجميع أصحاب حساب كنوز الذين لديهم أيضاً حساب قاصر
+🌟اكسب أرباحاً كل ربع سنة
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=kunooz_account"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>['NazzysCt']</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-04-27T10:55:00Z</t>
+          <t>2026-04-28T10:19:00Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=kunooz_account', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
@@ -2740,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -2749,12 +2785,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2048717639627751785</t>
+          <t>2049071039880085897</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048717639627751785</t>
+          <t>https://x.com/emiratesislamic/status/2049071039880085897</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2780,51 +2816,53 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>افتح حساب كنوز الميليونير اليوم.
+💸جائزة نقدية كبرى شهرياً بقيمة 1,000,000 درهم
+💸جائزة نقدية كبرى ربع سنوية بقيمة 1,000,000 درهم لعملاء الخدمات المصرفية المميزة والخاصة
+💸 جائزة نقدية شهرياً بقيمة 50,000 درهم لأولياء أمور أصحاب حساب كنوز قاصر</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>افتح حساب كنوز الميليونير اليوم.
+💸جائزة نقدية كبرى شهرياً بقيمة 1,000,000 درهم
+💸جائزة نقدية كبرى ربع سنوية بقيمة 1,000,000 درهم لعملاء الخدمات المصرفية المميزة والخاصة
+💸 جائزة نقدية شهرياً بقيمة 50,000 درهم لأولياء أمور أصحاب حساب كنوز قاصر</t>
         </is>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>['NazzysCt']</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-04-27T10:55:00Z</t>
+          <t>2026-04-28T10:19:00Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
@@ -2833,12 +2871,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2048717608422187229</t>
+          <t>2049068445883314237</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048717608422187229</t>
+          <t>https://x.com/emiratesislamic/status/2049068445883314237</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2864,12 +2902,14 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -2878,22 +2918,22 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>['NazzysCt']</t>
+          <t>['Thefatim2']</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+          <t>Apr 28, 2026 · 10:09 AM UTC</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-04-27T10:55:00Z</t>
+          <t>2026-04-28T10:09:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -2917,12 +2957,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2048716097206079817</t>
+          <t>2049067669018542591</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048716097206079817</t>
+          <t>https://x.com/emiratesislamic/status/2049067669018542591</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2948,36 +2988,38 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>['Allapichai25998']</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:49 AM UTC</t>
+          <t>Apr 28, 2026 · 10:06 AM UTC</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-04-27T10:49:00Z</t>
+          <t>2026-04-28T10:06:00Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
@@ -2986,13 +3028,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
@@ -3001,12 +3043,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2048703707424940064</t>
+          <t>2049067330747973658</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048703707424940064</t>
+          <t>https://x.com/emiratesislamic/status/2049067330747973658</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3032,22 +3074,20 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-emiratesislamic.ae/en/offers…</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -3057,23 +3097,23 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 10:04 AM UTC</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-04-27T10:00:00Z</t>
+          <t>2026-04-28T10:04:00Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3083,10 +3123,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32">
@@ -3095,12 +3135,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2048703707408175195</t>
+          <t>2049067328634007759</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048703707408175195</t>
+          <t>https://x.com/emiratesislamic/status/2049067328634007759</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3126,22 +3166,14 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>🚗 خدمة صف السيارات
-🛫 الدخول إلى صالات المطارات
-💳 بطاقة معدنية بتصميم فريد
-وغير ذلك الكثير
-📅 يسري العرض لغاية 31 مايو 2026
-emiratesislamic.ae/ar/offers…</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>🚗 خدمة صف السيارات
-🛫 الدخول إلى صالات المطارات
-💳 بطاقة معدنية بتصميم فريد
-وغير ذلك الكثير
-📅 يسري العرض لغاية 31 مايو 2026
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="K32" t="b">
@@ -3151,36 +3183,32 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 10:04 AM UTC</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-04-27T10:00:00Z</t>
+          <t>2026-04-28T10:04:00Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
@@ -3189,12 +3217,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2048703704107205039</t>
+          <t>2049067325454696477</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048703704107205039</t>
+          <t>https://x.com/emiratesislamic/status/2049067325454696477</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3220,18 +3248,20 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
-🍔 خصم لغاية %50 على طلبات</t>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
-🍔 خصم لغاية %50 على طلبات</t>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -3241,21 +3271,25 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 10:04 AM UTC</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-04-27T10:00:00Z</t>
+          <t>2026-04-28T10:04:00Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
@@ -3263,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
@@ -3275,12 +3309,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2048703703754932480</t>
+          <t>2049067320518013067</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048703703754932480</t>
+          <t>https://x.com/emiratesislamic/status/2049067320518013067</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3306,18 +3340,16 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
         </is>
       </c>
       <c r="K34" t="b">
@@ -3327,17 +3359,17 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 10:04 AM UTC</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-04-27T10:00:00Z</t>
+          <t>2026-04-28T10:04:00Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr"/>
@@ -3349,10 +3381,10 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
@@ -3361,12 +3393,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2048652591291093449</t>
+          <t>2049060823264350309</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048652591291093449</t>
+          <t>https://x.com/emiratesislamic/status/2049060823264350309</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3392,61 +3424,51 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; Dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp; conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; Dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="K35" t="b">
         <v>0</v>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>['Thefatim2']</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+          <t>Apr 28, 2026 · 9:39 AM UTC</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-04-27T06:36:00Z</t>
+          <t>2026-04-28T09:39:00Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -3455,12 +3477,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2048652578930507953</t>
+          <t>2049058620474593505</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048652578930507953</t>
+          <t>https://x.com/emiratesislamic/status/2049058620474593505</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3486,16 +3508,12 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
-👍Get AED 500 guaranteed welcome bonus*
-💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp; education spends</t>
+          <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
-👍Get AED 500 guaranteed welcome bonus*
-💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp;amp; education spends</t>
+          <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -3505,32 +3523,32 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+          <t>Apr 28, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-04-27T06:36:00Z</t>
+          <t>2026-04-28T09:30:00Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
@@ -3539,12 +3557,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2048652535938887711</t>
+          <t>2049058613566574791</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048652535938887711</t>
+          <t>https://x.com/emiratesislamic/status/2049058613566574791</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3570,22 +3588,12 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك</t>
         </is>
       </c>
       <c r="K37" t="b">
@@ -3595,36 +3603,32 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+          <t>Apr 28, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-04-27T06:36:00Z</t>
+          <t>2026-04-28T09:30:00Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
-        </is>
-      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
@@ -3633,12 +3637,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2048652524018651430</t>
+          <t>2049038747560300619</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048652524018651430</t>
+          <t>https://x.com/emiratesislamic/status/2049038747560300619</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3664,51 +3668,51 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
-👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
-💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better...</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
-👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
-💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better...</t>
         </is>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+          <t>Apr 28, 2026 · 8:11 AM UTC</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-04-27T06:36:00Z</t>
+          <t>2026-04-28T08:11:00Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
         <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="39">
@@ -3717,12 +3721,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2048643306221957276</t>
+          <t>2049038707563356267</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048643306221957276</t>
+          <t>https://x.com/emiratesislamic/status/2049038707563356267</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3748,59 +3752,51 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Airlines, courier services, and RTA all have official apps - use them directly.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better  ..</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Airlines, courier services, and RTA all have official apps - use them directly.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better  ..</t>
         </is>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:00 AM UTC</t>
+          <t>Apr 28, 2026 · 8:11 AM UTC</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-04-27T06:00:00Z</t>
+          <t>2026-04-28T08:11:00Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
         <v>1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>59</v>
       </c>
     </row>
     <row r="40">
@@ -3809,12 +3805,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2048643305903202426</t>
+          <t>2049038663674102051</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048643305903202426</t>
+          <t>https://x.com/emiratesislamic/status/2049038663674102051</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3840,46 +3836,40 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>شركات الطيران وخدمات التوصيل وهيئة الطرق والمواصلات لديها تطبيقات رسمية. استخدمها مباشرة وتجنب الروابط المشبوهة.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>شركات الطيران وخدمات التوصيل وهيئة الطرق والمواصلات لديها تطبيقات رسمية. استخدمها مباشرة وتجنب الروابط المشبوهة.
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:00 AM UTC</t>
+          <t>Apr 28, 2026 · 8:11 AM UTC</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-04-27T06:00:00Z</t>
+          <t>2026-04-28T08:11:00Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
         <v>0</v>
       </c>
@@ -3890,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3899,12 +3889,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2048630676312768835</t>
+          <t>2049038553271706094</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048630676312768835</t>
+          <t>https://x.com/emiratesislamic/status/2049038553271706094</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3930,12 +3920,12 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K41" t="b">
@@ -3944,22 +3934,22 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>['TariqAziz717052']</t>
+          <t>['NazzysCt']</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 5:09 AM UTC</t>
+          <t>Apr 28, 2026 · 8:10 AM UTC</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-04-27T05:09:00Z</t>
+          <t>2026-04-28T08:10:00Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -3983,12 +3973,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2048770536407232972</t>
+          <t>2049038477354729744</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048770536407232972</t>
+          <t>https://x.com/emiratesislamic/status/2049038477354729744</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4014,42 +4004,40 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
-#الإمارات_الإسلامي #الخدمات_المصرفية_للأعمال #الحلول_الرقمية.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_للأعمال"&gt;#الخدمات_المصرفية_للأعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الحلول_الرقمية"&gt;#الحلول_الرقمية&lt;/a&gt;.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+          <t>Apr 28, 2026 · 8:10 AM UTC</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-04-27T14:25:00Z</t>
+          <t>2026-04-28T08:10:00Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_للأعمال', 'https://x.com/search?f=tweets&amp;q=%23الحلول_الرقمية']</t>
-        </is>
-      </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
         <v>0</v>
       </c>
@@ -4057,10 +4045,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -4069,12 +4057,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2048770534553301143</t>
+          <t>2049038428889665640</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048770534553301143</t>
+          <t>https://x.com/emiratesislamic/status/2049038428889665640</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4100,47 +4088,51 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها" الإمارات الإسلامي"، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها&amp;#34; الإمارات الإسلامي&amp;#34;، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K43" t="b">
         <v>0</v>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+          <t>Apr 28, 2026 · 8:10 AM UTC</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-04-27T14:25:00Z</t>
+          <t>2026-04-28T08:10:00Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
         <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -4149,12 +4141,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2048770531961327711</t>
+          <t>2049038389718958544</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048770531961327711</t>
+          <t>https://x.com/emiratesislamic/status/2049038389718958544</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4180,38 +4172,42 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+          <t>Apr 28, 2026 · 8:09 AM UTC</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-04-27T14:25:00Z</t>
+          <t>2026-04-28T08:09:00Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -4220,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -4229,43 +4225,43 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2048724846792855697</t>
+          <t>2049038326598934628</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt/status/2048724846792855697</t>
+          <t>https://x.com/emiratesislamic/status/2049038326598934628</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/NazzysCt</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NazzysCt</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Janyt - 10XV</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Number dm’ed as requested</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Number dm’ed as requested</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K45" t="b">
@@ -4274,22 +4270,22 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['NazzysCt']</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 11:24 AM UTC</t>
+          <t>Apr 28, 2026 · 8:09 AM UTC</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-04-27T11:24:00Z</t>
+          <t>2026-04-28T08:09:00Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr"/>
@@ -4313,12 +4309,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2048703707424940064</t>
+          <t>2049027263874637939</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048703707424940064</t>
+          <t>https://x.com/emiratesislamic/status/2049027263874637939</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4344,48 +4340,44 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-emiratesislamic.ae/en/offers…</t>
+          <t>متعاملنا العزيز ، نشكرك على اختيارك للإمارات الإسلامي للإستثمار. يرجى الضغط علي الرابط بالأسفل بموقعنا الرسمي للمزيد من البيانات اللازمه بخصوص عرض الإستثمار المتاح. 
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>متعاملنا العزيز ، نشكرك على اختيارك للإمارات الإسلامي للإستثمار. يرجى الضغط علي الرابط بالأسفل بموقعنا الرسمي للمزيد من البيانات اللازمه بخصوص عرض الإستثمار المتاح. 
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions/invest-in-gold-and-silver"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>['gentle_arch']</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 7:25 AM UTC</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-04-27T10:00:00Z</t>
+          <t>2026-04-28T07:25:00Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions/invest-in-gold-and-silver']</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -4395,10 +4387,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -4407,12 +4399,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2048703707408175195</t>
+          <t>2049009470156485096</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048703707408175195</t>
+          <t>https://x.com/emiratesislamic/status/2049009470156485096</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4438,22 +4430,12 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>🚗 خدمة صف السيارات
-🛫 الدخول إلى صالات المطارات
-💳 بطاقة معدنية بتصميم فريد
-وغير ذلك الكثير
-📅 يسري العرض لغاية 31 مايو 2026
-emiratesislamic.ae/ar/offers…</t>
+          <t>وضع خطة واضحة لأموالك يجعل قراراتك اليومية أسهل. إدارة الإنفاق بوعي تساعد على تقليل التوتر والحفاظ على مسارك نحو أهدافك.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>🚗 خدمة صف السيارات
-🛫 الدخول إلى صالات المطارات
-💳 بطاقة معدنية بتصميم فريد
-وغير ذلك الكثير
-📅 يسري العرض لغاية 31 مايو 2026
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>وضع خطة واضحة لأموالك يجعل قراراتك اليومية أسهل. إدارة الإنفاق بوعي تساعد على تقليل التوتر والحفاظ على مسارك نحو أهدافك.</t>
         </is>
       </c>
       <c r="K47" t="b">
@@ -4463,25 +4445,21 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 6:15 AM UTC</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-04-27T10:00:00Z</t>
+          <t>2026-04-28T06:15:00Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
         <v>0</v>
       </c>
@@ -4489,10 +4467,10 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
@@ -4501,12 +4479,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2048652591291093449</t>
+          <t>2049008966907118061</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048652591291093449</t>
+          <t>https://x.com/emiratesislamic/status/2049008966907118061</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4532,22 +4510,14 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; Dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp; conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>Having a clear plan for your money can make everyday decisions easier. Managing spending thoughtfully helps reduce stress and keeps you on track toward your goals.
+#Finwell #FinancialWellbeing #EmiratesIslamic #Budgeting</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; Dining
-💳1% cashback on other spends
-And much more.
-*Offer valid till 30 June 2026
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>Having a clear plan for your money can make everyday decisions easier. Managing spending thoughtfully helps reduce stress and keeps you on track toward your goals.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Budgeting"&gt;#Budgeting&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -4557,23 +4527,23 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+          <t>Apr 28, 2026 · 6:13 AM UTC</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-04-27T06:36:00Z</t>
+          <t>2026-04-28T06:13:00Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Budgeting']</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -4583,10 +4553,10 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
@@ -4595,12 +4565,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2048652535938887711</t>
+          <t>2049005694838301088</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048652535938887711</t>
+          <t>https://x.com/emiratesislamic/status/2049005694838301088</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4626,22 +4596,22 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>Your biggest expense isn’t always what you think.
+Tip:
+Group your last week’s spending into categories.
+You might be surprised by what comes first.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
-💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
-وغير ذلك الكثير
-* يسري العرض لغاية 30  يونيو 2026
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>Your biggest expense isn’t always what you think.
+Tip:
+Group your last week’s spending into categories.
+You might be surprised by what comes first.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K49" t="b">
@@ -4651,23 +4621,23 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+          <t>Apr 28, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-04-27T06:36:00Z</t>
+          <t>2026-04-28T06:00:00Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -4680,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
@@ -4689,82 +4659,964 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2048641511525585317</t>
+          <t>2048995156636893623</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/Allapichai25998/status/2048641511525585317</t>
+          <t>https://x.com/emiratesislamic/status/2048995156636893623</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/Allapichai25998</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Allapichai25998</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sahul Allapichai</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>@emiratesislamic Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 5:52 AM UTC</t>
+          <t>Apr 28, 2026 · 5:18 AM UTC</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-04-27T05:52:00Z</t>
+          <t>2026-04-28T05:18:00Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2048990595058721180</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048990595058721180</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+Your Weekly Perspective. A step toward a more mindful financial week.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+Your Weekly Perspective. A step toward a more mindful financial week.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-04-28T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2049071045752111126</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049071045752111126</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>💸 Weekly cash prize of AED 50,000
+💸 Daily cash prize of AED 1,000 for Kunooz Youth account holders
+🌟Earn quarterly profit
+Terms &amp; Conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>💸 Weekly cash prize of AED 50,000
+💸 Daily cash prize of AED 1,000 for Kunooz Youth account holders
+🌟Earn quarterly profit
+Terms &amp;amp; Conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=kunooz_account"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:19:00Z</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=kunooz_account', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2049071043898139018</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049071043898139018</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Open a Kunooz Millionaire Account today!
+💸 Monthly grand cash prize of AED 1,000,000
+💸 Quarterly grand cash prize of AED 1,000,000 for Priority and Private Banking customers
+💸 Monthly cash prize of AED 50,000 for Parents of Kunooz Youth account holders</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Open a Kunooz Millionaire Account today!
+💸 Monthly grand cash prize of AED 1,000,000
+💸 Quarterly grand cash prize of AED 1,000,000 for Priority and Private Banking customers
+💸 Monthly cash prize of AED 50,000 for Parents of Kunooz Youth account holders</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:19:00Z</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2049071041889055148</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049071041889055148</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>💸 جائزة نقدية أسبوعياً بقيمة 50,000 درهم
+💸 جائزة نقدية يومياً بقيمة 1,000 درهم لجميع أصحاب حساب كنوز الذين لديهم أيضاً حساب قاصر
+🌟اكسب أرباحاً كل ربع سنة
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+emiratesislamic.ae/ar/offers…
+#الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>💸 جائزة نقدية أسبوعياً بقيمة 50,000 درهم
+💸 جائزة نقدية يومياً بقيمة 1,000 درهم لجميع أصحاب حساب كنوز الذين لديهم أيضاً حساب قاصر
+🌟اكسب أرباحاً كل ربع سنة
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=kunooz_account"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:19 AM UTC</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:19:00Z</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/kunooz-millionaire-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=kunooz_account', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2049067330747973658</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049067330747973658</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:04 AM UTC</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:04:00Z</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2049067328634007759</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049067328634007759</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+        </is>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:04 AM UTC</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:04:00Z</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2049067325454696477</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049067325454696477</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
+⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:04 AM UTC</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:04:00Z</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-facebook&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2049065369416159269</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2049065369416159269</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Thefatim2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fatima.M</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1664194240094543875/XH5sOaq-_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
+        </is>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 9:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-04-28T09:57:00Z</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2049058620474593505</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049058620474593505</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
+        </is>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 9:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-04-28T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2049022486218715385</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Thefatim2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fatima.M</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1664194240094543875/XH5sOaq-_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; اسوء بنك ، اسوء بنك ، اسوء بنك</t>
+        </is>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 7:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-04-28T07:06:00Z</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="S60" t="n">
         <v>1</v>
       </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>9</v>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,43 +541,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2049499248727933034</t>
+          <t>2049808521357914559</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/renukavenkat1/status/2049499248727933034</t>
+          <t>https://x.com/alnuaimi1979/status/2049808521357914559</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/renukavenkat1</t>
+          <t>https://x.com/alnuaimi1979</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>renukavenkat1</t>
+          <t>alnuaimi1979</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Renuka Venkat Iyer</t>
+          <t>عبدالرحمن النعيمي 🇦🇪</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/884260219966156800/44H4GnwE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042510760056885249/w-Tb8Gep_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>@emiratesislamic extremely disappointing service from Emirates Islamic Bank. Still waiting for a replacement card since last 30 days. Tired of making calls to the customer service and listening to the same story over and over again. Speed up guys. We are in Dubai!!</t>
+          <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; extremely disappointing service from Emirates Islamic Bank. Still waiting for a replacement card since last 30 days. Tired of making calls to the customer service and listening to the same story over and over again. Speed up guys. We are in Dubai!!</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -587,17 +587,17 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 · 2:41 PM UTC</t>
+          <t>Apr 30, 2026 · 11:10 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-29T14:41:00Z</t>
+          <t>2026-04-30T11:10:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -625,43 +625,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2049457101265592397</t>
+          <t>2049768124615143524</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049457101265592397</t>
+          <t>https://x.com/dcgguide/status/2049768124615143524</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/dcgguide</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>dcgguide</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products, a metal Visa Signature Debit Card with higher withdrawal and POS limits,</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes blog.uaetoday.com/emirates-i…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp;amp; FX advisor, preferential pricing on products, a metal Visa Signature Debit Card with higher withdrawal and POS limits,</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes &lt;a href="https://blog.uaetoday.com/emirates-islamic-launches-tailored-banking-benefits-to-support-uaes-frontline-heroes/"&gt;blog.uaetoday.com/emirates-i…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -671,32 +671,36 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 · 11:53 AM UTC</t>
+          <t>Apr 30, 2026 · 8:29 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-29T11:53:00Z</t>
+          <t>2026-04-30T08:29:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://blog.uaetoday.com/emirates-islamic-launches-tailored-banking-benefits-to-support-uaes-frontline-heroes/']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -705,47 +709,57 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2049445318471639518</t>
+          <t>2049760670133178628</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049445318471639518</t>
+          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/blocknewsint</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>blocknewsint</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Block News International</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1881352530807959552/YV-Uq6jL_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Emirates Islamic has been awarded ‘Sustainable Finance Deal of the Year – Middle East’ at the Global Finance Sustainable Finance Awards 2026 for the issuance of the world’s first Sustainability‑Linked Financing Sukuk.
-Read the article:
-emiratesislamic.ae/en/news-a…</t>
+          <t>Emirates Islamic (@emiratesislamic) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
+The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
+All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
+The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
+Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
+With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
+Read more: blocknewsint.com/articles/em…
+#EmiratesIslamic #DigitalBanking #IslamicFinance #PreciousMetals</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emirates Islamic has been awarded ‘Sustainable Finance Deal of the Year – Middle East’ at the Global Finance Sustainable Finance Awards 2026 for the issuance of the world’s first Sustainability‑Linked Financing Sukuk.
-Read the article:
-&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-wins-regional-award-at-global-finance-sustainable-finance-awards-2026"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+          <t>Emirates Islamic (&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
+The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
+All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
+The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
+Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
+With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
+Read more: &lt;a href="https://www.blocknewsint.com/articles/emirates-islamic-bank-launches-digital-precious-metals-investing-in-uae"&gt;blocknewsint.com/articles/em…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalBanking"&gt;#DigitalBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicFinance"&gt;#IslamicFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PreciousMetals"&gt;#PreciousMetals&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -755,23 +769,23 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 · 11:06 AM UTC</t>
+          <t>Apr 30, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-29T11:06:00Z</t>
+          <t>2026-04-30T08:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-wins-regional-award-at-global-finance-sustainable-finance-awards-2026']</t>
+          <t>['https://x.com/emiratesislamic', 'https://www.blocknewsint.com/articles/emirates-islamic-bank-launches-digital-precious-metals-investing-in-uae', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23DigitalBanking', 'https://x.com/search?f=tweets&amp;q=%23IslamicFinance', 'https://x.com/search?f=tweets&amp;q=%23PreciousMetals']</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -784,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -793,43 +807,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2049405822716072231</t>
+          <t>2049751774542848395</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/nimish_28/status/2049405822716072231</t>
+          <t>https://x.com/murtazaali2101/status/2049751774542848395</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/nimish_28</t>
+          <t>https://x.com/murtazaali2101</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nimish_28</t>
+          <t>murtazaali2101</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nimish</t>
+          <t>Murtaza Dharwala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/576399153195978752/hw5pNIVX_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1456168250409197570/cThnkexG_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>@Aramex How are we suppose to reach you in UAE. The delivery guys are not reachable, your support number doesnt allow an agent to speak and the chat is always one sided. How do we reach you? Will i ever get my shipment or should i ask my @emiratesislamic bank to cancel my card?</t>
+          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;a href="/Aramex" title="Aramex"&gt;@Aramex&lt;/a&gt; How are we suppose to reach you in UAE. The delivery guys are not reachable, your support number doesnt allow an agent to speak and the chat is always one sided. How do we reach you? Will i ever get my shipment or should i ask my &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; bank to cancel my card?</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; unable to update my passport details on the website, the page keeps loading kindly assist</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -839,27 +853,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 · 8:29 AM UTC</t>
+          <t>Apr 30, 2026 · 7:24 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-29T08:29:00Z</t>
+          <t>2026-04-30T07:24:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/Aramex',